--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A001791-9C59-4FB4-B0B4-1A0836B67B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBFF171B-8D14-4652-97B3-1B0B611A2D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3723" uniqueCount="3484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3725" uniqueCount="3486">
   <si>
     <t>криминальная</t>
   </si>
@@ -10597,6 +10597,12 @@
   </si>
   <si>
     <t>постоянное значение</t>
+  </si>
+  <si>
+    <t>реальность</t>
+  </si>
+  <si>
+    <t>действительность</t>
   </si>
 </sst>
 </file>
@@ -15155,7 +15161,12 @@
       </c>
     </row>
     <row r="504" spans="1:2">
-      <c r="A504" s="1"/>
+      <c r="A504" s="1" t="s">
+        <v>3484</v>
+      </c>
+      <c r="B504" t="s">
+        <v>3485</v>
+      </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" s="1" t="s">

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDCF2C6-64B2-48BF-9813-1E5FF5EE891A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1164128-87CA-4356-AE7F-8422A24C2239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20035" uniqueCount="3426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20051" uniqueCount="3442">
   <si>
     <t>криминальная</t>
   </si>
@@ -10421,6 +10421,54 @@
   </si>
   <si>
     <t>выполняемый дело</t>
+  </si>
+  <si>
+    <t>неконтролируемого</t>
+  </si>
+  <si>
+    <t>генератора</t>
+  </si>
+  <si>
+    <t>мыслеобраз</t>
+  </si>
+  <si>
+    <t>публикуется</t>
+  </si>
+  <si>
+    <t>обнародуется</t>
+  </si>
+  <si>
+    <t>публикует</t>
+  </si>
+  <si>
+    <t>обнародует</t>
+  </si>
+  <si>
+    <t>публикуют</t>
+  </si>
+  <si>
+    <t>обнародуют</t>
+  </si>
+  <si>
+    <t>преобразователя</t>
+  </si>
+  <si>
+    <t>аналогичная ситуация</t>
+  </si>
+  <si>
+    <t>аналогичный случай</t>
+  </si>
+  <si>
+    <t>неподвластного</t>
+  </si>
+  <si>
+    <t>по обстоятельству</t>
+  </si>
+  <si>
+    <t>по фактам</t>
+  </si>
+  <si>
+    <t>по обстоятельствам</t>
   </si>
 </sst>
 </file>
@@ -10917,7 +10965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCB9A67-77EF-4B4B-A409-BADD45AFE303}">
-  <dimension ref="A1:XFD1604"/>
+  <dimension ref="A1:XFD1609"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
@@ -72702,6 +72750,46 @@
       </c>
       <c r="B1604" t="s">
         <v>2739</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:2">
+      <c r="A1605" t="s">
+        <v>3429</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>3430</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:2">
+      <c r="A1606" t="s">
+        <v>3431</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>3432</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:2">
+      <c r="A1607" t="s">
+        <v>3433</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>3434</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:2">
+      <c r="A1608" t="s">
+        <v>3427</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:2">
+      <c r="A1609" t="s">
+        <v>3426</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>3438</v>
       </c>
     </row>
   </sheetData>
@@ -72719,7 +72807,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D669A2-CEB8-B743-9F48-CA926DA2420B}">
-  <dimension ref="A1:B226"/>
+  <dimension ref="A1:B229"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="51.26953125" customWidth="1"/>
@@ -74252,6 +74340,30 @@
       </c>
       <c r="B226" t="s">
         <v>235</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" t="s">
+        <v>3436</v>
+      </c>
+      <c r="B227" t="s">
+        <v>3437</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="15.75">
+      <c r="A228" s="16" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B228" t="s">
+        <v>3439</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="15.75">
+      <c r="A229" s="16" t="s">
+        <v>3440</v>
+      </c>
+      <c r="B229" t="s">
+        <v>3441</v>
       </c>
     </row>
   </sheetData>
@@ -74374,8 +74486,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A525149A-65EC-408A-9A2A-B87A37875F9B}">
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A88"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
+  <cols>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -74568,9 +74683,7 @@
       </c>
     </row>
     <row r="39" spans="1:1" ht="15.75">
-      <c r="A39" s="16" t="s">
-        <v>2804</v>
-      </c>
+      <c r="A39" s="16"/>
     </row>
     <row r="40" spans="1:1" ht="15.75">
       <c r="A40" s="16" t="s">
@@ -74795,6 +74908,11 @@
     <row r="84" spans="1:1">
       <c r="A84" t="s">
         <v>3388</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>3428</v>
       </c>
     </row>
   </sheetData>

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1164128-87CA-4356-AE7F-8422A24C2239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F107DB-2193-4B13-B95A-7C4816304E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Составные в 1 очередь" sheetId="5" r:id="rId4"/>
     <sheet name="не определено" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20051" uniqueCount="3442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19779" uniqueCount="3174">
   <si>
     <t>криминальная</t>
   </si>
@@ -6733,24 +6733,6 @@
   </si>
   <si>
     <t>важные сведения</t>
-  </si>
-  <si>
-    <t>общественный  положение</t>
-  </si>
-  <si>
-    <t>общественное положение</t>
-  </si>
-  <si>
-    <t xml:space="preserve">высокий общественное </t>
-  </si>
-  <si>
-    <t xml:space="preserve">высокое общественное </t>
-  </si>
-  <si>
-    <t xml:space="preserve">свободной соперничества </t>
-  </si>
-  <si>
-    <t xml:space="preserve">свободного соперничества </t>
   </si>
   <si>
     <t>эта аналогия</t>
@@ -6876,12 +6858,6 @@
     <t>эти сведения</t>
   </si>
   <si>
-    <t>важнейшую значение</t>
-  </si>
-  <si>
-    <t>важнейшее значение</t>
-  </si>
-  <si>
     <t>скандал</t>
   </si>
   <si>
@@ -6894,676 +6870,6 @@
     <t>необоснованн</t>
   </si>
   <si>
-    <t>в  воплощения</t>
-  </si>
-  <si>
-    <t>в  воплощении</t>
-  </si>
-  <si>
-    <t>вся обсуждение</t>
-  </si>
-  <si>
-    <t>всё обсуждение</t>
-  </si>
-  <si>
-    <t>ставшая ярлык</t>
-  </si>
-  <si>
-    <t>ставшая ярлыком</t>
-  </si>
-  <si>
-    <t>переносит, переносит</t>
-  </si>
-  <si>
-    <t>один обстоятельство</t>
-  </si>
-  <si>
-    <t>одно обстоятельство</t>
-  </si>
-  <si>
-    <t>в одинаковой случая</t>
-  </si>
-  <si>
-    <t>в одинаковом случае</t>
-  </si>
-  <si>
-    <t>семейный казна</t>
-  </si>
-  <si>
-    <t>семейная казна</t>
-  </si>
-  <si>
-    <r>
-      <t>та же</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve">самая правило </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">то же самое правило </t>
-  </si>
-  <si>
-    <t>достоверная сведения</t>
-  </si>
-  <si>
-    <t>достоверные сведения</t>
-  </si>
-  <si>
-    <r>
-      <t>управлять</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>животные позывы</t>
-    </r>
-  </si>
-  <si>
-    <t>управлять животными позывами</t>
-  </si>
-  <si>
-    <t>небольшой введение</t>
-  </si>
-  <si>
-    <t>небольшое введение</t>
-  </si>
-  <si>
-    <t>наибольший благополучие</t>
-  </si>
-  <si>
-    <t>наибольшее благополучие</t>
-  </si>
-  <si>
-    <t>той  сведениям</t>
-  </si>
-  <si>
-    <t>тем  сведениям</t>
-  </si>
-  <si>
-    <t>собственному мере</t>
-  </si>
-  <si>
-    <t>собственной мере</t>
-  </si>
-  <si>
-    <t xml:space="preserve">будущее возможности </t>
-  </si>
-  <si>
-    <t xml:space="preserve">будущие возможности </t>
-  </si>
-  <si>
-    <t>природный особенность</t>
-  </si>
-  <si>
-    <t>природная особенность</t>
-  </si>
-  <si>
-    <t>подобную сочетание</t>
-  </si>
-  <si>
-    <t>подобное сочетание</t>
-  </si>
-  <si>
-    <t>вызовет изъян</t>
-  </si>
-  <si>
-    <t>вызовет сбой</t>
-  </si>
-  <si>
-    <t>рукопись был правильным</t>
-  </si>
-  <si>
-    <t>рукопись была правильной</t>
-  </si>
-  <si>
-    <t>жёстко закодирован</t>
-  </si>
-  <si>
-    <t>жёстко задан</t>
-  </si>
-  <si>
-    <t>остальная ход мыслей</t>
-  </si>
-  <si>
-    <t>остальной ход мыслей</t>
-  </si>
-  <si>
-    <t>Согласно правил написания</t>
-  </si>
-  <si>
-    <t>многословную устройство</t>
-  </si>
-  <si>
-    <t>многословное устройство</t>
-  </si>
-  <si>
-    <t>подходящим соглашением</t>
-  </si>
-  <si>
-    <t>подходящим решением</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> о стопки</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> о стопке</t>
-  </si>
-  <si>
-    <t>случай, в которой</t>
-  </si>
-  <si>
-    <t>случай, в котором</t>
-  </si>
-  <si>
-    <t>ход мыслей которая</t>
-  </si>
-  <si>
-    <t>ход мыслей который</t>
-  </si>
-  <si>
-    <t>кодовой хранилища</t>
-  </si>
-  <si>
-    <t>хранилища рукописей</t>
-  </si>
-  <si>
-    <t>рукопись выполняющая</t>
-  </si>
-  <si>
-    <t>рукопись, выполняющую</t>
-  </si>
-  <si>
-    <t>основного рукописи</t>
-  </si>
-  <si>
-    <t>основной рукописи</t>
-  </si>
-  <si>
-    <t>вложенный среда</t>
-  </si>
-  <si>
-    <t>вложенная среда</t>
-  </si>
-  <si>
-    <t>написан рукопись</t>
-  </si>
-  <si>
-    <t>написана рукопись</t>
-  </si>
-  <si>
-    <t>рукопись имеющий</t>
-  </si>
-  <si>
-    <t>рукопись, имеющая</t>
-  </si>
-  <si>
-    <t>управлять устройство</t>
-  </si>
-  <si>
-    <t>управлять устройством</t>
-  </si>
-  <si>
-    <t>Рукопись следующий</t>
-  </si>
-  <si>
-    <t>Рукопись следующая</t>
-  </si>
-  <si>
-    <t>звено закрыт</t>
-  </si>
-  <si>
-    <t>звено закрыто</t>
-  </si>
-  <si>
-    <t>пустой проверка</t>
-  </si>
-  <si>
-    <t>пустую проверку</t>
-  </si>
-  <si>
-    <t>в последующей разделы</t>
-  </si>
-  <si>
-    <t>в последующих разделах</t>
-  </si>
-  <si>
-    <t>данную возможности</t>
-  </si>
-  <si>
-    <t>данные возможности</t>
-  </si>
-  <si>
-    <t>такую устройство</t>
-  </si>
-  <si>
-    <t>такое устройство</t>
-  </si>
-  <si>
-    <t>Разумная создание</t>
-  </si>
-  <si>
-    <t>Разумное создание</t>
-  </si>
-  <si>
-    <t>Пренебрегаем
-ими</t>
-  </si>
-  <si>
-    <t>выполняемое
-дело</t>
-  </si>
-  <si>
-    <t>в этой же папки</t>
-  </si>
-  <si>
-    <t>в этой же папке</t>
-  </si>
-  <si>
-    <t>Такая создание</t>
-  </si>
-  <si>
-    <t>Такое создание</t>
-  </si>
-  <si>
-    <t>стороннего рукописи</t>
-  </si>
-  <si>
-    <t>сторонней рукописи</t>
-  </si>
-  <si>
-    <t>какой-либо рукописи</t>
-  </si>
-  <si>
-    <t>какая-либо рукописи</t>
-  </si>
-  <si>
-    <t>Рукопись собрался</t>
-  </si>
-  <si>
-    <t>Рукопись собралась</t>
-  </si>
-  <si>
-    <t>неиспользованным рукописью</t>
-  </si>
-  <si>
-    <t>неиспользованной рукописью</t>
-  </si>
-  <si>
-    <t>корневой звено</t>
-  </si>
-  <si>
-    <t>корневое звено</t>
-  </si>
-  <si>
-    <t>со разделами</t>
-  </si>
-  <si>
-    <t>с разделами</t>
-  </si>
-  <si>
-    <t>среда в котором</t>
-  </si>
-  <si>
-    <t>среда в которой</t>
-  </si>
-  <si>
-    <t>с исходным рукописью</t>
-  </si>
-  <si>
-    <t>с исходной рукописью</t>
-  </si>
-  <si>
-    <t>общей подходом</t>
-  </si>
-  <si>
-    <t>общим подходом</t>
-  </si>
-  <si>
-    <t>корневое раздел</t>
-  </si>
-  <si>
-    <t>корневой раздел</t>
-  </si>
-  <si>
-    <t>набор возможности</t>
-  </si>
-  <si>
-    <t>набор возможностей</t>
-  </si>
-  <si>
-    <t>дополнение, содержащий</t>
-  </si>
-  <si>
-    <t>дополнение, содержащее</t>
-  </si>
-  <si>
-    <t>своего рукописи</t>
-  </si>
-  <si>
-    <t>своей рукописи</t>
-  </si>
-  <si>
-    <t>ту же ход мыслей</t>
-  </si>
-  <si>
-    <t>тот же ход мыслей</t>
-  </si>
-  <si>
-    <t>первые части состоящей</t>
-  </si>
-  <si>
-    <t>первые части состоящие</t>
-  </si>
-  <si>
-    <t>рукописи, найденном</t>
-  </si>
-  <si>
-    <t>рукописи, найденной</t>
-  </si>
-  <si>
-    <t>связанного рукописи</t>
-  </si>
-  <si>
-    <t>связанной рукописи</t>
-  </si>
-  <si>
-    <t>на согласования рукописи</t>
-  </si>
-  <si>
-    <t>на согласовании рукописи</t>
-  </si>
-  <si>
-    <t>объединенном рукописи</t>
-  </si>
-  <si>
-    <t>объединенной рукописи</t>
-  </si>
-  <si>
-    <t>Данная изложение</t>
-  </si>
-  <si>
-    <t>Данное изложение</t>
-  </si>
-  <si>
-    <t>через проверка</t>
-  </si>
-  <si>
-    <t>через проверку</t>
-  </si>
-  <si>
-    <t>такой согласования рукописи</t>
-  </si>
-  <si>
-    <t>такого согласования рукописи</t>
-  </si>
-  <si>
-    <t>согласованном рукописи</t>
-  </si>
-  <si>
-    <t>согласованной рукописи</t>
-  </si>
-  <si>
-    <t>в корне устройство</t>
-  </si>
-  <si>
-    <t>в корне устройства</t>
-  </si>
-  <si>
-    <t>мы используется</t>
-  </si>
-  <si>
-    <t>мы используем</t>
-  </si>
-  <si>
-    <t>с такой же устройством</t>
-  </si>
-  <si>
-    <t>с таким же устройством</t>
-  </si>
-  <si>
-    <t>рукописью использующим</t>
-  </si>
-  <si>
-    <t>рукописью использующей</t>
-  </si>
-  <si>
-    <t>он ещё не собирается</t>
-  </si>
-  <si>
-    <t>она ещё не собирается</t>
-  </si>
-  <si>
-    <t>видеть среда</t>
-  </si>
-  <si>
-    <t>видеть среду</t>
-  </si>
-  <si>
-    <t>внутреннего рукописи</t>
-  </si>
-  <si>
-    <t>внутренней рукописи</t>
-  </si>
-  <si>
-    <t>внешнего рукописи</t>
-  </si>
-  <si>
-    <t>внешней рукописи</t>
-  </si>
-  <si>
-    <t>ход мыслей такая же</t>
-  </si>
-  <si>
-    <t>ход мыслей такой же</t>
-  </si>
-  <si>
-    <t>лучшие опытов</t>
-  </si>
-  <si>
-    <t>лучшие опыты</t>
-  </si>
-  <si>
-    <t>рукописью, написанным</t>
-  </si>
-  <si>
-    <t>рукописью, написанной</t>
-  </si>
-  <si>
-    <t>Данная стопки</t>
-  </si>
-  <si>
-    <t>Данная стопка</t>
-  </si>
-  <si>
-    <t>Иная выполнение</t>
-  </si>
-  <si>
-    <t>Иное выполнение</t>
-  </si>
-  <si>
-    <t>обнародованную размещение</t>
-  </si>
-  <si>
-    <t>обнародованное размещение</t>
-  </si>
-  <si>
-    <t>условной выполнения</t>
-  </si>
-  <si>
-    <t>условного выполнения</t>
-  </si>
-  <si>
-    <t>во второй указания</t>
-  </si>
-  <si>
-    <t>во втором указании</t>
-  </si>
-  <si>
-    <t>внешний дополнение</t>
-  </si>
-  <si>
-    <t>внешнее дополнение</t>
-  </si>
-  <si>
-    <t>среду, в котором</t>
-  </si>
-  <si>
-    <t>среду, в которой</t>
-  </si>
-  <si>
-    <t>две указания</t>
-  </si>
-  <si>
-    <t>два указания</t>
-  </si>
-  <si>
-    <t>одинаковым приставкой</t>
-  </si>
-  <si>
-    <t>одинаковой приставкой</t>
-  </si>
-  <si>
-    <t>в одной указания</t>
-  </si>
-  <si>
-    <t>в одном указании</t>
-  </si>
-  <si>
-    <t>одну указанию</t>
-  </si>
-  <si>
-    <t>одно указание</t>
-  </si>
-  <si>
-    <t>эта указание</t>
-  </si>
-  <si>
-    <t>это указание</t>
-  </si>
-  <si>
-    <t>из приложении</t>
-  </si>
-  <si>
-    <t>из приложения</t>
-  </si>
-  <si>
-    <t>создаём папка</t>
-  </si>
-  <si>
-    <t>создаём папку</t>
-  </si>
-  <si>
-    <t>создаем папка</t>
-  </si>
-  <si>
-    <t>создаем папку</t>
-  </si>
-  <si>
-    <t>в отдельный папка</t>
-  </si>
-  <si>
-    <t>в отдельную папку</t>
-  </si>
-  <si>
-    <t>текущий рабочий папка</t>
-  </si>
-  <si>
-    <t>текущая рабочая папка</t>
-  </si>
-  <si>
-    <t>обрабатывает папка</t>
-  </si>
-  <si>
-    <t>обрабатывает папку</t>
-  </si>
-  <si>
-    <t>создайте папка</t>
-  </si>
-  <si>
-    <t>создайте папку</t>
-  </si>
-  <si>
-    <t>один папка</t>
-  </si>
-  <si>
-    <t>одна папка</t>
-  </si>
-  <si>
-    <t>свой собственный папка</t>
-  </si>
-  <si>
-    <t>свою собственную папку</t>
-  </si>
-  <si>
-    <t>из папка</t>
-  </si>
-  <si>
-    <t>из папки</t>
-  </si>
-  <si>
-    <t>старый исполнение</t>
-  </si>
-  <si>
-    <t>старое исполнение</t>
-  </si>
-  <si>
-    <t>любым рукописью</t>
-  </si>
-  <si>
-    <t>любой рукописью</t>
-  </si>
-  <si>
-    <t>важный мгновение</t>
-  </si>
-  <si>
-    <t>важное мгновение</t>
-  </si>
-  <si>
-    <t>одновременную изменение</t>
-  </si>
-  <si>
-    <t>одновременное изменение</t>
-  </si>
-  <si>
-    <t>был бы возможность</t>
-  </si>
-  <si>
-    <t>была бы возможность</t>
-  </si>
-  <si>
     <t>то техника</t>
   </si>
   <si>
@@ -7576,171 +6882,12 @@
     <t>о действиях</t>
   </si>
   <si>
-    <t>повторение завершена</t>
-  </si>
-  <si>
-    <t>повторение завершено</t>
-  </si>
-  <si>
-    <t>равнозначным рукописи</t>
-  </si>
-  <si>
-    <t>равнозначной рукописи</t>
-  </si>
-  <si>
-    <t>к ярлыке</t>
-  </si>
-  <si>
-    <t>к ярлыку</t>
-  </si>
-  <si>
-    <t>чья ярлык</t>
-  </si>
-  <si>
-    <t>чей ярлык</t>
-  </si>
-  <si>
-    <t>второй свойство</t>
-  </si>
-  <si>
-    <t>второе свойство</t>
-  </si>
-  <si>
-    <t>данная выполнение</t>
-  </si>
-  <si>
-    <t>данное выполнение</t>
-  </si>
-  <si>
-    <t>более производительна</t>
-  </si>
-  <si>
-    <t>более производительно</t>
-  </si>
-  <si>
-    <t>ни один из его свойств</t>
-  </si>
-  <si>
-    <t>ни одно из его свойств</t>
-  </si>
-  <si>
-    <t>неверный рукопись</t>
-  </si>
-  <si>
-    <t>неверная рукопись</t>
-  </si>
-  <si>
-    <t>необходимую преобразование</t>
-  </si>
-  <si>
-    <t>необходимое преобразование</t>
-  </si>
-  <si>
-    <t>В встроенной</t>
-  </si>
-  <si>
-    <t>Во встроенной</t>
-  </si>
-  <si>
-    <t>Эта ярлык</t>
-  </si>
-  <si>
-    <t>Этот ярлык</t>
-  </si>
-  <si>
-    <t>добавлен рукопись</t>
-  </si>
-  <si>
-    <t>добавлена рукопись</t>
-  </si>
-  <si>
-    <t>определён второе</t>
-  </si>
-  <si>
-    <t>определено второе</t>
-  </si>
-  <si>
-    <t>допустимым рукописью</t>
-  </si>
-  <si>
-    <t>допустимой рукописью</t>
-  </si>
-  <si>
-    <t>приведён рукопись</t>
-  </si>
-  <si>
-    <t>приведена рукопись</t>
-  </si>
-  <si>
-    <t>с этой сведениями</t>
-  </si>
-  <si>
-    <t>с этими сведениями</t>
-  </si>
-  <si>
-    <t>правильная преобразование</t>
-  </si>
-  <si>
-    <t>правильное преобразование</t>
-  </si>
-  <si>
-    <t>в выполнения</t>
-  </si>
-  <si>
-    <t>в выполнении</t>
-  </si>
-  <si>
-    <t>вызывающему рукописи</t>
-  </si>
-  <si>
-    <t>вызывающей рукописи</t>
-  </si>
-  <si>
-    <t>определённую ход мыслей</t>
-  </si>
-  <si>
-    <t>определённый ход мыслей</t>
-  </si>
-  <si>
-    <t>ход мыслей, которая</t>
-  </si>
-  <si>
-    <t>ход мыслей, который</t>
-  </si>
-  <si>
-    <t>вся ход мыслей</t>
-  </si>
-  <si>
-    <t>весь ход мыслей</t>
-  </si>
-  <si>
-    <t>ход мыслей, которую</t>
-  </si>
-  <si>
-    <t>Этот дополнение</t>
-  </si>
-  <si>
-    <t>Это дополнение</t>
-  </si>
-  <si>
-    <t>эта руководство</t>
-  </si>
-  <si>
-    <t>это руководство</t>
-  </si>
-  <si>
     <t>обобщим</t>
   </si>
   <si>
     <t>на практике</t>
   </si>
   <si>
-    <t>одну действие</t>
-  </si>
-  <si>
-    <t>одно действие</t>
-  </si>
-  <si>
     <t>Эта же концепция</t>
   </si>
   <si>
@@ -7759,24 +6906,6 @@
     <t>этот порядок</t>
   </si>
   <si>
-    <t>данный мгновение</t>
-  </si>
-  <si>
-    <t>данное мгновение</t>
-  </si>
-  <si>
-    <t>текущий мгновение</t>
-  </si>
-  <si>
-    <t>текущее мгновение</t>
-  </si>
-  <si>
-    <t>начало строки</t>
-  </si>
-  <si>
-    <t>Правила написания</t>
-  </si>
-  <si>
     <t>анти</t>
   </si>
   <si>
@@ -8584,12 +7713,6 @@
     <t>автор</t>
   </si>
   <si>
-    <t>объектного</t>
-  </si>
-  <si>
-    <t>предметного</t>
-  </si>
-  <si>
     <t>аксессуарах</t>
   </si>
   <si>
@@ -8671,21 +7794,12 @@
     <t>чрезвычайное</t>
   </si>
   <si>
-    <t>эту случай</t>
-  </si>
-  <si>
     <t>стратегическое</t>
   </si>
   <si>
     <t>физическое</t>
   </si>
   <si>
-    <t>В чрезвычайной случая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В чрезвычайном случае </t>
-  </si>
-  <si>
     <t>нормализовано</t>
   </si>
   <si>
@@ -10417,12 +9531,6 @@
     <t>приложения</t>
   </si>
   <si>
-    <t>Пренебрегаем их</t>
-  </si>
-  <si>
-    <t>выполняемый дело</t>
-  </si>
-  <si>
     <t>неконтролируемого</t>
   </si>
   <si>
@@ -10469,6 +9577,48 @@
   </si>
   <si>
     <t>по обстоятельствам</t>
+  </si>
+  <si>
+    <t>скандала</t>
+  </si>
+  <si>
+    <t>раздора</t>
+  </si>
+  <si>
+    <t>скандалы</t>
+  </si>
+  <si>
+    <t>раздоры</t>
+  </si>
+  <si>
+    <t>скандалу</t>
+  </si>
+  <si>
+    <t>раздору</t>
+  </si>
+  <si>
+    <t>скандалов</t>
+  </si>
+  <si>
+    <t>раздоров</t>
+  </si>
+  <si>
+    <t>скандальные</t>
+  </si>
+  <si>
+    <t>раздорные</t>
+  </si>
+  <si>
+    <t>скандальных</t>
+  </si>
+  <si>
+    <t>раздорных</t>
+  </si>
+  <si>
+    <t>скандальную</t>
+  </si>
+  <si>
+    <t>раздорную</t>
   </si>
 </sst>
 </file>
@@ -10598,7 +9748,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -10624,9 +9774,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -10965,7 +10112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCB9A67-77EF-4B4B-A409-BADD45AFE303}">
-  <dimension ref="A1:XFD1609"/>
+  <dimension ref="A1:XFD1617"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
@@ -11342,11 +10489,11 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="15.75">
-      <c r="A48" s="16" t="s">
-        <v>2791</v>
+      <c r="A48" s="15" t="s">
+        <v>2516</v>
       </c>
       <c r="B48" t="s">
-        <v>2792</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -11383,10 +10530,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>2794</v>
+        <v>2519</v>
       </c>
       <c r="B53" t="s">
-        <v>2795</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -11421,10 +10568,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>2797</v>
+        <v>2522</v>
       </c>
       <c r="B57" t="s">
-        <v>2798</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -11510,7 +10657,7 @@
         <v>1711</v>
       </c>
       <c r="D67" t="s">
-        <v>2720</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -11606,10 +10753,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>2800</v>
+        <v>2525</v>
       </c>
       <c r="B79" t="s">
-        <v>2799</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -11710,10 +10857,10 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>2564</v>
+        <v>2289</v>
       </c>
       <c r="B92" t="s">
-        <v>2565</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -11889,10 +11036,10 @@
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>2801</v>
+        <v>2526</v>
       </c>
       <c r="B114" t="s">
-        <v>2802</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -11945,18 +11092,18 @@
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="1" t="s">
-        <v>2809</v>
+        <v>2534</v>
       </c>
       <c r="B122" t="s">
-        <v>2810</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="1" t="s">
-        <v>2816</v>
+        <v>2539</v>
       </c>
       <c r="B124" t="s">
-        <v>2817</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -13187,34 +12334,34 @@
     </row>
     <row r="283" spans="1:3">
       <c r="A283" s="1" t="s">
-        <v>2825</v>
+        <v>2548</v>
       </c>
       <c r="B283" t="s">
-        <v>2822</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="284" spans="1:3">
       <c r="A284" s="1" t="s">
-        <v>2823</v>
+        <v>2546</v>
       </c>
       <c r="B284" t="s">
-        <v>2824</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="285" spans="1:3">
       <c r="A285" s="1" t="s">
-        <v>2821</v>
+        <v>2544</v>
       </c>
       <c r="B285" t="s">
-        <v>2822</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" s="1" t="s">
-        <v>2819</v>
+        <v>2542</v>
       </c>
       <c r="B286" t="s">
-        <v>2820</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -13510,7 +12657,7 @@
       </c>
     </row>
     <row r="323" spans="1:2" ht="15.75">
-      <c r="A323" s="16"/>
+      <c r="A323" s="15"/>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
@@ -13565,10 +12712,10 @@
     </row>
     <row r="331" spans="1:2">
       <c r="A331" s="4" t="s">
-        <v>2828</v>
+        <v>2551</v>
       </c>
       <c r="B331" t="s">
-        <v>2829</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -14339,10 +13486,10 @@
     </row>
     <row r="427" spans="1:3">
       <c r="A427" s="1" t="s">
-        <v>2553</v>
+        <v>2278</v>
       </c>
       <c r="B427" t="s">
-        <v>2554</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="428" spans="1:3">
@@ -14430,10 +13577,10 @@
     </row>
     <row r="438" spans="1:3">
       <c r="A438" s="1" t="s">
-        <v>2551</v>
+        <v>2276</v>
       </c>
       <c r="B438" t="s">
-        <v>2552</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -14957,10 +14104,10 @@
     </row>
     <row r="504" spans="1:2">
       <c r="A504" s="1" t="s">
-        <v>3401</v>
+        <v>3121</v>
       </c>
       <c r="B504" t="s">
-        <v>3402</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="505" spans="1:2">
@@ -15644,7 +14791,7 @@
         <v>730</v>
       </c>
       <c r="B588" t="s">
-        <v>2528</v>
+        <v>2261</v>
       </c>
       <c r="C588" t="s">
         <v>731</v>
@@ -15658,7 +14805,7 @@
         <v>1097</v>
       </c>
       <c r="B590" t="s">
-        <v>3143</v>
+        <v>2863</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -15934,7 +15081,7 @@
         <v>1157</v>
       </c>
       <c r="B625" t="s">
-        <v>2559</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="626" spans="1:3">
@@ -17135,7 +16282,7 @@
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>3416</v>
+        <v>3136</v>
       </c>
       <c r="B776" t="s">
         <v>315</v>
@@ -17143,7 +16290,7 @@
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>3415</v>
+        <v>3135</v>
       </c>
       <c r="B777" t="s">
         <v>1116</v>
@@ -17151,10 +16298,10 @@
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>3413</v>
+        <v>3133</v>
       </c>
       <c r="B778" t="s">
-        <v>3414</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="779" spans="1:2">
@@ -17199,7 +16346,7 @@
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>3417</v>
+        <v>3137</v>
       </c>
       <c r="B784" t="s">
         <v>1462</v>
@@ -17367,10 +16514,10 @@
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>3422</v>
+        <v>3142</v>
       </c>
       <c r="B807" t="s">
-        <v>3423</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="808" spans="1:2">
@@ -17789,10 +16936,10 @@
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>3405</v>
+        <v>3125</v>
       </c>
       <c r="B863" t="s">
-        <v>3406</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="864" spans="1:2">
@@ -17805,34 +16952,34 @@
     </row>
     <row r="865" spans="1:3">
       <c r="A865" t="s">
-        <v>3403</v>
+        <v>3123</v>
       </c>
       <c r="B865" t="s">
-        <v>3404</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="866" spans="1:3">
       <c r="A866" t="s">
-        <v>3407</v>
+        <v>3127</v>
       </c>
       <c r="B866" t="s">
-        <v>3408</v>
+        <v>3128</v>
       </c>
     </row>
     <row r="867" spans="1:3">
       <c r="A867" t="s">
-        <v>3409</v>
+        <v>3129</v>
       </c>
       <c r="B867" t="s">
-        <v>3410</v>
+        <v>3130</v>
       </c>
     </row>
     <row r="868" spans="1:3">
       <c r="A868" t="s">
-        <v>3411</v>
+        <v>3131</v>
       </c>
       <c r="B868" t="s">
-        <v>3412</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="869" spans="1:3">
@@ -18084,18 +17231,18 @@
     <row r="901" spans="1:16384" customFormat="1"/>
     <row r="902" spans="1:16384" customFormat="1">
       <c r="A902" t="s">
-        <v>3419</v>
+        <v>3139</v>
       </c>
       <c r="B902" t="s">
-        <v>3420</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="903" spans="1:16384" customFormat="1">
       <c r="A903" t="s">
-        <v>3418</v>
+        <v>3138</v>
       </c>
       <c r="B903" t="s">
-        <v>3421</v>
+        <v>3141</v>
       </c>
       <c r="C903" t="s">
         <v>1663</v>
@@ -68228,10 +67375,10 @@
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>2261</v>
+        <v>2253</v>
       </c>
       <c r="B1034" t="s">
-        <v>2262</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
@@ -69516,63 +68663,63 @@
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>2263</v>
+        <v>2255</v>
       </c>
       <c r="B1201" t="s">
-        <v>2264</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>2555</v>
+        <v>2280</v>
       </c>
       <c r="B1202" t="s">
-        <v>2556</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>2557</v>
+        <v>2282</v>
       </c>
       <c r="B1203" t="s">
-        <v>2558</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>2560</v>
+        <v>2285</v>
       </c>
       <c r="B1204" t="s">
-        <v>2561</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>2566</v>
+        <v>2291</v>
       </c>
       <c r="B1205" t="s">
-        <v>2567</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>2568</v>
+        <v>2293</v>
       </c>
       <c r="B1206" t="s">
-        <v>2569</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>2572</v>
+        <v>2297</v>
       </c>
       <c r="B1207" t="s">
-        <v>2573</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>2574</v>
+        <v>2299</v>
       </c>
       <c r="B1208" t="s">
         <v>780</v>
@@ -69580,47 +68727,47 @@
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" t="s">
-        <v>2575</v>
+        <v>2300</v>
       </c>
       <c r="B1209" t="s">
-        <v>2576</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="1210" spans="1:2">
       <c r="A1210" t="s">
-        <v>2577</v>
+        <v>2302</v>
       </c>
       <c r="B1210" t="s">
-        <v>2578</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="1211" spans="1:2">
       <c r="A1211" t="s">
-        <v>2579</v>
+        <v>2304</v>
       </c>
       <c r="B1211" t="s">
-        <v>2580</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="1212" spans="1:2">
       <c r="A1212" t="s">
-        <v>2581</v>
+        <v>2306</v>
       </c>
       <c r="B1212" t="s">
-        <v>2582</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="1213" spans="1:2">
       <c r="A1213" t="s">
-        <v>2585</v>
+        <v>2310</v>
       </c>
       <c r="B1213" t="s">
-        <v>2586</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="1214" spans="1:2">
       <c r="A1214" t="s">
-        <v>2587</v>
+        <v>2312</v>
       </c>
       <c r="B1214" t="s">
         <v>963</v>
@@ -69628,55 +68775,55 @@
     </row>
     <row r="1215" spans="1:2">
       <c r="A1215" t="s">
-        <v>2588</v>
+        <v>2313</v>
       </c>
       <c r="B1215" t="s">
-        <v>2589</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="1216" spans="1:2">
       <c r="A1216" t="s">
-        <v>2590</v>
+        <v>2315</v>
       </c>
       <c r="B1216" t="s">
-        <v>2591</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="1217" spans="1:2">
       <c r="A1217" t="s">
-        <v>2592</v>
+        <v>2317</v>
       </c>
       <c r="B1217" t="s">
-        <v>2593</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="1218" spans="1:2">
       <c r="A1218" t="s">
-        <v>2599</v>
+        <v>2324</v>
       </c>
       <c r="B1218" t="s">
-        <v>2594</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="1219" spans="1:2">
       <c r="A1219" t="s">
-        <v>2595</v>
+        <v>2320</v>
       </c>
       <c r="B1219" t="s">
-        <v>2596</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="1220" spans="1:2">
       <c r="A1220" t="s">
-        <v>2597</v>
+        <v>2322</v>
       </c>
       <c r="B1220" t="s">
-        <v>2598</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="1221" spans="1:2">
       <c r="A1221" t="s">
-        <v>2735</v>
+        <v>2460</v>
       </c>
       <c r="B1221" t="s">
         <v>1693</v>
@@ -69684,167 +68831,167 @@
     </row>
     <row r="1222" spans="1:2">
       <c r="A1222" t="s">
-        <v>2600</v>
+        <v>2325</v>
       </c>
       <c r="B1222" t="s">
-        <v>2601</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="1223" spans="1:2">
       <c r="A1223" t="s">
-        <v>2603</v>
+        <v>2328</v>
       </c>
       <c r="B1223" t="s">
-        <v>2604</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="1224" spans="1:2">
       <c r="A1224" t="s">
-        <v>2605</v>
+        <v>2330</v>
       </c>
       <c r="B1224" t="s">
-        <v>2606</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="1226" spans="1:2">
       <c r="A1226" t="s">
-        <v>2607</v>
+        <v>2332</v>
       </c>
       <c r="B1226" t="s">
-        <v>2608</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="1227" spans="1:2">
       <c r="A1227" t="s">
-        <v>2609</v>
+        <v>2334</v>
       </c>
       <c r="B1227" t="s">
-        <v>2610</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="1228" spans="1:2">
       <c r="A1228" t="s">
-        <v>2611</v>
+        <v>2336</v>
       </c>
       <c r="B1228" t="s">
-        <v>2612</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="1229" spans="1:2">
       <c r="A1229" t="s">
-        <v>2614</v>
+        <v>2339</v>
       </c>
       <c r="B1229" t="s">
-        <v>2613</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="1230" spans="1:2">
       <c r="A1230" t="s">
-        <v>2615</v>
+        <v>2340</v>
       </c>
       <c r="B1230" t="s">
-        <v>2616</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="1231" spans="1:2">
       <c r="A1231" t="s">
-        <v>2617</v>
+        <v>2342</v>
       </c>
       <c r="B1231" t="s">
-        <v>2618</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="1232" spans="1:2">
       <c r="A1232" t="s">
-        <v>2619</v>
+        <v>2344</v>
       </c>
       <c r="B1232" t="s">
-        <v>2620</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="1233" spans="1:2">
       <c r="A1233" t="s">
-        <v>2621</v>
+        <v>2346</v>
       </c>
       <c r="B1233" t="s">
-        <v>2622</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="1234" spans="1:2">
       <c r="A1234" t="s">
-        <v>2623</v>
+        <v>2348</v>
       </c>
       <c r="B1234" t="s">
-        <v>2620</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="1235" spans="1:2">
       <c r="A1235" t="s">
-        <v>2634</v>
+        <v>2359</v>
       </c>
       <c r="B1235" t="s">
-        <v>2635</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="1236" spans="1:2">
       <c r="A1236" t="s">
-        <v>2636</v>
+        <v>2361</v>
       </c>
       <c r="B1236" t="s">
-        <v>2637</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="1237" spans="1:2">
       <c r="A1237" t="s">
-        <v>2638</v>
+        <v>2363</v>
       </c>
       <c r="B1237" t="s">
-        <v>2639</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="1238" spans="1:2">
       <c r="A1238" t="s">
-        <v>2640</v>
+        <v>2365</v>
       </c>
       <c r="B1238" t="s">
-        <v>2641</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="1239" spans="1:2">
       <c r="A1239" t="s">
-        <v>2642</v>
+        <v>2367</v>
       </c>
       <c r="B1239" t="s">
-        <v>2643</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="1240" spans="1:2">
       <c r="A1240" t="s">
-        <v>2644</v>
+        <v>2369</v>
       </c>
       <c r="B1240" t="s">
-        <v>2645</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="1241" spans="1:2">
       <c r="A1241" t="s">
-        <v>2646</v>
+        <v>2371</v>
       </c>
       <c r="B1241" t="s">
-        <v>2647</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="1242" spans="1:2">
       <c r="A1242" t="s">
-        <v>2648</v>
+        <v>2373</v>
       </c>
       <c r="B1242" t="s">
-        <v>2649</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="1243" spans="1:2">
       <c r="A1243" t="s">
-        <v>2650</v>
+        <v>2375</v>
       </c>
       <c r="B1243" t="s">
         <v>2181</v>
@@ -69852,7 +68999,7 @@
     </row>
     <row r="1244" spans="1:2">
       <c r="A1244" t="s">
-        <v>2651</v>
+        <v>2376</v>
       </c>
       <c r="B1244" t="s">
         <v>1580</v>
@@ -69860,31 +69007,31 @@
     </row>
     <row r="1245" spans="1:2">
       <c r="A1245" t="s">
-        <v>2652</v>
+        <v>2377</v>
       </c>
       <c r="B1245" t="s">
-        <v>2653</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="1246" spans="1:2">
       <c r="A1246" t="s">
-        <v>2654</v>
+        <v>2379</v>
       </c>
       <c r="B1246" t="s">
-        <v>2655</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="1248" spans="1:2">
       <c r="A1248" t="s">
-        <v>2658</v>
+        <v>2383</v>
       </c>
       <c r="B1248" t="s">
-        <v>2659</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="1249" spans="1:2" ht="15.75">
-      <c r="A1249" s="16" t="s">
-        <v>2830</v>
+      <c r="A1249" s="15" t="s">
+        <v>2553</v>
       </c>
       <c r="B1249" t="s">
         <v>1572</v>
@@ -69892,191 +69039,191 @@
     </row>
     <row r="1250" spans="1:2">
       <c r="A1250" t="s">
-        <v>2660</v>
+        <v>2385</v>
       </c>
       <c r="B1250" t="s">
-        <v>2661</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="1251" spans="1:2">
       <c r="A1251" t="s">
-        <v>2663</v>
+        <v>2388</v>
       </c>
       <c r="B1251" t="s">
-        <v>2664</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="1252" spans="1:2">
       <c r="A1252" t="s">
-        <v>2665</v>
+        <v>2390</v>
       </c>
       <c r="B1252" t="s">
-        <v>2666</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="1253" spans="1:2">
       <c r="A1253" t="s">
-        <v>2667</v>
+        <v>2392</v>
       </c>
       <c r="B1253" t="s">
-        <v>2668</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="1254" spans="1:2">
       <c r="A1254" t="s">
-        <v>2669</v>
+        <v>2394</v>
       </c>
       <c r="B1254" t="s">
-        <v>2670</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="1255" spans="1:2">
       <c r="A1255" t="s">
-        <v>2673</v>
+        <v>2398</v>
       </c>
       <c r="B1255" t="s">
-        <v>2674</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="1256" spans="1:2">
       <c r="A1256" t="s">
-        <v>2676</v>
+        <v>2401</v>
       </c>
       <c r="B1256" t="s">
-        <v>2677</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="1257" spans="1:2">
       <c r="A1257" t="s">
-        <v>2678</v>
+        <v>2403</v>
       </c>
       <c r="B1257" t="s">
-        <v>2679</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="1258" spans="1:2">
       <c r="A1258" t="s">
-        <v>2680</v>
+        <v>2405</v>
       </c>
       <c r="B1258" t="s">
-        <v>2681</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="1259" spans="1:2">
       <c r="A1259" t="s">
-        <v>2682</v>
+        <v>2407</v>
       </c>
       <c r="B1259" t="s">
-        <v>2683</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="1260" spans="1:2">
       <c r="A1260" t="s">
-        <v>2684</v>
+        <v>2409</v>
       </c>
       <c r="B1260" t="s">
-        <v>2686</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="1261" spans="1:2">
       <c r="A1261" t="s">
-        <v>2687</v>
+        <v>2412</v>
       </c>
       <c r="B1261" t="s">
-        <v>2688</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="1262" spans="1:2">
       <c r="A1262" t="s">
-        <v>2689</v>
+        <v>2414</v>
       </c>
       <c r="B1262" t="s">
-        <v>2690</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="1263" spans="1:2">
       <c r="A1263" t="s">
-        <v>2691</v>
+        <v>2416</v>
       </c>
       <c r="B1263" t="s">
-        <v>2692</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="1264" spans="1:2">
       <c r="A1264" t="s">
-        <v>2695</v>
+        <v>2420</v>
       </c>
       <c r="B1264" t="s">
-        <v>2696</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="1265" spans="1:2">
       <c r="A1265" t="s">
-        <v>2698</v>
+        <v>2423</v>
       </c>
       <c r="B1265" t="s">
-        <v>2699</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="1266" spans="1:2">
       <c r="A1266" t="s">
-        <v>2702</v>
+        <v>2427</v>
       </c>
       <c r="B1266" t="s">
-        <v>2703</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="1267" spans="1:2">
       <c r="A1267" t="s">
-        <v>2704</v>
+        <v>2429</v>
       </c>
       <c r="B1267" t="s">
-        <v>2705</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="1268" spans="1:2">
       <c r="A1268" t="s">
-        <v>2706</v>
+        <v>2431</v>
       </c>
       <c r="B1268" t="s">
-        <v>2707</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="1269" spans="1:2">
       <c r="A1269" t="s">
-        <v>2708</v>
+        <v>2433</v>
       </c>
       <c r="B1269" t="s">
-        <v>2703</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="1270" spans="1:2">
       <c r="A1270" t="s">
-        <v>2711</v>
+        <v>2436</v>
       </c>
       <c r="B1270" t="s">
-        <v>2712</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="1271" spans="1:2">
       <c r="A1271" t="s">
-        <v>2788</v>
+        <v>2513</v>
       </c>
       <c r="B1271" t="s">
-        <v>2789</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="1272" spans="1:2">
       <c r="A1272" t="s">
-        <v>2717</v>
+        <v>2442</v>
       </c>
       <c r="B1272" t="s">
-        <v>2718</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="1273" spans="1:2">
       <c r="A1273" t="s">
-        <v>2719</v>
+        <v>2444</v>
       </c>
       <c r="B1273" t="s">
         <v>1512</v>
@@ -70084,127 +69231,127 @@
     </row>
     <row r="1274" spans="1:2">
       <c r="A1274" t="s">
-        <v>2786</v>
+        <v>2511</v>
       </c>
       <c r="B1274" t="s">
-        <v>2787</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="1275" spans="1:2">
       <c r="A1275" t="s">
-        <v>2721</v>
+        <v>2446</v>
       </c>
       <c r="B1275" t="s">
-        <v>2722</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="1276" spans="1:2">
       <c r="A1276" t="s">
-        <v>2723</v>
+        <v>2448</v>
       </c>
       <c r="B1276" t="s">
-        <v>2724</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="1277" spans="1:2">
       <c r="A1277" t="s">
-        <v>2725</v>
+        <v>2450</v>
       </c>
       <c r="B1277" t="s">
-        <v>2726</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="1278" spans="1:2">
       <c r="A1278" t="s">
-        <v>2727</v>
+        <v>2452</v>
       </c>
       <c r="B1278" t="s">
-        <v>2728</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="1279" spans="1:2">
       <c r="A1279" t="s">
-        <v>2729</v>
+        <v>2454</v>
       </c>
       <c r="B1279" t="s">
-        <v>2730</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="1280" spans="1:2">
       <c r="A1280" t="s">
-        <v>2731</v>
+        <v>2456</v>
       </c>
       <c r="B1280" t="s">
-        <v>2732</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="1281" spans="1:2">
       <c r="A1281" t="s">
-        <v>2733</v>
+        <v>2458</v>
       </c>
       <c r="B1281" t="s">
-        <v>2734</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="1282" spans="1:2">
       <c r="A1282" t="s">
-        <v>2740</v>
-      </c>
-      <c r="B1282" s="15" t="s">
-        <v>2741</v>
+        <v>2465</v>
+      </c>
+      <c r="B1282" s="14" t="s">
+        <v>2466</v>
       </c>
     </row>
     <row r="1283" spans="1:2">
       <c r="A1283" t="s">
-        <v>2742</v>
-      </c>
-      <c r="B1283" s="15" t="s">
-        <v>2743</v>
+        <v>2467</v>
+      </c>
+      <c r="B1283" s="14" t="s">
+        <v>2468</v>
       </c>
     </row>
     <row r="1284" spans="1:2">
       <c r="A1284" t="s">
-        <v>2744</v>
-      </c>
-      <c r="B1284" s="15" t="s">
-        <v>2745</v>
+        <v>2469</v>
+      </c>
+      <c r="B1284" s="14" t="s">
+        <v>2470</v>
       </c>
     </row>
     <row r="1285" spans="1:2">
       <c r="A1285" t="s">
-        <v>2746</v>
+        <v>2471</v>
       </c>
       <c r="B1285" t="s">
-        <v>2747</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="1286" spans="1:2">
       <c r="A1286" t="s">
-        <v>2748</v>
+        <v>2473</v>
       </c>
       <c r="B1286" t="s">
-        <v>2749</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="1287" spans="1:2">
       <c r="A1287" t="s">
-        <v>2750</v>
+        <v>2475</v>
       </c>
       <c r="B1287" t="s">
-        <v>2751</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="1288" spans="1:2">
       <c r="A1288" t="s">
-        <v>2752</v>
+        <v>2477</v>
       </c>
       <c r="B1288" t="s">
-        <v>2753</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="1289" spans="1:2">
       <c r="A1289" t="s">
-        <v>2754</v>
+        <v>2479</v>
       </c>
       <c r="B1289" t="s">
         <v>559</v>
@@ -70212,23 +69359,23 @@
     </row>
     <row r="1290" spans="1:2">
       <c r="A1290" t="s">
-        <v>2755</v>
+        <v>2480</v>
       </c>
       <c r="B1290" t="s">
-        <v>2756</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="1291" spans="1:2">
       <c r="A1291" t="s">
-        <v>2757</v>
+        <v>2482</v>
       </c>
       <c r="B1291" t="s">
-        <v>2758</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="1292" spans="1:2">
       <c r="A1292" t="s">
-        <v>2761</v>
+        <v>2486</v>
       </c>
       <c r="B1292" t="s">
         <v>1826</v>
@@ -70236,159 +69383,159 @@
     </row>
     <row r="1293" spans="1:2">
       <c r="A1293" t="s">
-        <v>2762</v>
+        <v>2487</v>
       </c>
       <c r="B1293" t="s">
-        <v>2763</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="1294" spans="1:2">
       <c r="A1294" t="s">
-        <v>2764</v>
+        <v>2489</v>
       </c>
       <c r="B1294" t="s">
-        <v>2661</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="1295" spans="1:2">
       <c r="A1295" t="s">
-        <v>2765</v>
+        <v>2490</v>
       </c>
       <c r="B1295" t="s">
-        <v>2766</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="1296" spans="1:2">
       <c r="A1296" t="s">
-        <v>2767</v>
+        <v>2492</v>
       </c>
       <c r="B1296" t="s">
-        <v>2768</v>
+        <v>2493</v>
       </c>
     </row>
     <row r="1297" spans="1:2">
       <c r="A1297" t="s">
-        <v>2769</v>
+        <v>2494</v>
       </c>
       <c r="B1297" t="s">
-        <v>2770</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="1298" spans="1:2">
       <c r="A1298" t="s">
-        <v>2771</v>
+        <v>2496</v>
       </c>
       <c r="B1298" t="s">
-        <v>2772</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="1299" spans="1:2">
       <c r="A1299" t="s">
-        <v>2774</v>
+        <v>2499</v>
       </c>
       <c r="B1299" t="s">
-        <v>2773</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="1300" spans="1:2">
       <c r="A1300" t="s">
-        <v>2775</v>
+        <v>2500</v>
       </c>
       <c r="B1300" t="s">
-        <v>2776</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="1301" spans="1:2">
       <c r="A1301" t="s">
-        <v>2777</v>
+        <v>2502</v>
       </c>
       <c r="B1301" t="s">
-        <v>2781</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="1302" spans="1:2">
       <c r="A1302" t="s">
-        <v>2778</v>
+        <v>2503</v>
       </c>
       <c r="B1302" t="s">
-        <v>2779</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="1303" spans="1:2">
       <c r="A1303" t="s">
-        <v>2780</v>
+        <v>2505</v>
       </c>
       <c r="B1303" t="s">
-        <v>2781</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="1304" spans="1:2">
       <c r="A1304" t="s">
-        <v>2783</v>
+        <v>2508</v>
       </c>
       <c r="B1304" t="s">
-        <v>2784</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="1305" spans="1:2">
       <c r="A1305" s="1" t="s">
-        <v>2833</v>
+        <v>2556</v>
       </c>
       <c r="B1305" t="s">
-        <v>2831</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="1306" spans="1:2">
       <c r="A1306" s="1" t="s">
-        <v>2832</v>
+        <v>2555</v>
       </c>
       <c r="B1306" t="s">
-        <v>2834</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="1307" spans="1:2">
       <c r="A1307" t="s">
-        <v>2835</v>
+        <v>2558</v>
       </c>
       <c r="B1307" t="s">
-        <v>2836</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="1308" spans="1:2">
       <c r="A1308" t="s">
-        <v>2837</v>
+        <v>2560</v>
       </c>
       <c r="B1308" t="s">
-        <v>2838</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="1309" spans="1:2">
       <c r="A1309" t="s">
-        <v>2839</v>
+        <v>2562</v>
       </c>
       <c r="B1309" t="s">
-        <v>2840</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="1310" spans="1:2">
       <c r="A1310" t="s">
-        <v>3028</v>
+        <v>2748</v>
       </c>
       <c r="B1310" t="s">
-        <v>2841</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="1311" spans="1:2">
       <c r="A1311" t="s">
-        <v>3042</v>
+        <v>2762</v>
       </c>
       <c r="B1311" t="s">
-        <v>3043</v>
+        <v>2763</v>
       </c>
     </row>
     <row r="1312" spans="1:2">
       <c r="A1312" t="s">
-        <v>2848</v>
+        <v>2568</v>
       </c>
       <c r="B1312" t="s">
         <v>1566</v>
@@ -70396,119 +69543,119 @@
     </row>
     <row r="1313" spans="1:2">
       <c r="A1313" t="s">
-        <v>2847</v>
+        <v>2567</v>
       </c>
       <c r="B1313" t="s">
-        <v>2849</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="1314" spans="1:2">
       <c r="A1314" t="s">
-        <v>2850</v>
+        <v>2570</v>
       </c>
       <c r="B1314" t="s">
-        <v>2851</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="1315" spans="1:2">
       <c r="A1315" t="s">
-        <v>2852</v>
+        <v>2572</v>
       </c>
       <c r="B1315" t="s">
-        <v>2853</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="1316" spans="1:2">
       <c r="A1316" t="s">
-        <v>2854</v>
+        <v>2574</v>
       </c>
       <c r="B1316" t="s">
-        <v>2855</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="1317" spans="1:2">
       <c r="A1317" t="s">
-        <v>2856</v>
+        <v>2576</v>
       </c>
       <c r="B1317" t="s">
-        <v>2857</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="1318" spans="1:2">
       <c r="A1318" t="s">
-        <v>2858</v>
+        <v>2578</v>
       </c>
       <c r="B1318" t="s">
-        <v>2861</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="1319" spans="1:2">
       <c r="A1319" t="s">
-        <v>2859</v>
+        <v>2579</v>
       </c>
       <c r="B1319" t="s">
-        <v>2860</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="1320" spans="1:2">
       <c r="A1320" t="s">
-        <v>2862</v>
+        <v>2582</v>
       </c>
       <c r="B1320" t="s">
-        <v>2861</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="1321" spans="1:2">
       <c r="A1321" t="s">
-        <v>2863</v>
+        <v>2583</v>
       </c>
       <c r="B1321" t="s">
-        <v>2864</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="1322" spans="1:2">
       <c r="A1322" t="s">
-        <v>2865</v>
+        <v>2585</v>
       </c>
       <c r="B1322" t="s">
-        <v>2866</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="1323" spans="1:2">
       <c r="A1323" t="s">
-        <v>2868</v>
+        <v>2588</v>
       </c>
       <c r="B1323" t="s">
-        <v>2867</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="1324" spans="1:2">
       <c r="A1324" t="s">
-        <v>2869</v>
+        <v>2589</v>
       </c>
       <c r="B1324" t="s">
-        <v>2870</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="1325" spans="1:2">
       <c r="A1325" t="s">
-        <v>3029</v>
+        <v>2749</v>
       </c>
       <c r="B1325" t="s">
-        <v>3030</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="1326" spans="1:2">
       <c r="A1326" t="s">
-        <v>2872</v>
+        <v>2592</v>
       </c>
       <c r="B1326" t="s">
-        <v>2873</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="1327" spans="1:2">
       <c r="A1327" t="s">
-        <v>2871</v>
+        <v>2591</v>
       </c>
       <c r="B1327" t="s">
         <v>527</v>
@@ -70516,47 +69663,47 @@
     </row>
     <row r="1328" spans="1:2">
       <c r="A1328" t="s">
-        <v>2875</v>
+        <v>2595</v>
       </c>
       <c r="B1328" t="s">
-        <v>2874</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="1329" spans="1:3">
       <c r="A1329" t="s">
-        <v>3031</v>
+        <v>2751</v>
       </c>
       <c r="B1329" t="s">
-        <v>2876</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="1330" spans="1:3">
       <c r="A1330" t="s">
-        <v>2877</v>
+        <v>2597</v>
       </c>
       <c r="B1330" t="s">
-        <v>2878</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="1331" spans="1:3">
       <c r="A1331" t="s">
-        <v>2879</v>
+        <v>2599</v>
       </c>
       <c r="B1331" t="s">
-        <v>2880</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="1332" spans="1:3">
       <c r="A1332" t="s">
-        <v>2881</v>
+        <v>2601</v>
       </c>
       <c r="B1332" t="s">
-        <v>2882</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="1333" spans="1:3">
       <c r="A1333" t="s">
-        <v>2883</v>
+        <v>2603</v>
       </c>
       <c r="B1333" t="s">
         <v>1037</v>
@@ -70564,26 +69711,26 @@
     </row>
     <row r="1334" spans="1:3">
       <c r="A1334" t="s">
-        <v>2812</v>
+        <v>2537</v>
       </c>
       <c r="B1334" t="s">
-        <v>2884</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="1335" spans="1:3">
       <c r="A1335" t="s">
-        <v>2885</v>
+        <v>2605</v>
       </c>
       <c r="B1335" t="s">
-        <v>2886</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="1336" spans="1:3">
       <c r="A1336" t="s">
-        <v>2887</v>
+        <v>2607</v>
       </c>
       <c r="B1336" t="s">
-        <v>2888</v>
+        <v>2608</v>
       </c>
       <c r="C1336" t="s">
         <v>2179</v>
@@ -70591,23 +69738,23 @@
     </row>
     <row r="1337" spans="1:3">
       <c r="A1337" t="s">
-        <v>2889</v>
+        <v>2609</v>
       </c>
       <c r="B1337" t="s">
-        <v>2890</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="1338" spans="1:3">
       <c r="A1338" t="s">
-        <v>2891</v>
+        <v>2611</v>
       </c>
       <c r="B1338" t="s">
-        <v>2892</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="1339" spans="1:3">
       <c r="A1339" t="s">
-        <v>2893</v>
+        <v>2613</v>
       </c>
       <c r="B1339" t="s">
         <v>189</v>
@@ -70615,7 +69762,7 @@
     </row>
     <row r="1340" spans="1:3">
       <c r="A1340" t="s">
-        <v>2894</v>
+        <v>2614</v>
       </c>
       <c r="B1340" t="s">
         <v>187</v>
@@ -70623,15 +69770,15 @@
     </row>
     <row r="1341" spans="1:3">
       <c r="A1341" t="s">
-        <v>3060</v>
+        <v>2780</v>
       </c>
       <c r="B1341" t="s">
-        <v>3061</v>
+        <v>2781</v>
       </c>
     </row>
     <row r="1342" spans="1:3">
       <c r="A1342" t="s">
-        <v>2895</v>
+        <v>2615</v>
       </c>
       <c r="B1342" t="s">
         <v>189</v>
@@ -70639,106 +69786,106 @@
     </row>
     <row r="1343" spans="1:3">
       <c r="A1343" t="s">
-        <v>2896</v>
+        <v>2616</v>
       </c>
       <c r="B1343" t="s">
-        <v>2897</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="1344" spans="1:3">
       <c r="A1344" t="s">
-        <v>2898</v>
+        <v>2618</v>
       </c>
       <c r="B1344" t="s">
-        <v>2899</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="1345" spans="1:3">
       <c r="A1345" t="s">
-        <v>2900</v>
+        <v>2620</v>
       </c>
       <c r="B1345" t="s">
-        <v>2901</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="1346" spans="1:3">
       <c r="A1346" t="s">
-        <v>2902</v>
+        <v>2622</v>
       </c>
       <c r="B1346" t="s">
-        <v>2903</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="1347" spans="1:3">
       <c r="A1347" t="s">
-        <v>2904</v>
+        <v>2624</v>
       </c>
       <c r="B1347" t="s">
-        <v>2905</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="1348" spans="1:3">
       <c r="A1348" t="s">
-        <v>2906</v>
+        <v>2626</v>
       </c>
       <c r="B1348" t="s">
-        <v>2907</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="1349" spans="1:3">
       <c r="A1349" t="s">
-        <v>2908</v>
+        <v>2628</v>
       </c>
       <c r="B1349" t="s">
-        <v>2909</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="1350" spans="1:3">
       <c r="A1350" t="s">
-        <v>2910</v>
+        <v>2630</v>
       </c>
       <c r="B1350" t="s">
-        <v>2911</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="1351" spans="1:3">
       <c r="A1351" t="s">
-        <v>2912</v>
+        <v>2632</v>
       </c>
       <c r="B1351" t="s">
-        <v>2913</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="1352" spans="1:3">
       <c r="A1352" t="s">
-        <v>2914</v>
+        <v>2634</v>
       </c>
       <c r="B1352" t="s">
-        <v>2915</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="1353" spans="1:3">
       <c r="A1353" t="s">
-        <v>2916</v>
+        <v>2636</v>
       </c>
       <c r="B1353" t="s">
-        <v>2917</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="1354" spans="1:3">
       <c r="A1354" t="s">
-        <v>2918</v>
+        <v>2638</v>
       </c>
       <c r="B1354" t="s">
-        <v>2919</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="1355" spans="1:3">
       <c r="A1355" t="s">
-        <v>2920</v>
+        <v>2640</v>
       </c>
       <c r="B1355" t="s">
-        <v>2921</v>
+        <v>2641</v>
       </c>
     </row>
     <row r="1356" spans="1:3">
@@ -70746,7 +69893,7 @@
         <v>1307</v>
       </c>
       <c r="B1356" t="s">
-        <v>2922</v>
+        <v>2642</v>
       </c>
       <c r="C1356" t="s">
         <v>1308</v>
@@ -70754,23 +69901,23 @@
     </row>
     <row r="1357" spans="1:3">
       <c r="A1357" t="s">
-        <v>2923</v>
+        <v>2643</v>
       </c>
       <c r="B1357" t="s">
-        <v>2924</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="1358" spans="1:3">
       <c r="A1358" t="s">
-        <v>2925</v>
+        <v>2645</v>
       </c>
       <c r="B1358" t="s">
-        <v>2926</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="1359" spans="1:3">
       <c r="A1359" t="s">
-        <v>2927</v>
+        <v>2647</v>
       </c>
       <c r="B1359" t="s">
         <v>2221</v>
@@ -70781,7 +69928,7 @@
         <v>1939</v>
       </c>
       <c r="B1360" t="s">
-        <v>2928</v>
+        <v>2648</v>
       </c>
       <c r="C1360" t="s">
         <v>1940</v>
@@ -70789,39 +69936,39 @@
     </row>
     <row r="1361" spans="1:2">
       <c r="A1361" t="s">
-        <v>2929</v>
+        <v>2649</v>
       </c>
       <c r="B1361" t="s">
-        <v>2930</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="1362" spans="1:2">
       <c r="A1362" t="s">
-        <v>2931</v>
+        <v>2651</v>
       </c>
       <c r="B1362" t="s">
-        <v>2932</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="1363" spans="1:2">
       <c r="A1363" t="s">
-        <v>2933</v>
+        <v>2653</v>
       </c>
       <c r="B1363" t="s">
-        <v>2934</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="1364" spans="1:2">
       <c r="A1364" t="s">
-        <v>2935</v>
+        <v>2655</v>
       </c>
       <c r="B1364" t="s">
-        <v>2936</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="1365" spans="1:2">
       <c r="A1365" t="s">
-        <v>2937</v>
+        <v>2657</v>
       </c>
       <c r="B1365" t="s">
         <v>496</v>
@@ -70829,7 +69976,7 @@
     </row>
     <row r="1366" spans="1:2">
       <c r="A1366" t="s">
-        <v>2938</v>
+        <v>2658</v>
       </c>
       <c r="B1366" t="s">
         <v>1995</v>
@@ -70837,79 +69984,79 @@
     </row>
     <row r="1367" spans="1:2">
       <c r="A1367" t="s">
-        <v>2939</v>
+        <v>2659</v>
       </c>
       <c r="B1367" t="s">
-        <v>2940</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="1368" spans="1:2">
       <c r="A1368" t="s">
-        <v>2941</v>
+        <v>2661</v>
       </c>
       <c r="B1368" t="s">
-        <v>2942</v>
+        <v>2662</v>
       </c>
     </row>
     <row r="1369" spans="1:2">
       <c r="A1369" t="s">
-        <v>2943</v>
+        <v>2663</v>
       </c>
       <c r="B1369" t="s">
-        <v>2944</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="1370" spans="1:2">
       <c r="A1370" t="s">
-        <v>2945</v>
+        <v>2665</v>
       </c>
       <c r="B1370" t="s">
-        <v>2946</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="1371" spans="1:2">
       <c r="A1371" t="s">
-        <v>2947</v>
+        <v>2667</v>
       </c>
       <c r="B1371" t="s">
-        <v>2948</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="1372" spans="1:2">
       <c r="A1372" t="s">
-        <v>2949</v>
+        <v>2669</v>
       </c>
       <c r="B1372" t="s">
-        <v>2950</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="1373" spans="1:2">
       <c r="A1373" t="s">
-        <v>2951</v>
+        <v>2671</v>
       </c>
       <c r="B1373" t="s">
-        <v>2946</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="1375" spans="1:2">
       <c r="A1375" t="s">
-        <v>2952</v>
+        <v>2672</v>
       </c>
       <c r="B1375" t="s">
-        <v>2953</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="1376" spans="1:2">
       <c r="A1376" t="s">
-        <v>2954</v>
+        <v>2674</v>
       </c>
       <c r="B1376" t="s">
-        <v>2955</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="1377" spans="1:3">
       <c r="A1377" t="s">
-        <v>2956</v>
+        <v>2676</v>
       </c>
       <c r="B1377" t="s">
         <v>492</v>
@@ -70917,15 +70064,15 @@
     </row>
     <row r="1378" spans="1:3">
       <c r="A1378" t="s">
-        <v>2957</v>
+        <v>2677</v>
       </c>
       <c r="B1378" t="s">
-        <v>2958</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="1379" spans="1:3">
       <c r="A1379" t="s">
-        <v>2959</v>
+        <v>2679</v>
       </c>
       <c r="B1379" t="s">
         <v>494</v>
@@ -70933,50 +70080,50 @@
     </row>
     <row r="1380" spans="1:3">
       <c r="A1380" t="s">
-        <v>2960</v>
+        <v>2680</v>
       </c>
       <c r="B1380" t="s">
-        <v>2961</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="1381" spans="1:3">
       <c r="A1381" t="s">
-        <v>2962</v>
+        <v>2682</v>
       </c>
       <c r="B1381" t="s">
-        <v>2963</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="1382" spans="1:3">
       <c r="A1382" t="s">
-        <v>2964</v>
+        <v>2684</v>
       </c>
       <c r="B1382" t="s">
-        <v>2965</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="1383" spans="1:3">
       <c r="A1383" t="s">
-        <v>2966</v>
+        <v>2686</v>
       </c>
       <c r="B1383" t="s">
-        <v>2967</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="1384" spans="1:3">
       <c r="A1384" t="s">
-        <v>2968</v>
+        <v>2688</v>
       </c>
       <c r="B1384" t="s">
-        <v>2969</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="1385" spans="1:3">
       <c r="A1385" t="s">
-        <v>2970</v>
+        <v>2690</v>
       </c>
       <c r="B1385" t="s">
-        <v>2836</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="1386" spans="1:3">
@@ -70984,7 +70131,7 @@
         <v>1489</v>
       </c>
       <c r="B1386" t="s">
-        <v>2834</v>
+        <v>2557</v>
       </c>
       <c r="C1386" t="s">
         <v>1490</v>
@@ -70992,42 +70139,42 @@
     </row>
     <row r="1387" spans="1:3">
       <c r="A1387" t="s">
-        <v>2971</v>
+        <v>2691</v>
       </c>
       <c r="B1387" t="s">
-        <v>2972</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="1388" spans="1:3">
       <c r="A1388" t="s">
-        <v>3036</v>
+        <v>2756</v>
       </c>
       <c r="B1388" t="s">
-        <v>2831</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="1389" spans="1:3">
       <c r="A1389" t="s">
-        <v>2973</v>
+        <v>2693</v>
       </c>
       <c r="B1389" t="s">
-        <v>2836</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="1390" spans="1:3">
       <c r="A1390" t="s">
-        <v>2974</v>
+        <v>2694</v>
       </c>
       <c r="B1390" t="s">
-        <v>2840</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="1391" spans="1:3">
       <c r="A1391" t="s">
-        <v>2975</v>
+        <v>2695</v>
       </c>
       <c r="B1391" t="s">
-        <v>2976</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="1392" spans="1:3">
@@ -71035,7 +70182,7 @@
         <v>654</v>
       </c>
       <c r="B1392" t="s">
-        <v>2841</v>
+        <v>2564</v>
       </c>
       <c r="C1392" t="s">
         <v>655</v>
@@ -71043,10 +70190,10 @@
     </row>
     <row r="1393" spans="1:3">
       <c r="A1393" t="s">
-        <v>2977</v>
+        <v>2697</v>
       </c>
       <c r="B1393" t="s">
-        <v>2978</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="1394" spans="1:3">
@@ -71054,15 +70201,15 @@
         <v>246</v>
       </c>
       <c r="B1394" t="s">
-        <v>2978</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="1395" spans="1:3">
       <c r="A1395" t="s">
-        <v>2979</v>
+        <v>2699</v>
       </c>
       <c r="B1395" t="s">
-        <v>2980</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="1396" spans="1:3">
@@ -71070,63 +70217,63 @@
         <v>247</v>
       </c>
       <c r="B1396" t="s">
-        <v>2981</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="1397" spans="1:3">
       <c r="A1397" t="s">
-        <v>2982</v>
+        <v>2702</v>
       </c>
       <c r="B1397" t="s">
-        <v>2983</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="1398" spans="1:3">
       <c r="A1398" t="s">
-        <v>2984</v>
+        <v>2704</v>
       </c>
       <c r="B1398" t="s">
-        <v>2985</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="1399" spans="1:3">
       <c r="A1399" t="s">
-        <v>2987</v>
+        <v>2707</v>
       </c>
       <c r="B1399" t="s">
-        <v>2986</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="1400" spans="1:3">
       <c r="A1400" t="s">
-        <v>2988</v>
+        <v>2708</v>
       </c>
       <c r="B1400" t="s">
-        <v>2989</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="1401" spans="1:3">
       <c r="A1401" t="s">
-        <v>2990</v>
+        <v>2710</v>
       </c>
       <c r="B1401" t="s">
-        <v>2991</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="1402" spans="1:3">
       <c r="A1402" t="s">
-        <v>2992</v>
+        <v>2712</v>
       </c>
       <c r="B1402" t="s">
-        <v>2986</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="1403" spans="1:3">
       <c r="A1403" t="s">
-        <v>2993</v>
+        <v>2713</v>
       </c>
       <c r="B1403" t="s">
-        <v>2994</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="1404" spans="1:3">
@@ -71134,7 +70281,7 @@
         <v>1746</v>
       </c>
       <c r="B1404" t="s">
-        <v>2995</v>
+        <v>2715</v>
       </c>
       <c r="C1404" t="s">
         <v>1747</v>
@@ -71142,79 +70289,79 @@
     </row>
     <row r="1405" spans="1:3">
       <c r="A1405" t="s">
-        <v>2996</v>
+        <v>2716</v>
       </c>
       <c r="B1405" t="s">
-        <v>2997</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="1406" spans="1:3">
       <c r="A1406" t="s">
-        <v>2998</v>
+        <v>2718</v>
       </c>
       <c r="B1406" t="s">
-        <v>2999</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="1407" spans="1:3">
       <c r="A1407" t="s">
-        <v>3000</v>
+        <v>2720</v>
       </c>
       <c r="B1407" t="s">
-        <v>3001</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="1408" spans="1:3">
       <c r="A1408" t="s">
-        <v>3002</v>
+        <v>2722</v>
       </c>
       <c r="B1408" t="s">
-        <v>3003</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="1409" spans="1:2">
       <c r="A1409" t="s">
-        <v>3004</v>
+        <v>2724</v>
       </c>
       <c r="B1409" t="s">
-        <v>3005</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="1410" spans="1:2">
       <c r="A1410" t="s">
-        <v>3006</v>
+        <v>2726</v>
       </c>
       <c r="B1410" t="s">
-        <v>3007</v>
+        <v>2727</v>
       </c>
     </row>
     <row r="1411" spans="1:2">
       <c r="A1411" t="s">
-        <v>3008</v>
+        <v>2728</v>
       </c>
       <c r="B1411" t="s">
-        <v>3005</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="1412" spans="1:2">
       <c r="A1412" t="s">
-        <v>3009</v>
+        <v>2729</v>
       </c>
       <c r="B1412" t="s">
-        <v>3010</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="1413" spans="1:2">
       <c r="A1413" t="s">
-        <v>3011</v>
+        <v>2731</v>
       </c>
       <c r="B1413" t="s">
-        <v>3012</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="1414" spans="1:2">
       <c r="A1414" t="s">
-        <v>3013</v>
+        <v>2733</v>
       </c>
       <c r="B1414" t="s">
         <v>1800</v>
@@ -71222,7 +70369,7 @@
     </row>
     <row r="1415" spans="1:2">
       <c r="A1415" t="s">
-        <v>3014</v>
+        <v>2734</v>
       </c>
       <c r="B1415" t="s">
         <v>1744</v>
@@ -71230,7 +70377,7 @@
     </row>
     <row r="1416" spans="1:2">
       <c r="A1416" t="s">
-        <v>3015</v>
+        <v>2735</v>
       </c>
       <c r="B1416" t="s">
         <v>1800</v>
@@ -71238,42 +70385,42 @@
     </row>
     <row r="1417" spans="1:2">
       <c r="A1417" t="s">
-        <v>3016</v>
+        <v>2736</v>
       </c>
       <c r="B1417" t="s">
-        <v>3017</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="1418" spans="1:2">
       <c r="A1418" t="s">
-        <v>3018</v>
+        <v>2738</v>
       </c>
       <c r="B1418" t="s">
-        <v>2810</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="1419" spans="1:2">
       <c r="A1419" t="s">
-        <v>2826</v>
+        <v>2549</v>
       </c>
       <c r="B1419" t="s">
-        <v>2827</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="1420" spans="1:2">
       <c r="A1420" t="s">
-        <v>3019</v>
+        <v>2739</v>
       </c>
       <c r="B1420" t="s">
-        <v>3020</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="1421" spans="1:2">
       <c r="A1421" t="s">
-        <v>3021</v>
+        <v>2741</v>
       </c>
       <c r="B1421" t="s">
-        <v>3022</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="1422" spans="1:2">
@@ -71281,7 +70428,7 @@
         <v>466</v>
       </c>
       <c r="B1422" t="s">
-        <v>3023</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="1423" spans="1:2">
@@ -71289,15 +70436,15 @@
         <v>49</v>
       </c>
       <c r="B1423" t="s">
-        <v>3024</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="1424" spans="1:2">
       <c r="A1424" t="s">
-        <v>3025</v>
+        <v>2745</v>
       </c>
       <c r="B1424" t="s">
-        <v>3026</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="1425" spans="1:2">
@@ -71305,28 +70452,28 @@
         <v>465</v>
       </c>
       <c r="B1425" t="s">
-        <v>3027</v>
+        <v>2747</v>
       </c>
     </row>
     <row r="1426" spans="1:2">
       <c r="A1426" t="s">
-        <v>3032</v>
+        <v>2752</v>
       </c>
       <c r="B1426" t="s">
-        <v>3033</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="1427" spans="1:2">
       <c r="A1427" t="s">
-        <v>3034</v>
+        <v>2754</v>
       </c>
       <c r="B1427" t="s">
-        <v>3035</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="1428" spans="1:2">
       <c r="A1428" t="s">
-        <v>3037</v>
+        <v>2757</v>
       </c>
       <c r="B1428" t="s">
         <v>1601</v>
@@ -71334,7 +70481,7 @@
     </row>
     <row r="1429" spans="1:2">
       <c r="A1429" t="s">
-        <v>3038</v>
+        <v>2758</v>
       </c>
       <c r="B1429" t="s">
         <v>138</v>
@@ -71342,7 +70489,7 @@
     </row>
     <row r="1430" spans="1:2">
       <c r="A1430" t="s">
-        <v>3039</v>
+        <v>2759</v>
       </c>
       <c r="B1430" t="s">
         <v>1601</v>
@@ -71350,23 +70497,23 @@
     </row>
     <row r="1431" spans="1:2">
       <c r="A1431" t="s">
-        <v>3040</v>
+        <v>2760</v>
       </c>
       <c r="B1431" t="s">
-        <v>3041</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="1432" spans="1:2">
       <c r="A1432" t="s">
-        <v>3044</v>
+        <v>2764</v>
       </c>
       <c r="B1432" t="s">
-        <v>3045</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="1433" spans="1:2">
       <c r="A1433" t="s">
-        <v>3046</v>
+        <v>2766</v>
       </c>
       <c r="B1433" t="s">
         <v>1490</v>
@@ -71374,263 +70521,263 @@
     </row>
     <row r="1434" spans="1:2">
       <c r="A1434" t="s">
-        <v>3047</v>
+        <v>2767</v>
       </c>
       <c r="B1434" t="s">
-        <v>3048</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="1435" spans="1:2">
       <c r="A1435" t="s">
-        <v>3049</v>
+        <v>2769</v>
       </c>
       <c r="B1435" t="s">
-        <v>3050</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="1436" spans="1:2">
       <c r="A1436" t="s">
-        <v>3051</v>
+        <v>2771</v>
       </c>
       <c r="B1436" t="s">
-        <v>3052</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="1437" spans="1:2">
       <c r="A1437" t="s">
-        <v>3053</v>
+        <v>2773</v>
       </c>
       <c r="B1437" t="s">
-        <v>3054</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="1438" spans="1:2">
       <c r="A1438" t="s">
-        <v>3055</v>
+        <v>2775</v>
       </c>
       <c r="B1438" t="s">
-        <v>3056</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="1439" spans="1:2">
       <c r="A1439" t="s">
-        <v>3057</v>
+        <v>2777</v>
       </c>
       <c r="B1439" t="s">
-        <v>3045</v>
+        <v>2765</v>
       </c>
     </row>
     <row r="1440" spans="1:2">
       <c r="A1440" t="s">
-        <v>3058</v>
+        <v>2778</v>
       </c>
       <c r="B1440" t="s">
-        <v>3059</v>
+        <v>2779</v>
       </c>
     </row>
     <row r="1441" spans="1:2">
       <c r="A1441" t="s">
-        <v>3062</v>
+        <v>2782</v>
       </c>
       <c r="B1441" t="s">
-        <v>3063</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="1442" spans="1:2">
       <c r="A1442" t="s">
-        <v>3064</v>
+        <v>2784</v>
       </c>
       <c r="B1442" t="s">
-        <v>3065</v>
+        <v>2785</v>
       </c>
     </row>
     <row r="1443" spans="1:2">
       <c r="A1443" t="s">
-        <v>3066</v>
+        <v>2786</v>
       </c>
       <c r="B1443" t="s">
-        <v>3067</v>
+        <v>2787</v>
       </c>
     </row>
     <row r="1444" spans="1:2">
       <c r="A1444" t="s">
-        <v>3068</v>
+        <v>2788</v>
       </c>
       <c r="B1444" t="s">
-        <v>3069</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="1445" spans="1:2">
       <c r="A1445" t="s">
-        <v>3070</v>
+        <v>2790</v>
       </c>
       <c r="B1445" t="s">
-        <v>3071</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="1446" spans="1:2">
       <c r="A1446" t="s">
-        <v>3072</v>
+        <v>2792</v>
       </c>
       <c r="B1446" t="s">
-        <v>3073</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="1447" spans="1:2">
       <c r="A1447" t="s">
-        <v>3074</v>
+        <v>2794</v>
       </c>
       <c r="B1447" t="s">
-        <v>2913</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="1448" spans="1:2">
       <c r="A1448" t="s">
-        <v>3075</v>
+        <v>2795</v>
       </c>
       <c r="B1448" t="s">
-        <v>3076</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="1449" spans="1:2">
       <c r="A1449" t="s">
-        <v>3077</v>
+        <v>2797</v>
       </c>
       <c r="B1449" t="s">
-        <v>3078</v>
+        <v>2798</v>
       </c>
     </row>
     <row r="1450" spans="1:2">
       <c r="A1450" t="s">
-        <v>3079</v>
+        <v>2799</v>
       </c>
       <c r="B1450" t="s">
-        <v>3080</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="1451" spans="1:2">
       <c r="A1451" t="s">
-        <v>3081</v>
+        <v>2801</v>
       </c>
       <c r="B1451" t="s">
-        <v>3082</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1452" spans="1:2">
       <c r="A1452" t="s">
-        <v>3083</v>
+        <v>2803</v>
       </c>
       <c r="B1452" t="s">
-        <v>3084</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="1453" spans="1:2">
       <c r="A1453" t="s">
-        <v>3085</v>
+        <v>2805</v>
       </c>
       <c r="B1453" t="s">
-        <v>3086</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="1454" spans="1:2">
       <c r="A1454" t="s">
-        <v>3087</v>
+        <v>2807</v>
       </c>
       <c r="B1454" t="s">
-        <v>3088</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="1455" spans="1:2">
       <c r="A1455" t="s">
-        <v>3089</v>
+        <v>2809</v>
       </c>
       <c r="B1455" t="s">
-        <v>3090</v>
+        <v>2810</v>
       </c>
     </row>
     <row r="1456" spans="1:2">
       <c r="A1456" t="s">
-        <v>3091</v>
+        <v>2811</v>
       </c>
       <c r="B1456" t="s">
-        <v>3092</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="1457" spans="1:2">
       <c r="A1457" t="s">
-        <v>3093</v>
+        <v>2813</v>
       </c>
       <c r="B1457" t="s">
-        <v>3094</v>
+        <v>2814</v>
       </c>
     </row>
     <row r="1458" spans="1:2">
       <c r="A1458" t="s">
-        <v>3095</v>
+        <v>2815</v>
       </c>
       <c r="B1458" t="s">
-        <v>2810</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="1459" spans="1:2">
       <c r="A1459" t="s">
-        <v>3096</v>
+        <v>2816</v>
       </c>
       <c r="B1459" t="s">
-        <v>3097</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="1460" spans="1:2">
       <c r="A1460" t="s">
-        <v>3098</v>
+        <v>2818</v>
       </c>
       <c r="B1460" t="s">
-        <v>3099</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="1461" spans="1:2">
       <c r="A1461" t="s">
-        <v>3100</v>
+        <v>2820</v>
       </c>
       <c r="B1461" t="s">
-        <v>3101</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="1462" spans="1:2">
       <c r="A1462" t="s">
-        <v>3102</v>
+        <v>2822</v>
       </c>
       <c r="B1462" t="s">
-        <v>3103</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="1463" spans="1:2">
       <c r="A1463" t="s">
-        <v>3104</v>
+        <v>2824</v>
       </c>
       <c r="B1463" t="s">
-        <v>3105</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="1464" spans="1:2">
       <c r="A1464" t="s">
-        <v>3106</v>
+        <v>2826</v>
       </c>
       <c r="B1464" t="s">
-        <v>3107</v>
+        <v>2827</v>
       </c>
     </row>
     <row r="1465" spans="1:2">
       <c r="A1465" t="s">
-        <v>2602</v>
+        <v>2327</v>
       </c>
       <c r="B1465" t="s">
-        <v>3108</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="1466" spans="1:2">
       <c r="A1466" t="s">
-        <v>3109</v>
+        <v>2829</v>
       </c>
       <c r="B1466" t="s">
         <v>15</v>
@@ -71638,122 +70785,122 @@
     </row>
     <row r="1467" spans="1:2">
       <c r="A1467" t="s">
-        <v>3110</v>
+        <v>2830</v>
       </c>
       <c r="B1467" t="s">
-        <v>3111</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="1468" spans="1:2">
       <c r="A1468" t="s">
-        <v>3112</v>
+        <v>2832</v>
       </c>
       <c r="B1468" t="s">
-        <v>3113</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="1469" spans="1:2">
       <c r="A1469" t="s">
-        <v>3114</v>
+        <v>2834</v>
       </c>
       <c r="B1469" t="s">
-        <v>3115</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="1470" spans="1:2">
       <c r="A1470" t="s">
-        <v>3116</v>
+        <v>2836</v>
       </c>
       <c r="B1470" t="s">
-        <v>3117</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="1471" spans="1:2">
       <c r="A1471" t="s">
-        <v>3118</v>
+        <v>2838</v>
       </c>
       <c r="B1471" t="s">
-        <v>3113</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="1472" spans="1:2">
       <c r="A1472" t="s">
-        <v>3119</v>
+        <v>2839</v>
       </c>
       <c r="B1472" t="s">
-        <v>3115</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="1473" spans="1:3">
       <c r="A1473" t="s">
-        <v>3120</v>
+        <v>2840</v>
       </c>
       <c r="B1473" t="s">
-        <v>3117</v>
+        <v>2837</v>
       </c>
     </row>
     <row r="1474" spans="1:3">
       <c r="A1474" t="s">
-        <v>3121</v>
+        <v>2841</v>
       </c>
       <c r="B1474" t="s">
-        <v>3113</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="1475" spans="1:3">
       <c r="A1475" t="s">
-        <v>3122</v>
+        <v>2842</v>
       </c>
       <c r="B1475" t="s">
-        <v>3123</v>
+        <v>2843</v>
       </c>
     </row>
     <row r="1476" spans="1:3">
       <c r="A1476" t="s">
-        <v>3124</v>
+        <v>2844</v>
       </c>
       <c r="B1476" t="s">
-        <v>3125</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="1477" spans="1:3">
       <c r="A1477" t="s">
-        <v>3126</v>
+        <v>2846</v>
       </c>
       <c r="B1477" t="s">
-        <v>3127</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="1478" spans="1:3">
       <c r="A1478" t="s">
-        <v>3128</v>
+        <v>2848</v>
       </c>
       <c r="B1478" t="s">
-        <v>3129</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="1479" spans="1:3">
       <c r="A1479" t="s">
-        <v>3130</v>
+        <v>2850</v>
       </c>
       <c r="B1479" t="s">
-        <v>3131</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="1480" spans="1:3">
       <c r="A1480" t="s">
-        <v>3132</v>
+        <v>2852</v>
       </c>
       <c r="B1480" t="s">
-        <v>3133</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="1481" spans="1:3">
       <c r="A1481" t="s">
-        <v>3134</v>
+        <v>2854</v>
       </c>
       <c r="B1481" t="s">
-        <v>2874</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="1482" spans="1:3">
@@ -71761,7 +70908,7 @@
         <v>611</v>
       </c>
       <c r="B1482" t="s">
-        <v>2873</v>
+        <v>2593</v>
       </c>
       <c r="C1482" t="s">
         <v>612</v>
@@ -71769,10 +70916,10 @@
     </row>
     <row r="1483" spans="1:3">
       <c r="A1483" t="s">
-        <v>3135</v>
+        <v>2855</v>
       </c>
       <c r="B1483" t="s">
-        <v>2867</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="1484" spans="1:3">
@@ -71788,7 +70935,7 @@
     </row>
     <row r="1485" spans="1:3">
       <c r="A1485" t="s">
-        <v>3139</v>
+        <v>2859</v>
       </c>
       <c r="B1485" t="s">
         <v>1120</v>
@@ -71796,7 +70943,7 @@
     </row>
     <row r="1486" spans="1:3">
       <c r="A1486" t="s">
-        <v>3140</v>
+        <v>2860</v>
       </c>
       <c r="B1486" t="s">
         <v>1116</v>
@@ -71804,7 +70951,7 @@
     </row>
     <row r="1487" spans="1:3">
       <c r="A1487" t="s">
-        <v>3142</v>
+        <v>2862</v>
       </c>
       <c r="B1487" t="s">
         <v>1126</v>
@@ -71812,7 +70959,7 @@
     </row>
     <row r="1488" spans="1:3">
       <c r="A1488" t="s">
-        <v>3141</v>
+        <v>2861</v>
       </c>
       <c r="B1488" t="s">
         <v>1116</v>
@@ -71820,10 +70967,10 @@
     </row>
     <row r="1489" spans="1:3">
       <c r="A1489" t="s">
-        <v>3136</v>
+        <v>2856</v>
       </c>
       <c r="B1489" t="s">
-        <v>3137</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="1490" spans="1:3">
@@ -71831,7 +70978,7 @@
         <v>1774</v>
       </c>
       <c r="B1490" t="s">
-        <v>3138</v>
+        <v>2858</v>
       </c>
       <c r="C1490" t="s">
         <v>607</v>
@@ -71839,178 +70986,178 @@
     </row>
     <row r="1491" spans="1:3">
       <c r="A1491" t="s">
-        <v>3148</v>
+        <v>2868</v>
       </c>
       <c r="B1491" t="s">
-        <v>3149</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="1492" spans="1:3">
       <c r="A1492" t="s">
-        <v>3150</v>
+        <v>2870</v>
       </c>
       <c r="B1492" t="s">
-        <v>3151</v>
+        <v>2871</v>
       </c>
     </row>
     <row r="1493" spans="1:3">
       <c r="A1493" t="s">
-        <v>3152</v>
+        <v>2872</v>
       </c>
       <c r="B1493" t="s">
-        <v>3153</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="1494" spans="1:3">
       <c r="A1494" t="s">
-        <v>3154</v>
+        <v>2874</v>
       </c>
       <c r="B1494" t="s">
-        <v>3155</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="1495" spans="1:3">
       <c r="A1495" t="s">
-        <v>3158</v>
+        <v>2878</v>
       </c>
       <c r="B1495" t="s">
-        <v>3159</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="1496" spans="1:3">
       <c r="A1496" t="s">
-        <v>3160</v>
+        <v>2880</v>
       </c>
       <c r="B1496" t="s">
-        <v>3161</v>
+        <v>2881</v>
       </c>
     </row>
     <row r="1497" spans="1:3">
       <c r="A1497" t="s">
-        <v>3162</v>
+        <v>2882</v>
       </c>
       <c r="B1497" t="s">
-        <v>3163</v>
+        <v>2883</v>
       </c>
     </row>
     <row r="1498" spans="1:3">
       <c r="A1498" t="s">
-        <v>3164</v>
+        <v>2884</v>
       </c>
       <c r="B1498" t="s">
-        <v>3165</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="1499" spans="1:3">
       <c r="A1499" t="s">
-        <v>3166</v>
+        <v>2886</v>
       </c>
       <c r="B1499" t="s">
-        <v>3167</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="1500" spans="1:3">
       <c r="A1500" t="s">
-        <v>3168</v>
+        <v>2888</v>
       </c>
       <c r="B1500" t="s">
-        <v>3169</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="1501" spans="1:3">
       <c r="A1501" t="s">
-        <v>3178</v>
+        <v>2898</v>
       </c>
       <c r="B1501" t="s">
-        <v>3179</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="1502" spans="1:3">
       <c r="A1502" t="s">
-        <v>3180</v>
+        <v>2900</v>
       </c>
       <c r="B1502" t="s">
-        <v>3181</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="1503" spans="1:3">
       <c r="A1503" t="s">
-        <v>3182</v>
+        <v>2902</v>
       </c>
       <c r="B1503" t="s">
-        <v>3179</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="1504" spans="1:3">
       <c r="A1504" t="s">
-        <v>3183</v>
+        <v>2903</v>
       </c>
       <c r="B1504" t="s">
-        <v>3184</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="1505" spans="1:3">
       <c r="A1505" t="s">
-        <v>3185</v>
+        <v>2905</v>
       </c>
       <c r="B1505" t="s">
-        <v>3186</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="1506" spans="1:3">
       <c r="A1506" t="s">
-        <v>3187</v>
+        <v>2907</v>
       </c>
       <c r="B1506" t="s">
-        <v>3188</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="1507" spans="1:3">
       <c r="A1507" t="s">
-        <v>3190</v>
+        <v>2910</v>
       </c>
       <c r="B1507" t="s">
-        <v>3189</v>
+        <v>2909</v>
       </c>
     </row>
     <row r="1508" spans="1:3">
       <c r="A1508" t="s">
-        <v>3191</v>
+        <v>2911</v>
       </c>
       <c r="B1508" t="s">
-        <v>3192</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="1509" spans="1:3">
       <c r="A1509" t="s">
-        <v>3193</v>
+        <v>2913</v>
       </c>
       <c r="B1509" t="s">
-        <v>2776</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="1510" spans="1:3">
       <c r="A1510" t="s">
-        <v>3194</v>
+        <v>2914</v>
       </c>
       <c r="B1510" t="s">
-        <v>3195</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="1511" spans="1:3">
       <c r="A1511" t="s">
-        <v>3196</v>
+        <v>2916</v>
       </c>
       <c r="B1511" t="s">
-        <v>3197</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="1512" spans="1:3">
       <c r="A1512" t="s">
-        <v>3200</v>
+        <v>2920</v>
       </c>
       <c r="B1512" t="s">
-        <v>3201</v>
+        <v>2921</v>
       </c>
     </row>
     <row r="1513" spans="1:3">
@@ -72018,7 +71165,7 @@
         <v>1515</v>
       </c>
       <c r="B1513" t="s">
-        <v>3202</v>
+        <v>2922</v>
       </c>
       <c r="C1513" t="s">
         <v>1516</v>
@@ -72026,119 +71173,119 @@
     </row>
     <row r="1514" spans="1:3">
       <c r="A1514" t="s">
-        <v>3203</v>
+        <v>2923</v>
       </c>
       <c r="B1514" t="s">
-        <v>3204</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="1515" spans="1:3">
       <c r="A1515" t="s">
-        <v>3205</v>
+        <v>2925</v>
       </c>
       <c r="B1515" t="s">
-        <v>3206</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="1516" spans="1:3">
       <c r="A1516" t="s">
-        <v>3207</v>
+        <v>2927</v>
       </c>
       <c r="B1516" t="s">
-        <v>3208</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="1517" spans="1:3">
       <c r="A1517" t="s">
-        <v>3209</v>
+        <v>2929</v>
       </c>
       <c r="B1517" t="s">
-        <v>3202</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="1518" spans="1:3">
       <c r="A1518" t="s">
-        <v>3210</v>
+        <v>2930</v>
       </c>
       <c r="B1518" t="s">
-        <v>3195</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="1519" spans="1:3">
       <c r="A1519" t="s">
-        <v>3211</v>
+        <v>2931</v>
       </c>
       <c r="B1519" t="s">
-        <v>3212</v>
+        <v>2932</v>
       </c>
     </row>
     <row r="1520" spans="1:3">
       <c r="A1520" t="s">
-        <v>3213</v>
+        <v>2933</v>
       </c>
       <c r="B1520" t="s">
-        <v>3214</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="1521" spans="1:2">
       <c r="A1521" t="s">
-        <v>3215</v>
+        <v>2935</v>
       </c>
       <c r="B1521" t="s">
-        <v>3216</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="1522" spans="1:2">
       <c r="A1522" t="s">
-        <v>3218</v>
+        <v>2938</v>
       </c>
       <c r="B1522" t="s">
-        <v>3217</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="1523" spans="1:2">
       <c r="A1523" t="s">
-        <v>3219</v>
+        <v>2939</v>
       </c>
       <c r="B1523" t="s">
-        <v>3220</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="1524" spans="1:2">
       <c r="A1524" t="s">
-        <v>3221</v>
+        <v>2941</v>
       </c>
       <c r="B1524" t="s">
-        <v>3222</v>
+        <v>2942</v>
       </c>
     </row>
     <row r="1525" spans="1:2">
       <c r="A1525" t="s">
-        <v>3223</v>
+        <v>2943</v>
       </c>
       <c r="B1525" t="s">
-        <v>3224</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="1526" spans="1:2">
       <c r="A1526" t="s">
-        <v>3331</v>
+        <v>3051</v>
       </c>
       <c r="B1526" t="s">
-        <v>3332</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="1527" spans="1:2">
       <c r="A1527" t="s">
-        <v>3225</v>
+        <v>2945</v>
       </c>
       <c r="B1527" t="s">
-        <v>3226</v>
+        <v>2946</v>
       </c>
     </row>
     <row r="1528" spans="1:2">
       <c r="A1528" t="s">
-        <v>3227</v>
+        <v>2947</v>
       </c>
       <c r="B1528" t="s">
         <v>1873</v>
@@ -72154,95 +71301,95 @@
     </row>
     <row r="1530" spans="1:2">
       <c r="A1530" t="s">
-        <v>3228</v>
+        <v>2948</v>
       </c>
       <c r="B1530" t="s">
-        <v>3229</v>
+        <v>2949</v>
       </c>
     </row>
     <row r="1531" spans="1:2">
       <c r="A1531" t="s">
-        <v>3230</v>
+        <v>2950</v>
       </c>
       <c r="B1531" t="s">
-        <v>3231</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="1532" spans="1:2">
       <c r="A1532" t="s">
-        <v>3232</v>
+        <v>2952</v>
       </c>
       <c r="B1532" t="s">
-        <v>3233</v>
+        <v>2953</v>
       </c>
     </row>
     <row r="1533" spans="1:2">
       <c r="A1533" t="s">
-        <v>3234</v>
+        <v>2954</v>
       </c>
       <c r="B1533" t="s">
-        <v>3235</v>
+        <v>2955</v>
       </c>
     </row>
     <row r="1534" spans="1:2">
       <c r="A1534" t="s">
-        <v>3236</v>
+        <v>2956</v>
       </c>
       <c r="B1534" t="s">
-        <v>3237</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="1535" spans="1:2">
       <c r="A1535" t="s">
-        <v>3238</v>
+        <v>2958</v>
       </c>
       <c r="B1535" t="s">
-        <v>3239</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="1536" spans="1:2">
       <c r="A1536" t="s">
-        <v>3240</v>
+        <v>2960</v>
       </c>
       <c r="B1536" t="s">
-        <v>3241</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="1537" spans="1:2">
       <c r="A1537" t="s">
-        <v>3242</v>
+        <v>2962</v>
       </c>
       <c r="B1537" t="s">
-        <v>3243</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="1538" spans="1:2">
       <c r="A1538" t="s">
-        <v>3244</v>
+        <v>2964</v>
       </c>
       <c r="B1538" t="s">
-        <v>3245</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="1539" spans="1:2">
       <c r="A1539" t="s">
-        <v>3246</v>
+        <v>2966</v>
       </c>
       <c r="B1539" t="s">
-        <v>3247</v>
+        <v>2967</v>
       </c>
     </row>
     <row r="1540" spans="1:2">
       <c r="A1540" t="s">
-        <v>3248</v>
+        <v>2968</v>
       </c>
       <c r="B1540" t="s">
-        <v>3249</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="1541" spans="1:2">
       <c r="A1541" t="s">
-        <v>3250</v>
+        <v>2970</v>
       </c>
       <c r="B1541" t="s">
         <v>979</v>
@@ -72250,71 +71397,71 @@
     </row>
     <row r="1542" spans="1:2">
       <c r="A1542" t="s">
-        <v>3251</v>
+        <v>2971</v>
       </c>
       <c r="B1542" t="s">
-        <v>3252</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="1543" spans="1:2">
       <c r="A1543" t="s">
-        <v>3254</v>
+        <v>2974</v>
       </c>
       <c r="B1543" t="s">
-        <v>3255</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="1544" spans="1:2">
       <c r="A1544" t="s">
-        <v>3256</v>
+        <v>2976</v>
       </c>
       <c r="B1544" t="s">
-        <v>3257</v>
+        <v>2977</v>
       </c>
     </row>
     <row r="1545" spans="1:2">
       <c r="A1545" t="s">
-        <v>3258</v>
+        <v>2978</v>
       </c>
       <c r="B1545" t="s">
-        <v>3259</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="1546" spans="1:2">
       <c r="A1546" t="s">
-        <v>3263</v>
+        <v>2983</v>
       </c>
       <c r="B1546" t="s">
-        <v>3264</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="1547" spans="1:2">
       <c r="A1547" t="s">
-        <v>3265</v>
+        <v>2985</v>
       </c>
       <c r="B1547" t="s">
-        <v>3266</v>
+        <v>2986</v>
       </c>
     </row>
     <row r="1548" spans="1:2">
       <c r="A1548" t="s">
-        <v>3267</v>
+        <v>2987</v>
       </c>
       <c r="B1548" t="s">
-        <v>3268</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="1549" spans="1:2">
       <c r="A1549" t="s">
-        <v>3269</v>
+        <v>2989</v>
       </c>
       <c r="B1549" t="s">
-        <v>3270</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="1550" spans="1:2">
       <c r="A1550" t="s">
-        <v>3271</v>
+        <v>2991</v>
       </c>
       <c r="B1550" t="s">
         <v>218</v>
@@ -72322,255 +71469,255 @@
     </row>
     <row r="1551" spans="1:2">
       <c r="A1551" t="s">
-        <v>3272</v>
+        <v>2992</v>
       </c>
       <c r="B1551" t="s">
-        <v>3273</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="1552" spans="1:2">
       <c r="A1552" t="s">
-        <v>3274</v>
+        <v>2994</v>
       </c>
       <c r="B1552" t="s">
-        <v>3275</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="1553" spans="1:2">
       <c r="A1553" t="s">
-        <v>2629</v>
+        <v>2354</v>
       </c>
       <c r="B1553" t="s">
-        <v>3082</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="1554" spans="1:2">
       <c r="A1554" t="s">
-        <v>3280</v>
+        <v>3000</v>
       </c>
       <c r="B1554" t="s">
-        <v>3080</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="1555" spans="1:2">
       <c r="A1555" t="s">
-        <v>3279</v>
+        <v>2999</v>
       </c>
       <c r="B1555" t="s">
-        <v>3281</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="1556" spans="1:2">
       <c r="A1556" t="s">
-        <v>3282</v>
+        <v>3002</v>
       </c>
       <c r="B1556" t="s">
-        <v>3283</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="1557" spans="1:2">
       <c r="A1557" t="s">
-        <v>3284</v>
+        <v>3004</v>
       </c>
       <c r="B1557" t="s">
-        <v>3285</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="1558" spans="1:2">
       <c r="A1558" t="s">
-        <v>3288</v>
+        <v>3008</v>
       </c>
       <c r="B1558" t="s">
-        <v>3281</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="1559" spans="1:2">
       <c r="A1559" t="s">
-        <v>3292</v>
+        <v>3012</v>
       </c>
       <c r="B1559" t="s">
-        <v>3293</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="1560" spans="1:2">
       <c r="A1560" t="s">
-        <v>3294</v>
+        <v>3014</v>
       </c>
       <c r="B1560" t="s">
-        <v>3295</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="1561" spans="1:2">
       <c r="A1561" t="s">
-        <v>3297</v>
+        <v>3017</v>
       </c>
       <c r="B1561" t="s">
-        <v>3296</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="1562" spans="1:2">
       <c r="A1562" t="s">
-        <v>3298</v>
+        <v>3018</v>
       </c>
       <c r="B1562" t="s">
-        <v>3299</v>
+        <v>3019</v>
       </c>
     </row>
     <row r="1563" spans="1:2">
       <c r="A1563" t="s">
-        <v>3301</v>
+        <v>3021</v>
       </c>
       <c r="B1563" t="s">
-        <v>3302</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="1564" spans="1:2">
       <c r="A1564" t="s">
-        <v>3303</v>
+        <v>3023</v>
       </c>
       <c r="B1564" t="s">
-        <v>3304</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="1565" spans="1:2">
       <c r="A1565" t="s">
-        <v>3306</v>
+        <v>3026</v>
       </c>
       <c r="B1565" t="s">
-        <v>3305</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="1566" spans="1:2">
       <c r="A1566" t="s">
-        <v>3307</v>
+        <v>3027</v>
       </c>
       <c r="B1566" t="s">
-        <v>3308</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="1567" spans="1:2">
       <c r="A1567" t="s">
-        <v>3309</v>
+        <v>3029</v>
       </c>
       <c r="B1567" t="s">
-        <v>3310</v>
+        <v>3030</v>
       </c>
     </row>
     <row r="1568" spans="1:2">
       <c r="A1568" t="s">
-        <v>3311</v>
+        <v>3031</v>
       </c>
       <c r="B1568" t="s">
-        <v>3312</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="1569" spans="1:2">
       <c r="A1569" t="s">
-        <v>3313</v>
+        <v>3033</v>
       </c>
       <c r="B1569" t="s">
-        <v>3314</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="1570" spans="1:2">
       <c r="A1570" t="s">
-        <v>3315</v>
+        <v>3035</v>
       </c>
       <c r="B1570" t="s">
-        <v>3316</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="1571" spans="1:2">
       <c r="A1571" t="s">
-        <v>3317</v>
+        <v>3037</v>
       </c>
       <c r="B1571" t="s">
-        <v>3318</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="1572" spans="1:2">
       <c r="A1572" t="s">
-        <v>3319</v>
+        <v>3039</v>
       </c>
       <c r="B1572" t="s">
-        <v>3320</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="1573" spans="1:2">
       <c r="A1573" t="s">
-        <v>3321</v>
+        <v>3041</v>
       </c>
       <c r="B1573" t="s">
-        <v>3322</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="1574" spans="1:2">
       <c r="A1574" t="s">
-        <v>3325</v>
+        <v>3045</v>
       </c>
       <c r="B1574" t="s">
-        <v>3326</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="1575" spans="1:2">
       <c r="A1575" t="s">
-        <v>3327</v>
+        <v>3047</v>
       </c>
       <c r="B1575" t="s">
-        <v>3328</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="1576" spans="1:2">
       <c r="A1576" t="s">
-        <v>3329</v>
+        <v>3049</v>
       </c>
       <c r="B1576" t="s">
-        <v>3326</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="1577" spans="1:2">
       <c r="A1577" t="s">
-        <v>3338</v>
+        <v>3058</v>
       </c>
       <c r="B1577" t="s">
-        <v>3339</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="1578" spans="1:2">
       <c r="A1578" t="s">
-        <v>3340</v>
+        <v>3060</v>
       </c>
       <c r="B1578" t="s">
-        <v>3341</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="1579" spans="1:2">
       <c r="A1579" t="s">
-        <v>3342</v>
+        <v>3062</v>
       </c>
       <c r="B1579" t="s">
-        <v>3343</v>
+        <v>3063</v>
       </c>
     </row>
     <row r="1580" spans="1:2">
       <c r="A1580" t="s">
-        <v>3344</v>
+        <v>3064</v>
       </c>
       <c r="B1580" t="s">
-        <v>3345</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="1581" spans="1:2">
       <c r="A1581" t="s">
-        <v>3346</v>
+        <v>3066</v>
       </c>
       <c r="B1581" t="s">
-        <v>3347</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="1582" spans="1:2">
       <c r="A1582" t="s">
-        <v>3349</v>
+        <v>3069</v>
       </c>
       <c r="B1582" t="s">
         <v>1967</v>
@@ -72578,7 +71725,7 @@
     </row>
     <row r="1583" spans="1:2">
       <c r="A1583" t="s">
-        <v>3353</v>
+        <v>3073</v>
       </c>
       <c r="B1583" t="s">
         <v>1887</v>
@@ -72586,47 +71733,47 @@
     </row>
     <row r="1584" spans="1:2">
       <c r="A1584" t="s">
-        <v>3357</v>
+        <v>3077</v>
       </c>
       <c r="B1584" t="s">
-        <v>3358</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="1585" spans="1:2">
       <c r="A1585" t="s">
-        <v>3359</v>
+        <v>3079</v>
       </c>
       <c r="B1585" t="s">
-        <v>3360</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="1586" spans="1:2">
       <c r="A1586" t="s">
-        <v>3361</v>
+        <v>3081</v>
       </c>
       <c r="B1586" t="s">
-        <v>3362</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="1587" spans="1:2">
       <c r="A1587" t="s">
-        <v>3363</v>
+        <v>3083</v>
       </c>
       <c r="B1587" t="s">
-        <v>3364</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="1588" spans="1:2">
       <c r="A1588" t="s">
-        <v>3365</v>
+        <v>3085</v>
       </c>
       <c r="B1588" t="s">
-        <v>3366</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="1589" spans="1:2">
       <c r="A1589" t="s">
-        <v>3367</v>
+        <v>3087</v>
       </c>
       <c r="B1589" t="s">
         <v>1806</v>
@@ -72634,34 +71781,34 @@
     </row>
     <row r="1590" spans="1:2">
       <c r="A1590" t="s">
-        <v>3369</v>
+        <v>3089</v>
       </c>
       <c r="B1590" t="s">
-        <v>3370</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="1591" spans="1:2">
       <c r="A1591" t="s">
-        <v>3371</v>
+        <v>3091</v>
       </c>
       <c r="B1591" t="s">
-        <v>3372</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="1592" spans="1:2">
       <c r="A1592" t="s">
-        <v>3373</v>
+        <v>3093</v>
       </c>
       <c r="B1592" t="s">
-        <v>3374</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="1593" spans="1:2">
       <c r="A1593" t="s">
-        <v>3375</v>
+        <v>3095</v>
       </c>
       <c r="B1593" t="s">
-        <v>3376</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="1594" spans="1:2">
@@ -72674,42 +71821,42 @@
     </row>
     <row r="1595" spans="1:2">
       <c r="A1595" t="s">
-        <v>3377</v>
+        <v>3097</v>
       </c>
       <c r="B1595" t="s">
-        <v>3378</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="1596" spans="1:2">
       <c r="A1596" t="s">
-        <v>3389</v>
+        <v>3109</v>
       </c>
       <c r="B1596" t="s">
-        <v>3390</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="1597" spans="1:2">
       <c r="A1597" t="s">
-        <v>3391</v>
+        <v>3111</v>
       </c>
       <c r="B1597" t="s">
-        <v>3392</v>
+        <v>3112</v>
       </c>
     </row>
     <row r="1598" spans="1:2">
       <c r="A1598" t="s">
-        <v>3393</v>
+        <v>3113</v>
       </c>
       <c r="B1598" t="s">
-        <v>3394</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="1599" spans="1:2">
       <c r="A1599" t="s">
-        <v>3395</v>
+        <v>3115</v>
       </c>
       <c r="B1599" t="s">
-        <v>3396</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="1600" spans="1:2">
@@ -72722,74 +71869,138 @@
     </row>
     <row r="1601" spans="1:2">
       <c r="A1601" t="s">
-        <v>3397</v>
+        <v>3117</v>
       </c>
       <c r="B1601" t="s">
-        <v>3398</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="1602" spans="1:2">
       <c r="A1602" t="s">
-        <v>3399</v>
+        <v>3119</v>
       </c>
       <c r="B1602" t="s">
-        <v>3400</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="1603" spans="1:2">
       <c r="A1603" t="s">
-        <v>2736</v>
+        <v>2461</v>
       </c>
       <c r="B1603" t="s">
-        <v>2737</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="1604" spans="1:2">
       <c r="A1604" t="s">
-        <v>2738</v>
+        <v>2463</v>
       </c>
       <c r="B1604" t="s">
-        <v>2739</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="1605" spans="1:2">
       <c r="A1605" t="s">
-        <v>3429</v>
+        <v>3147</v>
       </c>
       <c r="B1605" t="s">
-        <v>3430</v>
+        <v>3148</v>
       </c>
     </row>
     <row r="1606" spans="1:2">
       <c r="A1606" t="s">
-        <v>3431</v>
+        <v>3149</v>
       </c>
       <c r="B1606" t="s">
-        <v>3432</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="1607" spans="1:2">
       <c r="A1607" t="s">
-        <v>3433</v>
+        <v>3151</v>
       </c>
       <c r="B1607" t="s">
-        <v>3434</v>
+        <v>3152</v>
       </c>
     </row>
     <row r="1608" spans="1:2">
       <c r="A1608" t="s">
-        <v>3427</v>
+        <v>3145</v>
       </c>
       <c r="B1608" t="s">
-        <v>3435</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="1609" spans="1:2">
       <c r="A1609" t="s">
-        <v>3426</v>
+        <v>3144</v>
       </c>
       <c r="B1609" t="s">
-        <v>3438</v>
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:2">
+      <c r="A1610" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:2">
+      <c r="A1611" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>3161</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:2">
+      <c r="A1612" t="s">
+        <v>3162</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>3163</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:2">
+      <c r="A1613" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>3165</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:2">
+      <c r="A1614" t="s">
+        <v>3166</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>3167</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:2">
+      <c r="A1615" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>3169</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:2">
+      <c r="A1616" t="s">
+        <v>3170</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>3171</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:2">
+      <c r="A1617" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>3173</v>
       </c>
     </row>
   </sheetData>
@@ -72807,7 +72018,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D669A2-CEB8-B743-9F48-CA926DA2420B}">
-  <dimension ref="A1:B229"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="51.26953125" customWidth="1"/>
@@ -72871,39 +72082,39 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>2227</v>
+      <c r="A8" t="s">
+        <v>282</v>
       </c>
       <c r="B8" t="s">
-        <v>2228</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>2229</v>
+        <v>2227</v>
       </c>
       <c r="B9" t="s">
-        <v>2230</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
         <v>2231</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" t="s">
         <v>2232</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B11" t="s">
-        <v>283</v>
-      </c>
-    </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>2233</v>
       </c>
       <c r="B12" t="s">
@@ -72919,7 +72130,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>2237</v>
       </c>
       <c r="B14" t="s">
@@ -72927,7 +72138,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>2239</v>
       </c>
       <c r="B15" t="s">
@@ -72943,7 +72154,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>2243</v>
       </c>
       <c r="B17" t="s">
@@ -72959,7 +72170,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>2247</v>
       </c>
       <c r="B19" t="s">
@@ -72967,7 +72178,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" t="s">
+      <c r="A20" s="1" t="s">
         <v>2249</v>
       </c>
       <c r="B20" t="s">
@@ -72984,38 +72195,38 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>2253</v>
+        <v>2257</v>
       </c>
       <c r="B22" t="s">
-        <v>2254</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
-        <v>2255</v>
+      <c r="A23" t="s">
+        <v>2259</v>
       </c>
       <c r="B23" t="s">
-        <v>2256</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
-        <v>2257</v>
+      <c r="A24" t="s">
+        <v>2262</v>
       </c>
       <c r="B24" t="s">
-        <v>2258</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
-        <v>2259</v>
+      <c r="A25" t="s">
+        <v>2263</v>
       </c>
       <c r="B25" t="s">
-        <v>2260</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
+      <c r="A26" t="s">
         <v>2265</v>
       </c>
       <c r="B26" t="s">
@@ -73023,7 +72234,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
+      <c r="A27" t="s">
         <v>2267</v>
       </c>
       <c r="B27" t="s">
@@ -73031,1339 +72242,219 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
-        <v>2269</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>2270</v>
+      <c r="A28" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2273</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="1" t="s">
-        <v>2271</v>
+      <c r="A29" t="s">
+        <v>2274</v>
       </c>
       <c r="B29" t="s">
-        <v>932</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="1" t="s">
-        <v>2272</v>
+      <c r="A30" t="s">
+        <v>2287</v>
       </c>
       <c r="B30" t="s">
-        <v>2273</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
-        <v>2274</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>2275</v>
+      <c r="A31" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2353</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1" t="s">
-        <v>2276</v>
+      <c r="A32" t="s">
+        <v>2355</v>
       </c>
       <c r="B32" t="s">
-        <v>2277</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="1" t="s">
-        <v>2278</v>
+      <c r="A33" t="s">
+        <v>2357</v>
       </c>
       <c r="B33" t="s">
-        <v>2279</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1" t="s">
-        <v>2280</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>2281</v>
+      <c r="A34" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2382</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="1" t="s">
-        <v>2282</v>
+      <c r="A35" t="s">
+        <v>2439</v>
       </c>
       <c r="B35" t="s">
-        <v>2283</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="1" t="s">
-        <v>2284</v>
+      <c r="A36" t="s">
+        <v>2864</v>
       </c>
       <c r="B36" t="s">
-        <v>2285</v>
+        <v>2865</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="1" t="s">
-        <v>2286</v>
+      <c r="A37" t="s">
+        <v>2866</v>
       </c>
       <c r="B37" t="s">
-        <v>2287</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="1" t="s">
-        <v>2288</v>
+      <c r="A38" t="s">
+        <v>2876</v>
       </c>
       <c r="B38" t="s">
-        <v>2289</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="1" t="s">
-        <v>2290</v>
+      <c r="A39" t="s">
+        <v>2890</v>
       </c>
       <c r="B39" t="s">
-        <v>2291</v>
+        <v>2891</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1" t="s">
-        <v>2292</v>
+      <c r="A40" t="s">
+        <v>2893</v>
       </c>
       <c r="B40" t="s">
-        <v>2293</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1" t="s">
-        <v>2294</v>
+      <c r="A41" t="s">
+        <v>2894</v>
       </c>
       <c r="B41" t="s">
-        <v>2295</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>2296</v>
+        <v>2896</v>
       </c>
       <c r="B42" t="s">
-        <v>2297</v>
+        <v>2897</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>2298</v>
+        <v>2918</v>
       </c>
       <c r="B43" t="s">
-        <v>2299</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>2300</v>
+        <v>2981</v>
       </c>
       <c r="B44" t="s">
-        <v>2301</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>2302</v>
+        <v>3043</v>
       </c>
       <c r="B45" t="s">
-        <v>2303</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>2304</v>
+        <v>3056</v>
       </c>
       <c r="B46" t="s">
-        <v>2305</v>
+        <v>3057</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B47" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>2542</v>
+        <v>1509</v>
       </c>
       <c r="B48" t="s">
-        <v>2306</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>2543</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s">
-        <v>2306</v>
+        <v>366</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>2307</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s">
-        <v>2308</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>2309</v>
+      <c r="A51" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="B51" t="s">
-        <v>2310</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>2311</v>
+        <v>3154</v>
       </c>
       <c r="B52" t="s">
-        <v>2312</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>2313</v>
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75">
+      <c r="A53" s="15" t="s">
+        <v>2529</v>
       </c>
       <c r="B53" t="s">
-        <v>2314</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>2315</v>
+        <v>3157</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75">
+      <c r="A54" s="15" t="s">
+        <v>3158</v>
       </c>
       <c r="B54" t="s">
-        <v>2316</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>2317</v>
-      </c>
-      <c r="B56" t="s">
-        <v>2318</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>2319</v>
-      </c>
-      <c r="B57" t="s">
-        <v>2320</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>2321</v>
-      </c>
-      <c r="B58" t="s">
-        <v>2322</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>2323</v>
-      </c>
-      <c r="B59" t="s">
-        <v>2324</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>2325</v>
-      </c>
-      <c r="B60" t="s">
-        <v>2326</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>2327</v>
-      </c>
-      <c r="B61" t="s">
-        <v>2328</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>2329</v>
-      </c>
-      <c r="B62" t="s">
-        <v>2330</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>2331</v>
-      </c>
-      <c r="B63" t="s">
-        <v>2332</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>2333</v>
-      </c>
-      <c r="B64" t="s">
-        <v>2334</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>2335</v>
-      </c>
-      <c r="B65" t="s">
-        <v>2336</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>2337</v>
-      </c>
-      <c r="B66" t="s">
-        <v>2338</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>2339</v>
-      </c>
-      <c r="B67" t="s">
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>2341</v>
-      </c>
-      <c r="B68" t="s">
-        <v>2342</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>2343</v>
-      </c>
-      <c r="B69" t="s">
-        <v>2344</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="29.5">
-      <c r="A70" s="14" t="s">
-        <v>3424</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>2345</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="29.5">
-      <c r="A71" s="14" t="s">
-        <v>3425</v>
-      </c>
-      <c r="B71" s="14" t="s">
-        <v>2346</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
-        <v>2347</v>
-      </c>
-      <c r="B72" t="s">
-        <v>2348</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
-        <v>2349</v>
-      </c>
-      <c r="B73" t="s">
-        <v>2350</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" t="s">
-        <v>2351</v>
-      </c>
-      <c r="B74" t="s">
-        <v>2352</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" t="s">
-        <v>2353</v>
-      </c>
-      <c r="B75" t="s">
-        <v>2354</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" t="s">
-        <v>2355</v>
-      </c>
-      <c r="B76" t="s">
-        <v>2356</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" t="s">
-        <v>2357</v>
-      </c>
-      <c r="B77" t="s">
-        <v>2358</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" t="s">
-        <v>2359</v>
-      </c>
-      <c r="B78" t="s">
-        <v>2360</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" t="s">
-        <v>2361</v>
-      </c>
-      <c r="B79" t="s">
-        <v>2362</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" t="s">
-        <v>2363</v>
-      </c>
-      <c r="B80" t="s">
-        <v>2364</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" t="s">
-        <v>2365</v>
-      </c>
-      <c r="B81" t="s">
-        <v>2366</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
-        <v>2367</v>
-      </c>
-      <c r="B82" t="s">
-        <v>2368</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" t="s">
-        <v>2369</v>
-      </c>
-      <c r="B83" t="s">
-        <v>2370</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" t="s">
-        <v>2371</v>
-      </c>
-      <c r="B84" t="s">
-        <v>2372</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" t="s">
-        <v>2373</v>
-      </c>
-      <c r="B85" t="s">
-        <v>2374</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" t="s">
-        <v>2375</v>
-      </c>
-      <c r="B86" t="s">
-        <v>2376</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" t="s">
-        <v>2377</v>
-      </c>
-      <c r="B87" t="s">
-        <v>2378</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" t="s">
-        <v>2379</v>
-      </c>
-      <c r="B88" t="s">
-        <v>2380</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" t="s">
-        <v>2381</v>
-      </c>
-      <c r="B89" t="s">
-        <v>2382</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" t="s">
-        <v>2383</v>
-      </c>
-      <c r="B90" t="s">
-        <v>2384</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" t="s">
-        <v>2385</v>
-      </c>
-      <c r="B91" t="s">
-        <v>2386</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" t="s">
-        <v>2387</v>
-      </c>
-      <c r="B92" t="s">
-        <v>2388</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" t="s">
-        <v>2389</v>
-      </c>
-      <c r="B94" t="s">
-        <v>2390</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
-        <v>2391</v>
-      </c>
-      <c r="B95" t="s">
-        <v>2392</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" t="s">
-        <v>2393</v>
-      </c>
-      <c r="B96" t="s">
-        <v>2394</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" t="s">
-        <v>2395</v>
-      </c>
-      <c r="B97" t="s">
-        <v>2396</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" t="s">
-        <v>2397</v>
-      </c>
-      <c r="B99" t="s">
-        <v>2398</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
-        <v>2399</v>
-      </c>
-      <c r="B100" t="s">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
-        <v>2401</v>
-      </c>
-      <c r="B101" t="s">
-        <v>2402</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>2403</v>
-      </c>
-      <c r="B102" t="s">
-        <v>2404</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>2405</v>
-      </c>
-      <c r="B103" t="s">
-        <v>2406</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" t="s">
-        <v>2407</v>
-      </c>
-      <c r="B104" t="s">
-        <v>2408</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" t="s">
-        <v>2409</v>
-      </c>
-      <c r="B105" t="s">
-        <v>2410</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" t="s">
-        <v>2411</v>
-      </c>
-      <c r="B106" t="s">
-        <v>2412</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" t="s">
-        <v>2413</v>
-      </c>
-      <c r="B107" t="s">
-        <v>2414</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" t="s">
-        <v>2415</v>
-      </c>
-      <c r="B108" t="s">
-        <v>2416</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" t="s">
-        <v>2417</v>
-      </c>
-      <c r="B109" t="s">
-        <v>2418</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" t="s">
-        <v>2419</v>
-      </c>
-      <c r="B110" t="s">
-        <v>2420</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" t="s">
-        <v>2421</v>
-      </c>
-      <c r="B111" t="s">
-        <v>2422</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" t="s">
-        <v>2423</v>
-      </c>
-      <c r="B112" t="s">
-        <v>2424</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" t="s">
-        <v>2425</v>
-      </c>
-      <c r="B113" t="s">
-        <v>2426</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" t="s">
-        <v>2427</v>
-      </c>
-      <c r="B114" t="s">
-        <v>2428</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" t="s">
-        <v>2429</v>
-      </c>
-      <c r="B115" t="s">
-        <v>2430</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" t="s">
-        <v>2431</v>
-      </c>
-      <c r="B116" t="s">
-        <v>2432</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" t="s">
-        <v>2433</v>
-      </c>
-      <c r="B117" t="s">
-        <v>2434</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" t="s">
-        <v>2435</v>
-      </c>
-      <c r="B118" t="s">
-        <v>2436</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" t="s">
-        <v>2437</v>
-      </c>
-      <c r="B119" t="s">
-        <v>2438</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" t="s">
-        <v>2439</v>
-      </c>
-      <c r="B120" t="s">
-        <v>2440</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" t="s">
-        <v>2441</v>
-      </c>
-      <c r="B121" t="s">
-        <v>2442</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" t="s">
-        <v>2443</v>
-      </c>
-      <c r="B122" t="s">
-        <v>2444</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" t="s">
-        <v>2445</v>
-      </c>
-      <c r="B123" t="s">
-        <v>2446</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" t="s">
-        <v>2447</v>
-      </c>
-      <c r="B124" t="s">
-        <v>2448</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" t="s">
-        <v>2449</v>
-      </c>
-      <c r="B125" t="s">
-        <v>2450</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" t="s">
-        <v>2451</v>
-      </c>
-      <c r="B126" t="s">
-        <v>2452</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" t="s">
-        <v>2453</v>
-      </c>
-      <c r="B127" t="s">
-        <v>2454</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" t="s">
-        <v>2455</v>
-      </c>
-      <c r="B128" t="s">
-        <v>2456</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" t="s">
-        <v>2457</v>
-      </c>
-      <c r="B129" t="s">
-        <v>2458</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" t="s">
-        <v>2459</v>
-      </c>
-      <c r="B130" t="s">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" t="s">
-        <v>2461</v>
-      </c>
-      <c r="B131" t="s">
-        <v>2462</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" t="s">
-        <v>2463</v>
-      </c>
-      <c r="B133" t="s">
-        <v>2464</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" t="s">
-        <v>2465</v>
-      </c>
-      <c r="B134" t="s">
-        <v>2466</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" t="s">
-        <v>2467</v>
-      </c>
-      <c r="B135" t="s">
-        <v>2468</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" t="s">
-        <v>2469</v>
-      </c>
-      <c r="B137" t="s">
-        <v>2470</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" t="s">
-        <v>2471</v>
-      </c>
-      <c r="B139" t="s">
-        <v>2472</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" t="s">
-        <v>2473</v>
-      </c>
-      <c r="B140" t="s">
-        <v>2474</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" t="s">
-        <v>2475</v>
-      </c>
-      <c r="B141" t="s">
-        <v>2476</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" t="s">
-        <v>2477</v>
-      </c>
-      <c r="B144" t="s">
-        <v>2478</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" t="s">
-        <v>2479</v>
-      </c>
-      <c r="B145" t="s">
-        <v>2480</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" t="s">
-        <v>2481</v>
-      </c>
-      <c r="B146" t="s">
-        <v>2482</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" t="s">
-        <v>2483</v>
-      </c>
-      <c r="B147" t="s">
-        <v>2484</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" t="s">
-        <v>2485</v>
-      </c>
-      <c r="B148" t="s">
-        <v>2486</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" t="s">
-        <v>2487</v>
-      </c>
-      <c r="B149" t="s">
-        <v>2488</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" t="s">
-        <v>2489</v>
-      </c>
-      <c r="B150" t="s">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" t="s">
-        <v>2491</v>
-      </c>
-      <c r="B151" t="s">
-        <v>2492</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" t="s">
-        <v>2493</v>
-      </c>
-      <c r="B152" t="s">
-        <v>2494</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" t="s">
-        <v>2495</v>
-      </c>
-      <c r="B153" t="s">
-        <v>2496</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" t="s">
-        <v>2497</v>
-      </c>
-      <c r="B156" t="s">
-        <v>2498</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" t="s">
-        <v>2499</v>
-      </c>
-      <c r="B157" t="s">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" t="s">
-        <v>2501</v>
-      </c>
-      <c r="B158" t="s">
-        <v>2502</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" t="s">
-        <v>2503</v>
-      </c>
-      <c r="B159" t="s">
-        <v>2504</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" t="s">
-        <v>2505</v>
-      </c>
-      <c r="B160" t="s">
-        <v>2506</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" t="s">
-        <v>2507</v>
-      </c>
-      <c r="B162" t="s">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" t="s">
-        <v>2509</v>
-      </c>
-      <c r="B165" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" t="s">
-        <v>2511</v>
-      </c>
-      <c r="B166" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" t="s">
-        <v>2513</v>
-      </c>
-      <c r="B167" t="s">
-        <v>2514</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" t="s">
-        <v>2515</v>
-      </c>
-      <c r="B168" t="s">
-        <v>2516</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" t="s">
-        <v>2517</v>
-      </c>
-      <c r="B169" t="s">
-        <v>2518</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" t="s">
-        <v>2519</v>
-      </c>
-      <c r="B170" t="s">
-        <v>2520</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" t="s">
-        <v>2521</v>
-      </c>
-      <c r="B171" t="s">
-        <v>2522</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" t="s">
-        <v>2523</v>
-      </c>
-      <c r="B172" t="s">
-        <v>2520</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" t="s">
-        <v>2524</v>
-      </c>
-      <c r="B173" t="s">
-        <v>2525</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" t="s">
-        <v>2526</v>
-      </c>
-      <c r="B174" t="s">
-        <v>2527</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" t="s">
-        <v>2529</v>
-      </c>
-      <c r="B177" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" t="s">
-        <v>2530</v>
-      </c>
-      <c r="B178" t="s">
-        <v>2531</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" t="s">
-        <v>2532</v>
-      </c>
-      <c r="B180" t="s">
-        <v>2533</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" t="s">
-        <v>2534</v>
-      </c>
-      <c r="B181" t="s">
-        <v>2535</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="A198" t="s">
-        <v>2536</v>
-      </c>
-      <c r="B198" t="s">
-        <v>2537</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2">
-      <c r="A199" t="s">
-        <v>2538</v>
-      </c>
-      <c r="B199" t="s">
-        <v>2539</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="A200" t="s">
-        <v>2540</v>
-      </c>
-      <c r="B200" t="s">
-        <v>2541</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2">
-      <c r="A201" t="s">
-        <v>2547</v>
-      </c>
-      <c r="B201" t="s">
-        <v>2548</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2">
-      <c r="A202" t="s">
-        <v>2549</v>
-      </c>
-      <c r="B202" t="s">
-        <v>2550</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2">
-      <c r="A203" t="s">
-        <v>2562</v>
-      </c>
-      <c r="B203" t="s">
-        <v>2563</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2">
-      <c r="A204" t="s">
-        <v>2627</v>
-      </c>
-      <c r="B204" t="s">
-        <v>2628</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2">
-      <c r="A205" t="s">
-        <v>2630</v>
-      </c>
-      <c r="B205" t="s">
-        <v>2631</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2">
-      <c r="A206" t="s">
-        <v>2632</v>
-      </c>
-      <c r="B206" t="s">
-        <v>2633</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2">
-      <c r="A207" t="s">
-        <v>2656</v>
-      </c>
-      <c r="B207" t="s">
-        <v>2657</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2">
-      <c r="A208" t="s">
-        <v>2714</v>
-      </c>
-      <c r="B208" t="s">
-        <v>2715</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2">
-      <c r="A211" t="s">
-        <v>3144</v>
-      </c>
-      <c r="B211" t="s">
-        <v>3145</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
-      <c r="A212" t="s">
-        <v>3146</v>
-      </c>
-      <c r="B212" t="s">
-        <v>3147</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2">
-      <c r="A213" t="s">
-        <v>3156</v>
-      </c>
-      <c r="B213" t="s">
-        <v>3157</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2">
-      <c r="A214" t="s">
-        <v>3170</v>
-      </c>
-      <c r="B214" t="s">
-        <v>3171</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2">
-      <c r="A215" t="s">
-        <v>3173</v>
-      </c>
-      <c r="B215" t="s">
-        <v>3172</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
-      <c r="A216" t="s">
-        <v>3174</v>
-      </c>
-      <c r="B216" t="s">
-        <v>3175</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2">
-      <c r="A217" t="s">
-        <v>3176</v>
-      </c>
-      <c r="B217" t="s">
-        <v>3177</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2">
-      <c r="A218" t="s">
-        <v>3198</v>
-      </c>
-      <c r="B218" t="s">
-        <v>3199</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2">
-      <c r="A219" t="s">
-        <v>3261</v>
-      </c>
-      <c r="B219" t="s">
-        <v>3262</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
-      <c r="A220" t="s">
-        <v>3323</v>
-      </c>
-      <c r="B220" t="s">
-        <v>3324</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2">
-      <c r="A221" t="s">
-        <v>3336</v>
-      </c>
-      <c r="B221" t="s">
-        <v>3337</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2">
-      <c r="A222" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B222" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2">
-      <c r="A223" t="s">
-        <v>1509</v>
-      </c>
-      <c r="B223" t="s">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2">
-      <c r="A224" t="s">
-        <v>365</v>
-      </c>
-      <c r="B224" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2">
-      <c r="A225" t="s">
-        <v>453</v>
-      </c>
-      <c r="B225" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2">
-      <c r="A226" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B226" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2">
-      <c r="A227" t="s">
-        <v>3436</v>
-      </c>
-      <c r="B227" t="s">
-        <v>3437</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" ht="15.75">
-      <c r="A228" s="16" t="s">
-        <v>2804</v>
-      </c>
-      <c r="B228" t="s">
-        <v>3439</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2" ht="15.75">
-      <c r="A229" s="16" t="s">
-        <v>3440</v>
-      </c>
-      <c r="B229" t="s">
-        <v>3441</v>
+        <v>3159</v>
       </c>
     </row>
   </sheetData>
@@ -74373,7 +72464,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5409384-14AD-406E-9225-D6E905D70DE3}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="17.36328125" customWidth="1"/>
@@ -74383,70 +72474,54 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>2813</v>
+        <v>1554</v>
       </c>
       <c r="B1" t="s">
-        <v>2814</v>
+        <v>1555</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F1" t="s">
+        <v>573</v>
+      </c>
+      <c r="G1" t="s">
+        <v>2271</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1554</v>
+        <v>2255</v>
       </c>
       <c r="B2" t="s">
-        <v>1555</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="F2" t="s">
-        <v>573</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2546</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>2263</v>
+        <v>1235</v>
       </c>
       <c r="B3" t="s">
-        <v>2264</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1236</v>
+      <c r="E4" t="s">
+        <v>2269</v>
+      </c>
+      <c r="F4" t="s">
+        <v>2270</v>
+      </c>
+      <c r="H4" t="s">
+        <v>2349</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="E5" t="s">
-        <v>2544</v>
-      </c>
-      <c r="F5" t="s">
-        <v>2545</v>
-      </c>
-      <c r="H5" t="s">
-        <v>2624</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>2261</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2262</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>2570</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2571</v>
+      <c r="A5" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2296</v>
       </c>
     </row>
   </sheetData>
@@ -74456,30 +72531,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AD7347-2C61-4ECD-8840-77BC33B67550}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>2842</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2244</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2845</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2846</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -74534,87 +72592,87 @@
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>2583</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>2584</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>2602</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>2625</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>2626</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>2629</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>2662</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>2671</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>2672</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>2675</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>2685</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>2693</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>2694</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>2697</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>2700</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>2701</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>2709</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -74624,295 +72682,295 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>2710</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>2713</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>2716</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>2759</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>2760</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>2782</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>2785</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15.75">
-      <c r="A34" s="16" t="s">
-        <v>2790</v>
+      <c r="A34" s="15" t="s">
+        <v>2515</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15.75">
-      <c r="A35" s="16" t="s">
-        <v>2793</v>
+      <c r="A35" s="15" t="s">
+        <v>2518</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15.75">
-      <c r="A36" s="16" t="s">
-        <v>2796</v>
+      <c r="A36" s="15" t="s">
+        <v>2521</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="15.75">
-      <c r="A37" s="16" t="s">
-        <v>2782</v>
+      <c r="A37" s="15" t="s">
+        <v>2507</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15.75">
-      <c r="A38" s="16" t="s">
-        <v>2803</v>
+      <c r="A38" s="15" t="s">
+        <v>2528</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15.75">
-      <c r="A39" s="16"/>
+      <c r="A39" s="15"/>
     </row>
     <row r="40" spans="1:1" ht="15.75">
-      <c r="A40" s="16" t="s">
-        <v>2805</v>
+      <c r="A40" s="15" t="s">
+        <v>2530</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="15.75">
-      <c r="A41" s="16" t="s">
-        <v>2806</v>
+      <c r="A41" s="15" t="s">
+        <v>2531</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="15.75">
-      <c r="A42" s="16" t="s">
-        <v>2807</v>
+      <c r="A42" s="15" t="s">
+        <v>2532</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="15.75">
-      <c r="A43" s="16" t="s">
-        <v>2808</v>
+      <c r="A43" s="15" t="s">
+        <v>2533</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15.75">
-      <c r="A44" s="16" t="s">
-        <v>2809</v>
+      <c r="A44" s="15" t="s">
+        <v>2534</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="15.75">
-      <c r="A45" s="16" t="s">
-        <v>2811</v>
+      <c r="A45" s="15" t="s">
+        <v>2536</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15.75">
-      <c r="A46" s="16" t="s">
-        <v>2812</v>
+      <c r="A46" s="15" t="s">
+        <v>2537</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15.75">
-      <c r="A47" s="16" t="s">
-        <v>2815</v>
+      <c r="A47" s="15" t="s">
+        <v>2538</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="15.75">
-      <c r="A48" s="16" t="s">
-        <v>2818</v>
+      <c r="A48" s="15" t="s">
+        <v>2541</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>2843</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>2844</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15.75">
-      <c r="A51" s="16" t="s">
-        <v>3168</v>
+      <c r="A51" s="15" t="s">
+        <v>2888</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>3253</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>3260</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>3276</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>3277</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>3278</v>
+        <v>2998</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>3286</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>3287</v>
+        <v>3007</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>3289</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>3290</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>3291</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>3300</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>3330</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>3333</v>
+        <v>3053</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>3334</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>3335</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>3348</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>3350</v>
+        <v>3070</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>3351</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>3352</v>
+        <v>3072</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>3354</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>3355</v>
+        <v>3075</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>3356</v>
+        <v>3076</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>3368</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>3379</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>3380</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>3381</v>
+        <v>3101</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>3382</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>3383</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>3384</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>3385</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" t="s">
-        <v>3386</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" t="s">
-        <v>3387</v>
+        <v>3107</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>3388</v>
+        <v>3108</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>3428</v>
+        <v>3146</v>
       </c>
     </row>
   </sheetData>

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F107DB-2193-4B13-B95A-7C4816304E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D440EF0-27A2-4C82-829D-53C449083973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19779" uniqueCount="3174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19777" uniqueCount="3175">
   <si>
     <t>криминальная</t>
   </si>
@@ -9619,6 +9619,9 @@
   </si>
   <si>
     <t>раздорную</t>
+  </si>
+  <si>
+    <t>ортодоксальные</t>
   </si>
 </sst>
 </file>
@@ -67373,14 +67376,6 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="1034" spans="1:2">
-      <c r="A1034" t="s">
-        <v>2253</v>
-      </c>
-      <c r="B1034" t="s">
-        <v>2254</v>
-      </c>
-    </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
         <v>1901</v>
@@ -72741,7 +72736,9 @@
       </c>
     </row>
     <row r="39" spans="1:1" ht="15.75">
-      <c r="A39" s="15"/>
+      <c r="A39" s="15" t="s">
+        <v>3174</v>
+      </c>
     </row>
     <row r="40" spans="1:1" ht="15.75">
       <c r="A40" s="15" t="s">
@@ -72774,9 +72771,7 @@
       </c>
     </row>
     <row r="46" spans="1:1" ht="15.75">
-      <c r="A46" s="15" t="s">
-        <v>2537</v>
-      </c>
+      <c r="A46" s="15"/>
     </row>
     <row r="47" spans="1:1" ht="15.75">
       <c r="A47" s="15" t="s">

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D440EF0-27A2-4C82-829D-53C449083973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC61C50-3A14-471F-B2D0-9FB533C76337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19777" uniqueCount="3175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19796" uniqueCount="3193">
   <si>
     <t>криминальная</t>
   </si>
@@ -9622,6 +9622,60 @@
   </si>
   <si>
     <t>ортодоксальные</t>
+  </si>
+  <si>
+    <t>был ли шанс</t>
+  </si>
+  <si>
+    <t>была ли возможность</t>
+  </si>
+  <si>
+    <t>политика</t>
+  </si>
+  <si>
+    <t>управление</t>
+  </si>
+  <si>
+    <t>инициативе</t>
+  </si>
+  <si>
+    <t>предложению</t>
+  </si>
+  <si>
+    <t>динамичного</t>
+  </si>
+  <si>
+    <t>демократизации</t>
+  </si>
+  <si>
+    <t>энтузиазму</t>
+  </si>
+  <si>
+    <t>безкорыстию</t>
+  </si>
+  <si>
+    <t>безкорыстие</t>
+  </si>
+  <si>
+    <t>энтузиазм</t>
+  </si>
+  <si>
+    <t>энтузиазма</t>
+  </si>
+  <si>
+    <t>безкорыстия</t>
+  </si>
+  <si>
+    <t>политиканство</t>
+  </si>
+  <si>
+    <t>борьба за власть</t>
+  </si>
+  <si>
+    <t>политиканства</t>
+  </si>
+  <si>
+    <t>борьбы за власть</t>
   </si>
 </sst>
 </file>
@@ -9751,7 +9805,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9780,6 +9834,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -10115,7 +10170,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCB9A67-77EF-4B4B-A409-BADD45AFE303}">
-  <dimension ref="A1:XFD1617"/>
+  <dimension ref="A1:XFD1625"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
@@ -71996,6 +72051,70 @@
       </c>
       <c r="B1617" t="s">
         <v>3173</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:2">
+      <c r="A1618" t="s">
+        <v>3177</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:2">
+      <c r="A1619" t="s">
+        <v>3179</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:2">
+      <c r="A1620" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:2">
+      <c r="A1621" t="s">
+        <v>3183</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:2">
+      <c r="A1622" t="s">
+        <v>3186</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:2">
+      <c r="A1623" t="s">
+        <v>3187</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>3188</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:2">
+      <c r="A1624" t="s">
+        <v>3189</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:2">
+      <c r="A1625" t="s">
+        <v>3191</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>3192</v>
       </c>
     </row>
   </sheetData>
@@ -72013,7 +72132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D669A2-CEB8-B743-9F48-CA926DA2420B}">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="51.26953125" customWidth="1"/>
@@ -72450,6 +72569,14 @@
       </c>
       <c r="B54" t="s">
         <v>3159</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>3175</v>
+      </c>
+      <c r="B55" t="s">
+        <v>3176</v>
       </c>
     </row>
   </sheetData>
@@ -72539,7 +72666,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A525149A-65EC-408A-9A2A-B87A37875F9B}">
-  <dimension ref="A1:A88"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="2" max="2" width="24.54296875" customWidth="1"/>
@@ -72863,82 +72990,89 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>3054</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>3055</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>3068</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>3070</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>3071</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>3072</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>3074</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>3075</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>3076</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>3088</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>3099</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>3100</v>
       </c>
-    </row>
-    <row r="77" spans="1:1">
+      <c r="E76">
+        <v>120800</v>
+      </c>
+      <c r="F76" s="16">
+        <f>E76-15704</f>
+        <v>105096</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>3101</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>3102</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>3103</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>3104</v>
       </c>
@@ -72961,6 +73095,11 @@
     <row r="84" spans="1:1">
       <c r="A84" t="s">
         <v>3108</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>3181</v>
       </c>
     </row>
     <row r="88" spans="1:1">

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC61C50-3A14-471F-B2D0-9FB533C76337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED59A9BE-C239-4D6F-932E-FA446AF2D0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19796" uniqueCount="3193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19806" uniqueCount="3201">
   <si>
     <t>криминальная</t>
   </si>
@@ -9676,6 +9676,30 @@
   </si>
   <si>
     <t>борьбы за власть</t>
+  </si>
+  <si>
+    <t>сенсорных</t>
+  </si>
+  <si>
+    <t xml:space="preserve">третьего глаза </t>
+  </si>
+  <si>
+    <t>третьего очи</t>
+  </si>
+  <si>
+    <t>гуру</t>
+  </si>
+  <si>
+    <t>духовный наставник</t>
+  </si>
+  <si>
+    <t>патогенных</t>
+  </si>
+  <si>
+    <t>процессах</t>
+  </si>
+  <si>
+    <t>зарегистрирована</t>
   </si>
 </sst>
 </file>
@@ -72666,9 +72690,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A525149A-65EC-408A-9A2A-B87A37875F9B}">
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
+    <col min="1" max="1" width="19.6328125" customWidth="1"/>
     <col min="2" max="2" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -73077,34 +73102,80 @@
         <v>3104</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>3105</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>3106</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>3107</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>3108</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>3181</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>3194</v>
+      </c>
+      <c r="B87" t="s">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
         <v>3146</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>3196</v>
+      </c>
+      <c r="B89" t="s">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>3198</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>2708</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>2777</v>
       </c>
     </row>
   </sheetData>

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED59A9BE-C239-4D6F-932E-FA446AF2D0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BA8983-97CB-4D3B-8003-0F5786160239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19806" uniqueCount="3201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19844" uniqueCount="3234">
   <si>
     <t>криминальная</t>
   </si>
@@ -9700,6 +9700,105 @@
   </si>
   <si>
     <t>зарегистрирована</t>
+  </si>
+  <si>
+    <t>интерпретации</t>
+  </si>
+  <si>
+    <t>Сложившаяся случай</t>
+  </si>
+  <si>
+    <t>всей нашей общества, не сумевшей</t>
+  </si>
+  <si>
+    <t>средства массовой сведениям буквально</t>
+  </si>
+  <si>
+    <t>массовой</t>
+  </si>
+  <si>
+    <t>поголовной</t>
+  </si>
+  <si>
+    <t>рискует</t>
+  </si>
+  <si>
+    <t>авиации</t>
+  </si>
+  <si>
+    <t>ракурсов</t>
+  </si>
+  <si>
+    <t>точек зрения</t>
+  </si>
+  <si>
+    <t>ракурса</t>
+  </si>
+  <si>
+    <t>точки зрения</t>
+  </si>
+  <si>
+    <t>герметизма,</t>
+  </si>
+  <si>
+    <t>профанированном</t>
+  </si>
+  <si>
+    <t>рассмотрим одни и те же трудности в разных взглядах.</t>
+  </si>
+  <si>
+    <t>Не бывает колдовства черной или белой,</t>
+  </si>
+  <si>
+    <t>В настоящий особенность</t>
+  </si>
+  <si>
+    <t>4-я воплощение закончилась</t>
+  </si>
+  <si>
+    <t>«фантиками»,</t>
+  </si>
+  <si>
+    <t>энергоинформационного</t>
+  </si>
+  <si>
+    <t>этнос</t>
+  </si>
+  <si>
+    <t>«фантиков».</t>
+  </si>
+  <si>
+    <t>агонии</t>
+  </si>
+  <si>
+    <t>одноактное</t>
+  </si>
+  <si>
+    <t>физической.</t>
+  </si>
+  <si>
+    <t>пассажиры</t>
+  </si>
+  <si>
+    <t>инкарнацию</t>
+  </si>
+  <si>
+    <t>реинкарнациях,</t>
+  </si>
+  <si>
+    <t>методах</t>
+  </si>
+  <si>
+    <t>религиозно-политический</t>
+  </si>
+  <si>
+    <t>институт,</t>
+  </si>
+  <si>
+    <t>трактовку</t>
+  </si>
+  <si>
+    <t>скандалом</t>
   </si>
 </sst>
 </file>
@@ -10194,7 +10293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCB9A67-77EF-4B4B-A409-BADD45AFE303}">
-  <dimension ref="A1:XFD1625"/>
+  <dimension ref="A1:XFD1628"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
@@ -72139,6 +72238,30 @@
       </c>
       <c r="B1625" t="s">
         <v>3192</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:2">
+      <c r="A1626" t="s">
+        <v>3205</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>3206</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:2">
+      <c r="A1627" t="s">
+        <v>3209</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>3210</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:2">
+      <c r="A1628" t="s">
+        <v>3211</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>3212</v>
       </c>
     </row>
   </sheetData>
@@ -72690,7 +72813,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A525149A-65EC-408A-9A2A-B87A37875F9B}">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F126"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="19.6328125" customWidth="1"/>
@@ -73178,6 +73301,166 @@
         <v>2777</v>
       </c>
     </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>3201</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="B96" t="s">
+        <v>3202</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="B97" t="s">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="B98" t="s">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>3208</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>3209</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>3213</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>3214</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="B105" t="s">
+        <v>3215</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="B106" t="s">
+        <v>3216</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="B107" t="s">
+        <v>3217</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="B108" t="s">
+        <v>3218</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>3219</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>2997</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>3221</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>3222</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>3223</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>3224</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" t="s">
+        <v>3225</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" t="s">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" t="s">
+        <v>3227</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" t="s">
+        <v>3228</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" t="s">
+        <v>3229</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" t="s">
+        <v>3230</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" t="s">
+        <v>3231</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" t="s">
+        <v>3232</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>3233</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>3020</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BA8983-97CB-4D3B-8003-0F5786160239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B7F8C7-DE68-42D1-9AE3-90BDBC1BDC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19844" uniqueCount="3234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19854" uniqueCount="3242">
   <si>
     <t>криминальная</t>
   </si>
@@ -9799,6 +9799,30 @@
   </si>
   <si>
     <t>скандалом</t>
+  </si>
+  <si>
+    <t>экстрасенсы,</t>
+  </si>
+  <si>
+    <t>деструктивной колдовства.</t>
+  </si>
+  <si>
+    <t>Инициация</t>
+  </si>
+  <si>
+    <t>координата</t>
+  </si>
+  <si>
+    <t>(астральный</t>
+  </si>
+  <si>
+    <t>информационное</t>
+  </si>
+  <si>
+    <t>трансляция</t>
+  </si>
+  <si>
+    <t>передача</t>
   </si>
 </sst>
 </file>
@@ -72813,7 +72837,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A525149A-65EC-408A-9A2A-B87A37875F9B}">
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="19.6328125" customWidth="1"/>
@@ -73461,6 +73485,52 @@
         <v>3020</v>
       </c>
     </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>3234</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" t="s">
+        <v>3235</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>3236</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>3237</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>3238</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>3239</v>
+      </c>
+      <c r="B132" t="s">
+        <v>3055</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>3240</v>
+      </c>
+      <c r="C133" t="s">
+        <v>3241</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>3074</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F576AA-89E4-4E1B-AC8B-776A17122466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E714D748-D697-4762-B229-77894E8CA577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" tabRatio="736" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4043" uniqueCount="3773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4328" uniqueCount="4047">
   <si>
     <t>криминальная</t>
   </si>
@@ -11417,6 +11417,828 @@
   </si>
   <si>
     <t>гравитации</t>
+  </si>
+  <si>
+    <t>протогалактики</t>
+  </si>
+  <si>
+    <t>инфляционной</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> раздувающейся</t>
+  </si>
+  <si>
+    <t>массы</t>
+  </si>
+  <si>
+    <t>аппаратом</t>
+  </si>
+  <si>
+    <t>импульса</t>
+  </si>
+  <si>
+    <t>момента</t>
+  </si>
+  <si>
+    <t>гравитационного</t>
+  </si>
+  <si>
+    <t>идей</t>
+  </si>
+  <si>
+    <t>детектировать</t>
+  </si>
+  <si>
+    <t>релятивисткая</t>
+  </si>
+  <si>
+    <t>релятивисткая учение</t>
+  </si>
+  <si>
+    <t>фридмановскую прообраз</t>
+  </si>
+  <si>
+    <t>на базе</t>
+  </si>
+  <si>
+    <t>тройную множества солнца</t>
+  </si>
+  <si>
+    <t>гравитационными</t>
+  </si>
+  <si>
+    <t>коллапсировать</t>
+  </si>
+  <si>
+    <t>гравитационном</t>
+  </si>
+  <si>
+    <t>массивного</t>
+  </si>
+  <si>
+    <t>внушительного</t>
+  </si>
+  <si>
+    <t>радиоастраномами</t>
+  </si>
+  <si>
+    <t>реликтового</t>
+  </si>
+  <si>
+    <t>сценарий</t>
+  </si>
+  <si>
+    <t>нейтральной</t>
+  </si>
+  <si>
+    <t>формирования</t>
+  </si>
+  <si>
+    <t>эксперименты</t>
+  </si>
+  <si>
+    <t>фонового</t>
+  </si>
+  <si>
+    <t>изотропной</t>
+  </si>
+  <si>
+    <t>нейтрино</t>
+  </si>
+  <si>
+    <t>микромира</t>
+  </si>
+  <si>
+    <t>сценариев</t>
+  </si>
+  <si>
+    <t>экстраполяция</t>
+  </si>
+  <si>
+    <t>гигантомании</t>
+  </si>
+  <si>
+    <t>философов</t>
+  </si>
+  <si>
+    <t>паронормальных</t>
+  </si>
+  <si>
+    <t>прогрессивных</t>
+  </si>
+  <si>
+    <t>континуума</t>
+  </si>
+  <si>
+    <t>агрегатов</t>
+  </si>
+  <si>
+    <t>организованным</t>
+  </si>
+  <si>
+    <t>ортодоксов</t>
+  </si>
+  <si>
+    <t>зафиксировано</t>
+  </si>
+  <si>
+    <t>может быть осуществлена изменение</t>
+  </si>
+  <si>
+    <t>организмов</t>
+  </si>
+  <si>
+    <t>вневременную сведения</t>
+  </si>
+  <si>
+    <t>сведения в мироздании распространяется</t>
+  </si>
+  <si>
+    <t>такой древа</t>
+  </si>
+  <si>
+    <t>сигналы</t>
+  </si>
+  <si>
+    <t>аналогично</t>
+  </si>
+  <si>
+    <t>реакций</t>
+  </si>
+  <si>
+    <t>термоядерных</t>
+  </si>
+  <si>
+    <t>ядерных</t>
+  </si>
+  <si>
+    <t>координаты</t>
+  </si>
+  <si>
+    <t>пропорциям</t>
+  </si>
+  <si>
+    <t>потенциалов</t>
+  </si>
+  <si>
+    <t>электронные</t>
+  </si>
+  <si>
+    <t>спираль</t>
+  </si>
+  <si>
+    <t>информационной</t>
+  </si>
+  <si>
+    <t>молекулы</t>
+  </si>
+  <si>
+    <t>ментальной</t>
+  </si>
+  <si>
+    <t>центр по исследованию</t>
+  </si>
+  <si>
+    <t>структурами</t>
+  </si>
+  <si>
+    <t>центральная нервная</t>
+  </si>
+  <si>
+    <t>коммутатора</t>
+  </si>
+  <si>
+    <t>философских</t>
+  </si>
+  <si>
+    <t>эфирное</t>
+  </si>
+  <si>
+    <t>астральное</t>
+  </si>
+  <si>
+    <t>ментальное</t>
+  </si>
+  <si>
+    <t>бутихальное</t>
+  </si>
+  <si>
+    <t>атманическое</t>
+  </si>
+  <si>
+    <t>печальная случай</t>
+  </si>
+  <si>
+    <t>цивилизаций</t>
+  </si>
+  <si>
+    <t>технократический</t>
+  </si>
+  <si>
+    <t>любой общества</t>
+  </si>
+  <si>
+    <t>данная учение (теория)</t>
+  </si>
+  <si>
+    <t>экспериментов</t>
+  </si>
+  <si>
+    <t>экспериментаторы</t>
+  </si>
+  <si>
+    <t>кювет</t>
+  </si>
+  <si>
+    <t>календарь</t>
+  </si>
+  <si>
+    <t>биополей</t>
+  </si>
+  <si>
+    <t>метакодов</t>
+  </si>
+  <si>
+    <t>ментального</t>
+  </si>
+  <si>
+    <t>прогрессивное</t>
+  </si>
+  <si>
+    <t>свою значение</t>
+  </si>
+  <si>
+    <t>технократическому</t>
+  </si>
+  <si>
+    <t>биороботов</t>
+  </si>
+  <si>
+    <t>эгоизма</t>
+  </si>
+  <si>
+    <t>псевдоэзотерической</t>
+  </si>
+  <si>
+    <t>литературе</t>
+  </si>
+  <si>
+    <t>логически</t>
+  </si>
+  <si>
+    <t>сугубо</t>
+  </si>
+  <si>
+    <t>субъективной</t>
+  </si>
+  <si>
+    <t>архитектуру</t>
+  </si>
+  <si>
+    <t>проблематично</t>
+  </si>
+  <si>
+    <t>негатива</t>
+  </si>
+  <si>
+    <t>позитива</t>
+  </si>
+  <si>
+    <t>фотопечати</t>
+  </si>
+  <si>
+    <t>мастеров</t>
+  </si>
+  <si>
+    <t>обычная повседневная случай</t>
+  </si>
+  <si>
+    <t>планета</t>
+  </si>
+  <si>
+    <t>проектировщики</t>
+  </si>
+  <si>
+    <t>кодах</t>
+  </si>
+  <si>
+    <t>кармическим</t>
+  </si>
+  <si>
+    <t>экспериментами</t>
+  </si>
+  <si>
+    <t>грандиозное</t>
+  </si>
+  <si>
+    <t>активации</t>
+  </si>
+  <si>
+    <t>деструкции</t>
+  </si>
+  <si>
+    <t>принял враждебный личность</t>
+  </si>
+  <si>
+    <t>деструктивный личность</t>
+  </si>
+  <si>
+    <t>сенсорика</t>
+  </si>
+  <si>
+    <t>телепатия</t>
+  </si>
+  <si>
+    <t>трактаты</t>
+  </si>
+  <si>
+    <t>теорий</t>
+  </si>
+  <si>
+    <t>скорость передачи сведениям</t>
+  </si>
+  <si>
+    <t>многократно</t>
+  </si>
+  <si>
+    <t>микролептонных</t>
+  </si>
+  <si>
+    <t>тахионных</t>
+  </si>
+  <si>
+    <t>торсионных</t>
+  </si>
+  <si>
+    <t>гипотезах</t>
+  </si>
+  <si>
+    <t>гипотетические</t>
+  </si>
+  <si>
+    <t>массой</t>
+  </si>
+  <si>
+    <t>формирует</t>
+  </si>
+  <si>
+    <t>спинт</t>
+  </si>
+  <si>
+    <t>спинторсионных</t>
+  </si>
+  <si>
+    <t>динамического</t>
+  </si>
+  <si>
+    <t>постоянное значение становится очень большой</t>
+  </si>
+  <si>
+    <t>визуализированными</t>
+  </si>
+  <si>
+    <t>технологии</t>
+  </si>
+  <si>
+    <t>догм</t>
+  </si>
+  <si>
+    <t>потенциальная</t>
+  </si>
+  <si>
+    <t>симметрией</t>
+  </si>
+  <si>
+    <t>интенсивность</t>
+  </si>
+  <si>
+    <t>низкоэнергетические</t>
+  </si>
+  <si>
+    <t>реликтовые</t>
+  </si>
+  <si>
+    <t>экранировать</t>
+  </si>
+  <si>
+    <t>моделировании</t>
+  </si>
+  <si>
+    <t>поляризация</t>
+  </si>
+  <si>
+    <t>спиновая</t>
+  </si>
+  <si>
+    <t>вакуума</t>
+  </si>
+  <si>
+    <t>групповая</t>
+  </si>
+  <si>
+    <t>гипотетических</t>
+  </si>
+  <si>
+    <t>голографии</t>
+  </si>
+  <si>
+    <t>фотографировании</t>
+  </si>
+  <si>
+    <t>фотоэмульсии</t>
+  </si>
+  <si>
+    <t>фотографируемого</t>
+  </si>
+  <si>
+    <t>ориентацию</t>
+  </si>
+  <si>
+    <t>эмульсии</t>
+  </si>
+  <si>
+    <t>объекте</t>
+  </si>
+  <si>
+    <t>24 независимые компоненты</t>
+  </si>
+  <si>
+    <t>спин-торсионные</t>
+  </si>
+  <si>
+    <t>техническом</t>
+  </si>
+  <si>
+    <t>металлической</t>
+  </si>
+  <si>
+    <t>получения сведениям</t>
+  </si>
+  <si>
+    <t>традиционными</t>
+  </si>
+  <si>
+    <t>методами</t>
+  </si>
+  <si>
+    <t>структурирована</t>
+  </si>
+  <si>
+    <t>технологий</t>
+  </si>
+  <si>
+    <t>спровоцировали</t>
+  </si>
+  <si>
+    <t>техногенного</t>
+  </si>
+  <si>
+    <t>зомбирование</t>
+  </si>
+  <si>
+    <t>внеземных цивилизаций</t>
+  </si>
+  <si>
+    <t>торсионной</t>
+  </si>
+  <si>
+    <t>алгоритму</t>
+  </si>
+  <si>
+    <t>пассажирского</t>
+  </si>
+  <si>
+    <t>контролирующее</t>
+  </si>
+  <si>
+    <t>генераторов</t>
+  </si>
+  <si>
+    <t>планировалось</t>
+  </si>
+  <si>
+    <t>орбиту</t>
+  </si>
+  <si>
+    <t>коммуникационные</t>
+  </si>
+  <si>
+    <t>каналы</t>
+  </si>
+  <si>
+    <t>проекты</t>
+  </si>
+  <si>
+    <t>фиаско</t>
+  </si>
+  <si>
+    <t>передачи сведениям в</t>
+  </si>
+  <si>
+    <t>генетики</t>
+  </si>
+  <si>
+    <t>контейнере</t>
+  </si>
+  <si>
+    <t>пермалоевом</t>
+  </si>
+  <si>
+    <t>биомасса</t>
+  </si>
+  <si>
+    <t>морфогенным</t>
+  </si>
+  <si>
+    <t>механизме</t>
+  </si>
+  <si>
+    <t>формообразование</t>
+  </si>
+  <si>
+    <t>сведений сделать</t>
+  </si>
+  <si>
+    <t>формальная прообраз</t>
+  </si>
+  <si>
+    <t>анализа</t>
+  </si>
+  <si>
+    <t>общесоциальных</t>
+  </si>
+  <si>
+    <t>паралогических</t>
+  </si>
+  <si>
+    <t>эту прообраз</t>
+  </si>
+  <si>
+    <t>метрики</t>
+  </si>
+  <si>
+    <t>протон</t>
+  </si>
+  <si>
+    <t>нейтрон</t>
+  </si>
+  <si>
+    <t>кодами</t>
+  </si>
+  <si>
+    <t>алфавит</t>
+  </si>
+  <si>
+    <t>переориентировать</t>
+  </si>
+  <si>
+    <t>символах</t>
+  </si>
+  <si>
+    <t>кодировку</t>
+  </si>
+  <si>
+    <t>диаметр</t>
+  </si>
+  <si>
+    <t>прецессии</t>
+  </si>
+  <si>
+    <t>полимеры</t>
+  </si>
+  <si>
+    <t>молекула</t>
+  </si>
+  <si>
+    <t>мельчайшие</t>
+  </si>
+  <si>
+    <t>ассоциаций</t>
+  </si>
+  <si>
+    <t>моно</t>
+  </si>
+  <si>
+    <t>мономолекулы</t>
+  </si>
+  <si>
+    <t>полимерные</t>
+  </si>
+  <si>
+    <t>кластеров</t>
+  </si>
+  <si>
+    <t>двумеров</t>
+  </si>
+  <si>
+    <t>тримеров</t>
+  </si>
+  <si>
+    <t>тетрамеров</t>
+  </si>
+  <si>
+    <t>пентамеров</t>
+  </si>
+  <si>
+    <t>гексамеров</t>
+  </si>
+  <si>
+    <t>объемных</t>
+  </si>
+  <si>
+    <t>дипольная</t>
+  </si>
+  <si>
+    <t>схема</t>
+  </si>
+  <si>
+    <t>ассоциативов</t>
+  </si>
+  <si>
+    <t>равновесная устройство</t>
+  </si>
+  <si>
+    <t>несимметричным</t>
+  </si>
+  <si>
+    <t>магнитную</t>
+  </si>
+  <si>
+    <t>компаса</t>
+  </si>
+  <si>
+    <t>ориентируемую</t>
+  </si>
+  <si>
+    <t>орагнизмов</t>
+  </si>
+  <si>
+    <t>азбукой</t>
+  </si>
+  <si>
+    <t>перекодирование</t>
+  </si>
+  <si>
+    <t>информационная емкость</t>
+  </si>
+  <si>
+    <t>теориями</t>
+  </si>
+  <si>
+    <t>экранированной</t>
+  </si>
+  <si>
+    <t>физико-химические</t>
+  </si>
+  <si>
+    <t>поляризацию</t>
+  </si>
+  <si>
+    <t>это привычный нам количество, описываемый координатами</t>
+  </si>
+  <si>
+    <t>резонанса</t>
+  </si>
+  <si>
+    <t>запатентован</t>
+  </si>
+  <si>
+    <t>сенсетиом</t>
+  </si>
+  <si>
+    <t>структурирут</t>
+  </si>
+  <si>
+    <t>абстрактных</t>
+  </si>
+  <si>
+    <t>скульптур</t>
+  </si>
+  <si>
+    <t>биологические</t>
+  </si>
+  <si>
+    <t>резонаторы</t>
+  </si>
+  <si>
+    <t>мебель</t>
+  </si>
+  <si>
+    <t>интструменты</t>
+  </si>
+  <si>
+    <t>преппараты</t>
+  </si>
+  <si>
+    <t>катализаторов</t>
+  </si>
+  <si>
+    <t>реаций</t>
+  </si>
+  <si>
+    <t>аналогичные</t>
+  </si>
+  <si>
+    <t>эффекты</t>
+  </si>
+  <si>
+    <t>гемеопатических</t>
+  </si>
+  <si>
+    <t>концетрация</t>
+  </si>
+  <si>
+    <t>комонента</t>
+  </si>
+  <si>
+    <t>сведениям, записанная</t>
+  </si>
+  <si>
+    <t>на объемной виде молекулы</t>
+  </si>
+  <si>
+    <t>информационная составляющая</t>
+  </si>
+  <si>
+    <t>тайный и физический особенность</t>
+  </si>
+  <si>
+    <t>синтез</t>
+  </si>
+  <si>
+    <t>объемнорезонирующих</t>
+  </si>
+  <si>
+    <t>фиксиованные</t>
+  </si>
+  <si>
+    <t>фотоаппарат</t>
+  </si>
+  <si>
+    <t>сведения записывается</t>
+  </si>
+  <si>
+    <t>объемнорезонирующую</t>
+  </si>
+  <si>
+    <t>объектом</t>
+  </si>
+  <si>
+    <t>инкарционного</t>
+  </si>
+  <si>
+    <t>накполенной информацией</t>
+  </si>
+  <si>
+    <t>саморегуляции</t>
+  </si>
+  <si>
+    <t>диаорни</t>
+  </si>
+  <si>
+    <t>энергетической</t>
+  </si>
+  <si>
+    <t>регламентировано</t>
+  </si>
+  <si>
+    <t>музыкат</t>
+  </si>
+  <si>
+    <t>верабльном</t>
+  </si>
+  <si>
+    <t>сложился понятие</t>
+  </si>
+  <si>
+    <t>шоу предпринимательстве</t>
+  </si>
+  <si>
+    <t>актер</t>
+  </si>
+  <si>
+    <t>биоэнергетик</t>
+  </si>
+  <si>
+    <t>публику</t>
+  </si>
+  <si>
+    <t>кланы</t>
+  </si>
+  <si>
+    <t>ордена</t>
+  </si>
+  <si>
+    <t>секты</t>
+  </si>
+  <si>
+    <t>публики</t>
+  </si>
+  <si>
+    <t>кампании</t>
+  </si>
+  <si>
+    <t>закончил на пятимерные пространства</t>
   </si>
 </sst>
 </file>
@@ -27320,7 +28142,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A525149A-65EC-408A-9A2A-B87A37875F9B}">
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F437"/>
   <sheetFormatPr defaultRowHeight="14.75"/>
   <cols>
     <col min="1" max="1" width="29.26953125" customWidth="1"/>
@@ -27883,82 +28705,85 @@
         <v>3098</v>
       </c>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:2">
       <c r="A113" t="s">
         <v>3692</v>
       </c>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" spans="1:2">
       <c r="A114" t="s">
         <v>3693</v>
       </c>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:2">
       <c r="A115" t="s">
         <v>3694</v>
       </c>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:2">
       <c r="A116" t="s">
         <v>3695</v>
       </c>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:2">
       <c r="A117" t="s">
         <v>3696</v>
       </c>
-    </row>
-    <row r="118" spans="1:1">
+      <c r="B117" t="s">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
       <c r="A118" t="s">
         <v>3697</v>
       </c>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" spans="1:2">
       <c r="A119" t="s">
         <v>3698</v>
       </c>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" spans="1:2">
       <c r="A120" t="s">
         <v>3699</v>
       </c>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" spans="1:2">
       <c r="A121" t="s">
         <v>3700</v>
       </c>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" spans="1:2">
       <c r="A122" t="s">
         <v>3701</v>
       </c>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:2">
       <c r="A123" t="s">
         <v>3702</v>
       </c>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:2">
       <c r="A124" t="s">
         <v>3705</v>
       </c>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:2">
       <c r="A125" t="s">
         <v>3706</v>
       </c>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:2">
       <c r="A126" t="s">
         <v>3707</v>
       </c>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:2">
       <c r="A127" t="s">
         <v>3708</v>
       </c>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" spans="1:2">
       <c r="A128" t="s">
         <v>3710</v>
       </c>
@@ -28206,54 +29031,1318 @@
         <v>3761</v>
       </c>
     </row>
-    <row r="177" spans="1:1">
+    <row r="177" spans="1:2">
       <c r="A177" t="s">
         <v>3762</v>
       </c>
     </row>
-    <row r="178" spans="1:1">
+    <row r="178" spans="1:2">
       <c r="A178" t="s">
         <v>3763</v>
       </c>
     </row>
-    <row r="179" spans="1:1">
+    <row r="179" spans="1:2">
       <c r="A179" t="s">
         <v>3764</v>
       </c>
     </row>
-    <row r="180" spans="1:1">
+    <row r="180" spans="1:2">
       <c r="A180" t="s">
         <v>3766</v>
       </c>
     </row>
-    <row r="181" spans="1:1">
+    <row r="181" spans="1:2">
       <c r="A181" t="s">
         <v>3767</v>
       </c>
     </row>
-    <row r="182" spans="1:1">
+    <row r="182" spans="1:2">
       <c r="A182" t="s">
         <v>3768</v>
       </c>
     </row>
-    <row r="183" spans="1:1">
+    <row r="183" spans="1:2">
       <c r="A183" t="s">
         <v>3769</v>
       </c>
     </row>
-    <row r="184" spans="1:1">
+    <row r="184" spans="1:2">
       <c r="A184" t="s">
         <v>3770</v>
       </c>
     </row>
-    <row r="185" spans="1:1">
+    <row r="185" spans="1:2">
       <c r="A185" t="s">
         <v>3771</v>
       </c>
     </row>
-    <row r="186" spans="1:1">
+    <row r="186" spans="1:2">
       <c r="A186" t="s">
         <v>3772</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" t="s">
+        <v>3773</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" t="s">
+        <v>3774</v>
+      </c>
+      <c r="B188" t="s">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" t="s">
+        <v>3776</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" t="s">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" t="s">
+        <v>3778</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" t="s">
+        <v>3779</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" t="s">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" t="s">
+        <v>3782</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" t="s">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" t="s">
+        <v>3786</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" t="s">
+        <v>3788</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" t="s">
+        <v>3789</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" t="s">
+        <v>3790</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" t="s">
+        <v>3791</v>
+      </c>
+      <c r="B201" t="s">
+        <v>3792</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" t="s">
+        <v>3793</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" t="s">
+        <v>3794</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" t="s">
+        <v>3795</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" t="s">
+        <v>3715</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" t="s">
+        <v>3796</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" t="s">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210" t="s">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" t="s">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212" t="s">
+        <v>3802</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>3803</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" t="s">
+        <v>3804</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" t="s">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>3806</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217" t="s">
+        <v>3807</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>3808</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219" t="s">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>3809</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" t="s">
+        <v>3812</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223" t="s">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" t="s">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" t="s">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" t="s">
+        <v>3820</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" t="s">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" t="s">
+        <v>3822</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229" t="s">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" t="s">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231" t="s">
+        <v>3825</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232" t="s">
+        <v>3826</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233" t="s">
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234" t="s">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235" t="s">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236" t="s">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" t="s">
+        <v>3831</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238" t="s">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239" t="s">
+        <v>3833</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240" t="s">
+        <v>3834</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241" t="s">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242" t="s">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243" t="s">
+        <v>3837</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244" t="s">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245" t="s">
+        <v>3839</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246" t="s">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247" t="s">
+        <v>3841</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248" t="s">
+        <v>3843</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249" t="s">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250" t="s">
+        <v>3847</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251" t="s">
+        <v>3848</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252" t="s">
+        <v>3849</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253" t="s">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254" t="s">
+        <v>3851</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256" t="s">
+        <v>3853</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258" t="s">
+        <v>3854</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260" t="s">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261" t="s">
+        <v>3858</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262" t="s">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263" t="s">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264" t="s">
+        <v>3861</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265" t="s">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266" t="s">
+        <v>3863</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267" t="s">
+        <v>3864</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268" t="s">
+        <v>3865</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269" t="s">
+        <v>3866</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270" t="s">
+        <v>3867</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271" t="s">
+        <v>3868</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272" t="s">
+        <v>3869</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273" t="s">
+        <v>3871</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274" t="s">
+        <v>3872</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275" t="s">
+        <v>3873</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276" t="s">
+        <v>3874</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277" t="s">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278" t="s">
+        <v>3876</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279" t="s">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280" t="s">
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281" t="s">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282" t="s">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283" t="s">
+        <v>3882</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284" t="s">
+        <v>3883</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285" t="s">
+        <v>3884</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286" t="s">
+        <v>3886</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287" t="s">
+        <v>3887</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288" t="s">
+        <v>3888</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289" t="s">
+        <v>3889</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290" t="s">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291" t="s">
+        <v>3891</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292" t="s">
+        <v>3892</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293" t="s">
+        <v>3893</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294" t="s">
+        <v>3894</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295" t="s">
+        <v>3895</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296" t="s">
+        <v>3896</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297" t="s">
+        <v>3898</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298" t="s">
+        <v>3899</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299" t="s">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300" t="s">
+        <v>3901</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301" t="s">
+        <v>3902</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304" t="s">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305" t="s">
+        <v>3906</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306" t="s">
+        <v>3907</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307" t="s">
+        <v>3908</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308" t="s">
+        <v>3909</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309" t="s">
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310" t="s">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311" t="s">
+        <v>3912</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312" t="s">
+        <v>3913</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313" t="s">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314" t="s">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315" t="s">
+        <v>3916</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316" t="s">
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317" t="s">
+        <v>3918</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318" t="s">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319" t="s">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320" t="s">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321" t="s">
+        <v>3923</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322" t="s">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323" t="s">
+        <v>3926</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324" t="s">
+        <v>3927</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1">
+      <c r="A325" t="s">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1">
+      <c r="A326" t="s">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1">
+      <c r="A327" t="s">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1">
+      <c r="A328" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1">
+      <c r="A329" t="s">
+        <v>3933</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1">
+      <c r="A330" t="s">
+        <v>3934</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1">
+      <c r="A331" t="s">
+        <v>3935</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1">
+      <c r="A332" t="s">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1">
+      <c r="A333" t="s">
+        <v>3937</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1">
+      <c r="A334" t="s">
+        <v>3938</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1">
+      <c r="A335" t="s">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1">
+      <c r="A336" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1">
+      <c r="A337" t="s">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1">
+      <c r="A338" t="s">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1">
+      <c r="A339" t="s">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1">
+      <c r="A340" t="s">
+        <v>3945</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1">
+      <c r="A341" t="s">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1">
+      <c r="A342" t="s">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1">
+      <c r="A343" t="s">
+        <v>3948</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1">
+      <c r="A344" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1">
+      <c r="A345" t="s">
+        <v>3949</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1">
+      <c r="A346" t="s">
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1">
+      <c r="A347" t="s">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1">
+      <c r="A348" t="s">
+        <v>3954</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1">
+      <c r="A349" t="s">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1">
+      <c r="A350" t="s">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1">
+      <c r="A351" t="s">
+        <v>3958</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1">
+      <c r="A352" t="s">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" t="s">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" t="s">
+        <v>3961</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" t="s">
+        <v>3962</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" t="s">
+        <v>3963</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" t="s">
+        <v>3964</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" t="s">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" t="s">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" t="s">
+        <v>3967</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" t="s">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" t="s">
+        <v>3969</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" t="s">
+        <v>3971</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" t="s">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" t="s">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" t="s">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" t="s">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" t="s">
+        <v>3976</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1">
+      <c r="A369" t="s">
+        <v>3977</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1">
+      <c r="A370" t="s">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1">
+      <c r="A371" t="s">
+        <v>3979</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1">
+      <c r="A372" t="s">
+        <v>3980</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1">
+      <c r="A373" t="s">
+        <v>3981</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1">
+      <c r="A374" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1">
+      <c r="A375" t="s">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1">
+      <c r="A376" t="s">
+        <v>3983</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1">
+      <c r="A377" t="s">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1">
+      <c r="A378" t="s">
+        <v>3977</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1">
+      <c r="A379" t="s">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1">
+      <c r="A380" t="s">
+        <v>3979</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1">
+      <c r="A381" t="s">
+        <v>3986</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1">
+      <c r="A382" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1">
+      <c r="A383" t="s">
+        <v>3988</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1">
+      <c r="A384" t="s">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1">
+      <c r="A385" t="s">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1">
+      <c r="A386" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1">
+      <c r="A387" t="s">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1">
+      <c r="A388" t="s">
+        <v>3993</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1">
+      <c r="A389" t="s">
+        <v>3994</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1">
+      <c r="A390" t="s">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1">
+      <c r="A391" t="s">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1">
+      <c r="A392" t="s">
+        <v>3997</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1">
+      <c r="A393" t="s">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1">
+      <c r="A394" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1">
+      <c r="A395" t="s">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1">
+      <c r="A396" t="s">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1">
+      <c r="A397" t="s">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1">
+      <c r="A398" t="s">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1">
+      <c r="A399" t="s">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1">
+      <c r="A400" t="s">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1">
+      <c r="A401" t="s">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1">
+      <c r="A402" t="s">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1">
+      <c r="A403" t="s">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1">
+      <c r="A404" t="s">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1">
+      <c r="A405" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1">
+      <c r="A406" t="s">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1">
+      <c r="A407" t="s">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1">
+      <c r="A408" t="s">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1">
+      <c r="A409" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1">
+      <c r="A410" t="s">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1">
+      <c r="A411" t="s">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1">
+      <c r="A412" t="s">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1">
+      <c r="A413" t="s">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1">
+      <c r="A414" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1">
+      <c r="A415" t="s">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1">
+      <c r="A416" t="s">
+        <v>4026</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1">
+      <c r="A417" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1">
+      <c r="A418" t="s">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1">
+      <c r="A419" t="s">
+        <v>3093</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1">
+      <c r="A420" t="s">
+        <v>4029</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1">
+      <c r="A421" t="s">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1">
+      <c r="A422" t="s">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1">
+      <c r="A423" t="s">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1">
+      <c r="A424" t="s">
+        <v>4033</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1">
+      <c r="A425" t="s">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1">
+      <c r="A426" t="s">
+        <v>4034</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1">
+      <c r="A427" t="s">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1">
+      <c r="A428" t="s">
+        <v>4037</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1">
+      <c r="A429" t="s">
+        <v>4038</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1">
+      <c r="A430" t="s">
+        <v>4039</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1">
+      <c r="A431" t="s">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1">
+      <c r="A432" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1">
+      <c r="A433" t="s">
+        <v>4042</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1">
+      <c r="A434" t="s">
+        <v>4043</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1">
+      <c r="A435" t="s">
+        <v>4044</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1">
+      <c r="A436" t="s">
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1">
+      <c r="A437" t="s">
+        <v>4046</v>
       </c>
     </row>
   </sheetData>
@@ -28315,14 +30404,162 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>3784</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>3817</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>3818</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>3842</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>3845</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>3846</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>3855</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>3879</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>3226</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>3227</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>3924</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>3944</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3952</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>3953</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>3998</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>4025</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>4036</v>
       </c>
     </row>
     <row r="132" spans="1:2">

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E714D748-D697-4762-B229-77894E8CA577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB600ED5-1584-414F-904C-C70DCB2BCFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" tabRatio="736" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="736" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Составные в 1 очередь" sheetId="5" r:id="rId4"/>
     <sheet name="не определено" sheetId="3" r:id="rId5"/>
     <sheet name="ошибки после перевода" sheetId="6" r:id="rId6"/>
+    <sheet name="что осталось" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,15 +34,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4328" uniqueCount="4047">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4393" uniqueCount="4081">
   <si>
     <t>криминальная</t>
   </si>
@@ -10897,12 +10895,6 @@
     <t>энергетических</t>
   </si>
   <si>
-    <t>серьезную статистическую</t>
-  </si>
-  <si>
-    <t xml:space="preserve">важную </t>
-  </si>
-  <si>
     <t>третьего глаза</t>
   </si>
   <si>
@@ -12239,6 +12231,114 @@
   </si>
   <si>
     <t>закончил на пятимерные пространства</t>
+  </si>
+  <si>
+    <t>объемную модель</t>
+  </si>
+  <si>
+    <t>объёмный прообраз</t>
+  </si>
+  <si>
+    <t>ая теория</t>
+  </si>
+  <si>
+    <t>ое учение</t>
+  </si>
+  <si>
+    <t>ой модели</t>
+  </si>
+  <si>
+    <t>ом виде поведения</t>
+  </si>
+  <si>
+    <t>вес</t>
+  </si>
+  <si>
+    <t>и информации</t>
+  </si>
+  <si>
+    <t>и сведений</t>
+  </si>
+  <si>
+    <t>свою роль</t>
+  </si>
+  <si>
+    <t>своё значение</t>
+  </si>
+  <si>
+    <t>ой цивилизации</t>
+  </si>
+  <si>
+    <t>го общества</t>
+  </si>
+  <si>
+    <t>ая ситуация</t>
+  </si>
+  <si>
+    <t>ый случай</t>
+  </si>
+  <si>
+    <t>го вида поведения</t>
+  </si>
+  <si>
+    <t>общая модель</t>
+  </si>
+  <si>
+    <t>общий прообраз</t>
+  </si>
+  <si>
+    <t>объёмная модель</t>
+  </si>
+  <si>
+    <t>математическую модель</t>
+  </si>
+  <si>
+    <t>матический прообраз</t>
+  </si>
+  <si>
+    <t>формальная модель</t>
+  </si>
+  <si>
+    <t>формальный прообраз</t>
+  </si>
+  <si>
+    <t>эту модель</t>
+  </si>
+  <si>
+    <t>этот прообраз</t>
+  </si>
+  <si>
+    <t>эгрегориальная модель</t>
+  </si>
+  <si>
+    <t>эгрегориальный прообраз</t>
+  </si>
+  <si>
+    <t>космологическая модель</t>
+  </si>
+  <si>
+    <t>космологический прообраз</t>
+  </si>
+  <si>
+    <t>абстрактная модель</t>
+  </si>
+  <si>
+    <t>абстрактный прообраз</t>
+  </si>
+  <si>
+    <t>масштабная модель</t>
+  </si>
+  <si>
+    <t>масштабная прообраз</t>
+  </si>
+  <si>
+    <t>эта модель</t>
+  </si>
+  <si>
+    <t>ую информацию</t>
+  </si>
+  <si>
+    <t>ые сведения</t>
   </si>
 </sst>
 </file>
@@ -12368,7 +12468,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -12397,7 +12497,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -12734,7 +12833,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCB9A67-77EF-4B4B-A409-BADD45AFE303}">
   <dimension ref="A1:D1887"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="29.36328125" customWidth="1"/>
@@ -13109,7 +13208,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75">
+    <row r="48" spans="1:3" ht="15.5">
       <c r="A48" s="15" t="s">
         <v>2511</v>
       </c>
@@ -15270,6 +15369,9 @@
       <c r="B318" t="s">
         <v>601</v>
       </c>
+      <c r="C318" t="s">
+        <v>4051</v>
+      </c>
     </row>
     <row r="319" spans="1:3">
       <c r="A319" s="1" t="s">
@@ -15303,7 +15405,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="323" spans="1:2" ht="15.75">
+    <row r="323" spans="1:2" ht="15.5">
       <c r="A323" s="15"/>
     </row>
     <row r="324" spans="1:2">
@@ -17755,7 +17857,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="632" spans="1:3" ht="15.75">
+    <row r="632" spans="1:3" ht="15.5">
       <c r="A632" s="6" t="s">
         <v>1171</v>
       </c>
@@ -19428,15 +19530,15 @@
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>3665</v>
+        <v>3663</v>
       </c>
       <c r="B847" t="s">
-        <v>3664</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>3667</v>
+        <v>3665</v>
       </c>
       <c r="B848" t="s">
         <v>1553</v>
@@ -19444,7 +19546,7 @@
     </row>
     <row r="849" spans="1:3">
       <c r="A849" t="s">
-        <v>3666</v>
+        <v>3664</v>
       </c>
       <c r="B849" t="s">
         <v>1553</v>
@@ -19452,7 +19554,7 @@
     </row>
     <row r="850" spans="1:3">
       <c r="A850" t="s">
-        <v>3670</v>
+        <v>3668</v>
       </c>
       <c r="B850" t="s">
         <v>1553</v>
@@ -19460,7 +19562,7 @@
     </row>
     <row r="851" spans="1:3">
       <c r="A851" t="s">
-        <v>3669</v>
+        <v>3667</v>
       </c>
       <c r="B851" t="s">
         <v>1553</v>
@@ -19468,7 +19570,7 @@
     </row>
     <row r="852" spans="1:3">
       <c r="A852" t="s">
-        <v>3668</v>
+        <v>3666</v>
       </c>
       <c r="B852" t="s">
         <v>1553</v>
@@ -19476,7 +19578,7 @@
     </row>
     <row r="853" spans="1:3">
       <c r="A853" t="s">
-        <v>3671</v>
+        <v>3669</v>
       </c>
       <c r="B853" t="s">
         <v>1553</v>
@@ -19487,7 +19589,7 @@
         <v>1552</v>
       </c>
       <c r="B854" t="s">
-        <v>3664</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="855" spans="1:3">
@@ -22623,7 +22725,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="1267" spans="1:2" ht="15.75">
+    <row r="1267" spans="1:2" ht="15.5">
       <c r="A1267" s="15" t="s">
         <v>2548</v>
       </c>
@@ -24403,10 +24505,10 @@
     </row>
     <row r="1488" spans="1:2">
       <c r="A1488" t="s">
-        <v>3616</v>
+        <v>3614</v>
       </c>
       <c r="B1488" t="s">
-        <v>3615</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="1489" spans="1:3">
@@ -26141,7 +26243,7 @@
         <v>3329</v>
       </c>
     </row>
-    <row r="1710" spans="1:2" ht="15.75">
+    <row r="1710" spans="1:2" ht="15.5">
       <c r="A1710" s="15" t="s">
         <v>2533</v>
       </c>
@@ -26189,7 +26291,7 @@
         <v>3338</v>
       </c>
     </row>
-    <row r="1716" spans="1:2" ht="15.75">
+    <row r="1716" spans="1:2" ht="15.5">
       <c r="A1716" s="15" t="s">
         <v>2531</v>
       </c>
@@ -26197,7 +26299,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="1717" spans="1:2" ht="15.75">
+    <row r="1717" spans="1:2" ht="15.5">
       <c r="A1717" s="15" t="s">
         <v>2529</v>
       </c>
@@ -26213,7 +26315,7 @@
         <v>3340</v>
       </c>
     </row>
-    <row r="1719" spans="1:2" ht="15.75">
+    <row r="1719" spans="1:2" ht="15.5">
       <c r="A1719" s="15" t="s">
         <v>3341</v>
       </c>
@@ -26221,7 +26323,7 @@
         <v>3342</v>
       </c>
     </row>
-    <row r="1720" spans="1:2" ht="15.75">
+    <row r="1720" spans="1:2" ht="15.5">
       <c r="A1720" s="15" t="s">
         <v>3343</v>
       </c>
@@ -26229,7 +26331,7 @@
         <v>3344</v>
       </c>
     </row>
-    <row r="1721" spans="1:2" ht="15.75">
+    <row r="1721" spans="1:2" ht="15.5">
       <c r="A1721" s="15" t="s">
         <v>2523</v>
       </c>
@@ -26237,7 +26339,7 @@
         <v>3345</v>
       </c>
     </row>
-    <row r="1722" spans="1:2" ht="15.75">
+    <row r="1722" spans="1:2" ht="15.5">
       <c r="A1722" s="15" t="s">
         <v>3346</v>
       </c>
@@ -26245,7 +26347,7 @@
         <v>3347</v>
       </c>
     </row>
-    <row r="1723" spans="1:2" ht="15.75">
+    <row r="1723" spans="1:2" ht="15.5">
       <c r="A1723" s="15" t="s">
         <v>3348</v>
       </c>
@@ -26253,7 +26355,7 @@
         <v>3349</v>
       </c>
     </row>
-    <row r="1724" spans="1:2" ht="15.75">
+    <row r="1724" spans="1:2" ht="15.5">
       <c r="A1724" s="15" t="s">
         <v>3350</v>
       </c>
@@ -26261,7 +26363,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="1725" spans="1:2" ht="15.75">
+    <row r="1725" spans="1:2" ht="15.5">
       <c r="A1725" s="15" t="s">
         <v>3351</v>
       </c>
@@ -26269,7 +26371,7 @@
         <v>3352</v>
       </c>
     </row>
-    <row r="1726" spans="1:2" ht="15.75">
+    <row r="1726" spans="1:2" ht="15.5">
       <c r="A1726" s="15" t="s">
         <v>3353</v>
       </c>
@@ -26277,7 +26379,7 @@
         <v>3354</v>
       </c>
     </row>
-    <row r="1727" spans="1:2" ht="15.75">
+    <row r="1727" spans="1:2" ht="15.5">
       <c r="A1727" s="15" t="s">
         <v>3355</v>
       </c>
@@ -26285,7 +26387,7 @@
         <v>3356</v>
       </c>
     </row>
-    <row r="1728" spans="1:2" ht="15.75">
+    <row r="1728" spans="1:2" ht="15.5">
       <c r="A1728" s="15" t="s">
         <v>3357</v>
       </c>
@@ -26293,7 +26395,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="1729" spans="1:2" ht="15.75">
+    <row r="1729" spans="1:2" ht="15.5">
       <c r="A1729" s="15" t="s">
         <v>3358</v>
       </c>
@@ -26301,7 +26403,7 @@
         <v>3359</v>
       </c>
     </row>
-    <row r="1730" spans="1:2" ht="15.75">
+    <row r="1730" spans="1:2" ht="15.5">
       <c r="A1730" s="15" t="s">
         <v>3360</v>
       </c>
@@ -26309,7 +26411,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="1731" spans="1:2" ht="15.75">
+    <row r="1731" spans="1:2" ht="15.5">
       <c r="A1731" s="15" t="s">
         <v>2502</v>
       </c>
@@ -26317,10 +26419,10 @@
         <v>3434</v>
       </c>
     </row>
-    <row r="1732" spans="1:2" ht="15.75">
+    <row r="1732" spans="1:2" ht="15.5">
       <c r="A1732" s="15"/>
     </row>
-    <row r="1733" spans="1:2" ht="15.75">
+    <row r="1733" spans="1:2" ht="15.5">
       <c r="A1733" s="15" t="s">
         <v>871</v>
       </c>
@@ -26328,7 +26430,7 @@
         <v>3428</v>
       </c>
     </row>
-    <row r="1734" spans="1:2" ht="15.75">
+    <row r="1734" spans="1:2" ht="15.5">
       <c r="A1734" s="15" t="s">
         <v>3362</v>
       </c>
@@ -26336,7 +26438,7 @@
         <v>3426</v>
       </c>
     </row>
-    <row r="1735" spans="1:2" ht="15.75">
+    <row r="1735" spans="1:2" ht="15.5">
       <c r="A1735" s="15" t="s">
         <v>3363</v>
       </c>
@@ -26344,10 +26446,10 @@
         <v>3429</v>
       </c>
     </row>
-    <row r="1736" spans="1:2" ht="15.75">
+    <row r="1736" spans="1:2" ht="15.5">
       <c r="A1736" s="15"/>
     </row>
-    <row r="1737" spans="1:2" ht="15.75">
+    <row r="1737" spans="1:2" ht="15.5">
       <c r="A1737" s="15" t="s">
         <v>3364</v>
       </c>
@@ -26355,7 +26457,7 @@
         <v>3430</v>
       </c>
     </row>
-    <row r="1738" spans="1:2" ht="15.75">
+    <row r="1738" spans="1:2" ht="15.5">
       <c r="A1738" s="15" t="s">
         <v>3365</v>
       </c>
@@ -26363,7 +26465,7 @@
         <v>3431</v>
       </c>
     </row>
-    <row r="1739" spans="1:2" ht="15.75">
+    <row r="1739" spans="1:2" ht="15.5">
       <c r="A1739" s="15" t="s">
         <v>3366</v>
       </c>
@@ -26371,7 +26473,7 @@
         <v>3432</v>
       </c>
     </row>
-    <row r="1740" spans="1:2" ht="15.75">
+    <row r="1740" spans="1:2" ht="15.5">
       <c r="A1740" s="15" t="s">
         <v>846</v>
       </c>
@@ -26379,7 +26481,7 @@
         <v>3433</v>
       </c>
     </row>
-    <row r="1741" spans="1:2" ht="15.75">
+    <row r="1741" spans="1:2" ht="15.5">
       <c r="A1741" s="15" t="s">
         <v>2516</v>
       </c>
@@ -26387,7 +26489,7 @@
         <v>3371</v>
       </c>
     </row>
-    <row r="1742" spans="1:2" ht="15.75">
+    <row r="1742" spans="1:2" ht="15.5">
       <c r="A1742" s="15" t="s">
         <v>3367</v>
       </c>
@@ -26395,7 +26497,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="1743" spans="1:2" ht="15.75">
+    <row r="1743" spans="1:2" ht="15.5">
       <c r="A1743" s="15" t="s">
         <v>3368</v>
       </c>
@@ -26403,7 +26505,7 @@
         <v>3373</v>
       </c>
     </row>
-    <row r="1744" spans="1:2" ht="15.75">
+    <row r="1744" spans="1:2" ht="15.5">
       <c r="A1744" s="15" t="s">
         <v>3369</v>
       </c>
@@ -26411,7 +26513,7 @@
         <v>3374</v>
       </c>
     </row>
-    <row r="1745" spans="1:2" ht="15.75">
+    <row r="1745" spans="1:2" ht="15.5">
       <c r="A1745" s="15" t="s">
         <v>3370</v>
       </c>
@@ -26419,7 +26521,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="1746" spans="1:2" ht="15.75">
+    <row r="1746" spans="1:2" ht="15.5">
       <c r="A1746" s="15" t="s">
         <v>3376</v>
       </c>
@@ -26427,7 +26529,7 @@
         <v>3377</v>
       </c>
     </row>
-    <row r="1747" spans="1:2" ht="15.75">
+    <row r="1747" spans="1:2" ht="15.5">
       <c r="A1747" s="15" t="s">
         <v>2510</v>
       </c>
@@ -26435,7 +26537,7 @@
         <v>3378</v>
       </c>
     </row>
-    <row r="1748" spans="1:2" ht="15.75">
+    <row r="1748" spans="1:2" ht="15.5">
       <c r="A1748" s="15" t="s">
         <v>3379</v>
       </c>
@@ -26443,7 +26545,7 @@
         <v>3380</v>
       </c>
     </row>
-    <row r="1749" spans="1:2" ht="15.75">
+    <row r="1749" spans="1:2" ht="15.5">
       <c r="A1749" s="15" t="s">
         <v>3381</v>
       </c>
@@ -26451,7 +26553,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="1750" spans="1:2" ht="15.75">
+    <row r="1750" spans="1:2" ht="15.5">
       <c r="A1750" s="15" t="s">
         <v>3383</v>
       </c>
@@ -27222,10 +27324,10 @@
     </row>
     <row r="1847" spans="1:3">
       <c r="A1847" t="s">
-        <v>3603</v>
+        <v>3601</v>
       </c>
       <c r="B1847" t="s">
-        <v>3604</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="1848" spans="1:3">
@@ -27233,7 +27335,7 @@
         <v>2963</v>
       </c>
       <c r="B1848" t="s">
-        <v>3605</v>
+        <v>3603</v>
       </c>
       <c r="C1848" t="s">
         <v>2964</v>
@@ -27241,10 +27343,10 @@
     </row>
     <row r="1849" spans="1:3">
       <c r="A1849" t="s">
-        <v>3606</v>
+        <v>3604</v>
       </c>
       <c r="B1849" t="s">
-        <v>3607</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="1850" spans="1:3">
@@ -27265,10 +27367,10 @@
     </row>
     <row r="1852" spans="1:3">
       <c r="A1852" t="s">
-        <v>3608</v>
+        <v>3606</v>
       </c>
       <c r="B1852" t="s">
-        <v>3609</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="1853" spans="1:3">
@@ -27281,7 +27383,7 @@
     </row>
     <row r="1854" spans="1:3">
       <c r="A1854" t="s">
-        <v>3610</v>
+        <v>3608</v>
       </c>
       <c r="B1854" t="s">
         <v>2964</v>
@@ -27289,23 +27391,23 @@
     </row>
     <row r="1855" spans="1:3">
       <c r="A1855" t="s">
-        <v>3611</v>
+        <v>3609</v>
       </c>
       <c r="B1855" t="s">
-        <v>3612</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="1856" spans="1:3">
       <c r="A1856" t="s">
-        <v>3613</v>
+        <v>3611</v>
       </c>
       <c r="B1856" t="s">
-        <v>3614</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="1857" spans="1:2">
       <c r="A1857" t="s">
-        <v>3644</v>
+        <v>3642</v>
       </c>
       <c r="B1857" t="s">
         <v>2927</v>
@@ -27313,15 +27415,15 @@
     </row>
     <row r="1858" spans="1:2">
       <c r="A1858" t="s">
-        <v>3643</v>
+        <v>3641</v>
       </c>
       <c r="B1858" t="s">
-        <v>3642</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="1859" spans="1:2">
       <c r="A1859" t="s">
-        <v>3641</v>
+        <v>3639</v>
       </c>
       <c r="B1859" t="s">
         <v>688</v>
@@ -27329,7 +27431,7 @@
     </row>
     <row r="1860" spans="1:2">
       <c r="A1860" t="s">
-        <v>3640</v>
+        <v>3638</v>
       </c>
       <c r="B1860" t="s">
         <v>277</v>
@@ -27337,98 +27439,98 @@
     </row>
     <row r="1861" spans="1:2">
       <c r="A1861" t="s">
-        <v>3639</v>
+        <v>3637</v>
       </c>
       <c r="B1861" t="s">
-        <v>3635</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="1862" spans="1:2">
       <c r="A1862" t="s">
-        <v>3638</v>
+        <v>3636</v>
       </c>
       <c r="B1862" t="s">
-        <v>3637</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="1863" spans="1:2">
       <c r="A1863" t="s">
-        <v>3636</v>
+        <v>3634</v>
       </c>
       <c r="B1863" t="s">
-        <v>3635</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="1864" spans="1:2">
       <c r="A1864" t="s">
-        <v>3634</v>
+        <v>3632</v>
       </c>
       <c r="B1864" t="s">
-        <v>3633</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="1865" spans="1:2">
       <c r="A1865" t="s">
-        <v>3632</v>
+        <v>3630</v>
       </c>
       <c r="B1865" t="s">
-        <v>3631</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="1867" spans="1:2">
       <c r="A1867" t="s">
-        <v>3630</v>
+        <v>3628</v>
       </c>
       <c r="B1867" t="s">
-        <v>3629</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="1868" spans="1:2">
       <c r="A1868" t="s">
-        <v>3628</v>
+        <v>3626</v>
       </c>
       <c r="B1868" t="s">
-        <v>3627</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="1869" spans="1:2">
       <c r="A1869" t="s">
-        <v>3626</v>
+        <v>3624</v>
       </c>
       <c r="B1869" t="s">
-        <v>3625</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="1872" spans="1:2">
       <c r="A1872" t="s">
-        <v>3624</v>
+        <v>3622</v>
       </c>
       <c r="B1872" t="s">
-        <v>3623</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="1873" spans="1:2">
       <c r="A1873" t="s">
-        <v>3622</v>
+        <v>3620</v>
       </c>
       <c r="B1873" t="s">
-        <v>3621</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="1874" spans="1:2">
       <c r="A1874" t="s">
-        <v>3620</v>
+        <v>3618</v>
       </c>
       <c r="B1874" t="s">
-        <v>3619</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="1875" spans="1:2">
       <c r="A1875" t="s">
-        <v>3618</v>
+        <v>3616</v>
       </c>
       <c r="B1875" t="s">
-        <v>3617</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="1876" spans="1:2">
@@ -27441,15 +27543,15 @@
     </row>
     <row r="1877" spans="1:2">
       <c r="A1877" t="s">
-        <v>3645</v>
+        <v>3643</v>
       </c>
       <c r="B1877" t="s">
-        <v>3646</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="1878" spans="1:2">
       <c r="A1878" t="s">
-        <v>3677</v>
+        <v>3675</v>
       </c>
       <c r="B1878" t="s">
         <v>2490</v>
@@ -27457,66 +27559,66 @@
     </row>
     <row r="1879" spans="1:2">
       <c r="A1879" t="s">
-        <v>3647</v>
+        <v>3645</v>
       </c>
       <c r="B1879" t="s">
-        <v>3663</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="1880" spans="1:2">
       <c r="A1880" t="s">
-        <v>3648</v>
+        <v>3646</v>
       </c>
       <c r="B1880" t="s">
-        <v>3649</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="1881" spans="1:2">
       <c r="A1881" t="s">
-        <v>3650</v>
+        <v>3648</v>
       </c>
       <c r="B1881" t="s">
-        <v>3651</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="1882" spans="1:2">
       <c r="A1882" t="s">
-        <v>3652</v>
+        <v>3650</v>
       </c>
       <c r="B1882" t="s">
-        <v>3653</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="1883" spans="1:2">
       <c r="A1883" t="s">
-        <v>3654</v>
+        <v>3652</v>
       </c>
       <c r="B1883" t="s">
-        <v>3655</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="1884" spans="1:2">
       <c r="A1884" t="s">
-        <v>3656</v>
+        <v>3654</v>
       </c>
       <c r="B1884" t="s">
-        <v>3657</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="1885" spans="1:2">
       <c r="A1885" t="s">
-        <v>3658</v>
+        <v>3656</v>
       </c>
       <c r="B1885" t="s">
-        <v>3659</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="1886" spans="1:2">
       <c r="A1886" t="s">
-        <v>3660</v>
+        <v>3658</v>
       </c>
       <c r="B1886" t="s">
-        <v>3661</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="1887" spans="1:2">
@@ -27524,7 +27626,7 @@
         <v>3218</v>
       </c>
       <c r="B1887" t="s">
-        <v>3662</v>
+        <v>3660</v>
       </c>
     </row>
   </sheetData>
@@ -27542,8 +27644,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D669A2-CEB8-B743-9F48-CA926DA2420B}">
-  <dimension ref="A1:B64"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <dimension ref="A1:B77"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="51.26953125" customWidth="1"/>
     <col min="2" max="2" width="24.54296875" customWidth="1"/>
@@ -27965,7 +28067,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75">
+    <row r="53" spans="1:2" ht="15.5">
       <c r="A53" s="15" t="s">
         <v>2524</v>
       </c>
@@ -27973,7 +28075,7 @@
         <v>3147</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75">
+    <row r="54" spans="1:2" ht="15.5">
       <c r="A54" s="15" t="s">
         <v>3148</v>
       </c>
@@ -28045,20 +28147,108 @@
         <v>3581</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>3599</v>
-      </c>
-      <c r="B63" t="s">
-        <v>3600</v>
-      </c>
-    </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>3601</v>
+        <v>3599</v>
       </c>
       <c r="B64" t="s">
-        <v>3602</v>
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>4061</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4062</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>4063</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>4064</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4065</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>4054</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>4045</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>4066</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4067</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>4068</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4069</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>4070</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4071</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>4072</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4073</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>4074</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>4076</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4077</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>4078</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4069</v>
       </c>
     </row>
   </sheetData>
@@ -28069,7 +28259,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5409384-14AD-406E-9225-D6E905D70DE3}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="17.36328125" customWidth="1"/>
     <col min="2" max="2" width="22.36328125" customWidth="1"/>
@@ -28129,13 +28319,74 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AD7347-2C61-4ECD-8840-77BC33B67550}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.453125" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>4047</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4048</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>4079</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4056</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4058</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>4052</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4053</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>4049</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="B8" s="12"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -28143,7 +28394,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A525149A-65EC-408A-9A2A-B87A37875F9B}">
   <dimension ref="A1:F437"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="29.26953125" customWidth="1"/>
     <col min="2" max="2" width="24.54296875" customWidth="1"/>
@@ -28279,32 +28530,32 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="15.75">
+    <row r="31" spans="1:1" ht="15.5">
       <c r="A31" s="15" t="s">
         <v>2513</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="15.75">
+    <row r="32" spans="1:1" ht="15.5">
       <c r="A32" s="15" t="s">
         <v>3164</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="15.75">
+    <row r="33" spans="1:1" ht="15.5">
       <c r="A33" s="15" t="s">
         <v>2525</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="15.75">
+    <row r="34" spans="1:1" ht="15.5">
       <c r="A34" s="15" t="s">
         <v>2526</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="15.75">
+    <row r="35" spans="1:1" ht="15.5">
       <c r="A35" s="15" t="s">
         <v>2527</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="15.75">
+    <row r="36" spans="1:1" ht="15.5">
       <c r="A36" s="15" t="s">
         <v>2528</v>
       </c>
@@ -28319,7 +28570,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="15.75">
+    <row r="39" spans="1:1" ht="15.5">
       <c r="A39" s="15" t="s">
         <v>2883</v>
       </c>
@@ -28431,7 +28682,7 @@
       <c r="E60">
         <v>120800</v>
       </c>
-      <c r="F60" s="16">
+      <c r="F60">
         <f>E60-15704</f>
         <v>105096</v>
       </c>
@@ -28596,62 +28847,62 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>3673</v>
+        <v>3671</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>3674</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>3675</v>
+        <v>3673</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>3676</v>
+        <v>3674</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>3678</v>
+        <v>3676</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>3680</v>
+        <v>3678</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>3681</v>
+        <v>3679</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>3682</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>3683</v>
+        <v>3681</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>3684</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>3679</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -28661,17 +28912,17 @@
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>3685</v>
+        <v>3683</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>3686</v>
+        <v>3684</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>3687</v>
+        <v>3685</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -28684,20 +28935,20 @@
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>3688</v>
+        <v>3686</v>
       </c>
       <c r="B109" t="s">
-        <v>3689</v>
+        <v>3687</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>3690</v>
+        <v>3688</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>3691</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -28707,320 +28958,320 @@
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>3692</v>
+        <v>3690</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>3693</v>
+        <v>3691</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>3694</v>
+        <v>3692</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>3695</v>
+        <v>3693</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>3696</v>
+        <v>3694</v>
       </c>
       <c r="B117" t="s">
-        <v>3970</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>3697</v>
+        <v>3695</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>3698</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>3699</v>
+        <v>3697</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>3700</v>
+        <v>3698</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>3701</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>3702</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>3705</v>
+        <v>3703</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>3706</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>3707</v>
+        <v>3705</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>3708</v>
+        <v>3706</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>3710</v>
+        <v>3708</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>3711</v>
+        <v>3709</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>3712</v>
+        <v>3710</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>3714</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" t="s">
-        <v>3715</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" t="s">
-        <v>3716</v>
+        <v>3714</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>3717</v>
+        <v>3715</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>3718</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>3720</v>
+        <v>3718</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>3721</v>
+        <v>3719</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>3722</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>3723</v>
+        <v>3721</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>3724</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>3725</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>3726</v>
+        <v>3724</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>3727</v>
+        <v>3725</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>3728</v>
+        <v>3726</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>3729</v>
+        <v>3727</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" t="s">
-        <v>3730</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>3731</v>
+        <v>3729</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>3732</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>3733</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>3734</v>
+        <v>3732</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>3735</v>
+        <v>3733</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>3736</v>
+        <v>3734</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" t="s">
-        <v>3737</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>3738</v>
+        <v>3736</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>3739</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>3740</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>3741</v>
+        <v>3739</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>3742</v>
+        <v>3740</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>3743</v>
+        <v>3741</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>3744</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>3745</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>3746</v>
+        <v>3744</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>3747</v>
+        <v>3745</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>3748</v>
+        <v>3746</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>3749</v>
+        <v>3747</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>3750</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>3751</v>
+        <v>3749</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>3752</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>3753</v>
+        <v>3751</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>3754</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>3755</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>3756</v>
+        <v>3754</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>3757</v>
+        <v>3755</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>3758</v>
+        <v>3756</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>3759</v>
+        <v>3757</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -29028,848 +29279,848 @@
         <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>3761</v>
+        <v>3759</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>3762</v>
+        <v>3760</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>3763</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>3764</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>3766</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>3767</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>3768</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>3769</v>
+        <v>3767</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>3770</v>
+        <v>3768</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>3771</v>
+        <v>3769</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>3772</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>3773</v>
+        <v>3771</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>3774</v>
+        <v>3772</v>
       </c>
       <c r="B188" t="s">
-        <v>3775</v>
+        <v>3773</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>3776</v>
+        <v>3774</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>3777</v>
+        <v>3775</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
-        <v>3778</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>3779</v>
+        <v>3777</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>3780</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>3781</v>
+        <v>3779</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>3782</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>3783</v>
+        <v>3781</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
-        <v>3786</v>
+        <v>3784</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>3788</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>3789</v>
+        <v>3787</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>3790</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>3791</v>
+        <v>3789</v>
       </c>
       <c r="B201" t="s">
-        <v>3792</v>
+        <v>3790</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>3793</v>
+        <v>3791</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>3794</v>
+        <v>3792</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>3795</v>
+        <v>3793</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>3715</v>
+        <v>3713</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>3796</v>
+        <v>3794</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>3797</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>3798</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>3799</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="210" spans="1:1">
       <c r="A210" t="s">
-        <v>3800</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>3801</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" t="s">
-        <v>3802</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>3803</v>
+        <v>3801</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>3804</v>
+        <v>3802</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>3805</v>
+        <v>3803</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>3806</v>
+        <v>3804</v>
       </c>
     </row>
     <row r="217" spans="1:1">
       <c r="A217" t="s">
-        <v>3807</v>
+        <v>3805</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>3808</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" t="s">
-        <v>3810</v>
+        <v>3808</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>3809</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" t="s">
-        <v>3811</v>
+        <v>3809</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>3812</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" t="s">
-        <v>3813</v>
+        <v>3811</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>3815</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>3819</v>
+        <v>3817</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>3820</v>
+        <v>3818</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>3821</v>
+        <v>3819</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>3822</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="229" spans="1:1">
       <c r="A229" t="s">
-        <v>3823</v>
+        <v>3821</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>3824</v>
+        <v>3822</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" t="s">
-        <v>3825</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" t="s">
-        <v>3826</v>
+        <v>3824</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" t="s">
-        <v>3827</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" t="s">
-        <v>3828</v>
+        <v>3826</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" t="s">
-        <v>3829</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" t="s">
-        <v>3830</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="237" spans="1:1">
       <c r="A237" t="s">
-        <v>3831</v>
+        <v>3829</v>
       </c>
     </row>
     <row r="238" spans="1:1">
       <c r="A238" t="s">
-        <v>3832</v>
+        <v>3830</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" t="s">
-        <v>3833</v>
+        <v>3831</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" t="s">
-        <v>3834</v>
+        <v>3832</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" t="s">
-        <v>3835</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" t="s">
-        <v>3836</v>
+        <v>3834</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" t="s">
-        <v>3837</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" t="s">
-        <v>3838</v>
+        <v>3836</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" t="s">
-        <v>3839</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" t="s">
-        <v>3840</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" t="s">
-        <v>3841</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="248" spans="1:1">
       <c r="A248" t="s">
-        <v>3843</v>
+        <v>3841</v>
       </c>
     </row>
     <row r="249" spans="1:1">
       <c r="A249" t="s">
-        <v>3844</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" t="s">
-        <v>3847</v>
+        <v>3845</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" t="s">
-        <v>3848</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="252" spans="1:1">
       <c r="A252" t="s">
-        <v>3849</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="253" spans="1:1">
       <c r="A253" t="s">
-        <v>3850</v>
+        <v>3848</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" t="s">
-        <v>3851</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" t="s">
-        <v>3852</v>
+        <v>3850</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" t="s">
-        <v>3853</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" t="s">
-        <v>3798</v>
+        <v>3796</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" t="s">
-        <v>3854</v>
+        <v>3852</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" t="s">
-        <v>3856</v>
+        <v>3854</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" t="s">
-        <v>3857</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" t="s">
-        <v>3858</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="262" spans="1:1">
       <c r="A262" t="s">
-        <v>3859</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="263" spans="1:1">
       <c r="A263" t="s">
-        <v>3860</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" t="s">
-        <v>3861</v>
+        <v>3859</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" t="s">
-        <v>3862</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" t="s">
-        <v>3863</v>
+        <v>3861</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" t="s">
-        <v>3864</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" t="s">
-        <v>3865</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" t="s">
-        <v>3866</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" t="s">
-        <v>3867</v>
+        <v>3865</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" t="s">
-        <v>3868</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" t="s">
-        <v>3869</v>
+        <v>3867</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" t="s">
-        <v>3871</v>
+        <v>3869</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" t="s">
-        <v>3872</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" t="s">
-        <v>3873</v>
+        <v>3871</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" t="s">
-        <v>3874</v>
+        <v>3872</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" t="s">
-        <v>3875</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" t="s">
-        <v>3876</v>
+        <v>3874</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" t="s">
-        <v>3877</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" t="s">
-        <v>3878</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" t="s">
-        <v>3880</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" t="s">
-        <v>3881</v>
+        <v>3879</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" t="s">
-        <v>3882</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" t="s">
-        <v>3883</v>
+        <v>3881</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" t="s">
-        <v>3884</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" t="s">
-        <v>3886</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" t="s">
-        <v>3887</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" t="s">
-        <v>3888</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" t="s">
-        <v>3889</v>
+        <v>3887</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" t="s">
-        <v>3890</v>
+        <v>3888</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" t="s">
-        <v>3891</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" t="s">
-        <v>3892</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" t="s">
-        <v>3893</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" t="s">
-        <v>3894</v>
+        <v>3892</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" t="s">
-        <v>3895</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" t="s">
-        <v>3896</v>
+        <v>3894</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" t="s">
-        <v>3898</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="298" spans="1:1">
       <c r="A298" t="s">
-        <v>3899</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="299" spans="1:1">
       <c r="A299" t="s">
-        <v>3900</v>
+        <v>3898</v>
       </c>
     </row>
     <row r="300" spans="1:1">
       <c r="A300" t="s">
-        <v>3901</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="301" spans="1:1">
       <c r="A301" t="s">
-        <v>3902</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="302" spans="1:1">
       <c r="A302" t="s">
-        <v>3903</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="303" spans="1:1">
       <c r="A303" t="s">
-        <v>3904</v>
+        <v>3902</v>
       </c>
     </row>
     <row r="304" spans="1:1">
       <c r="A304" t="s">
-        <v>3905</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" t="s">
-        <v>3906</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" t="s">
-        <v>3907</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" t="s">
-        <v>3908</v>
+        <v>3906</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" t="s">
-        <v>3909</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" t="s">
-        <v>3910</v>
+        <v>3908</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" t="s">
-        <v>3911</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" t="s">
-        <v>3912</v>
+        <v>3910</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" t="s">
-        <v>3913</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" t="s">
-        <v>3914</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" t="s">
-        <v>3915</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" t="s">
-        <v>3916</v>
+        <v>3914</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" t="s">
-        <v>3917</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" t="s">
-        <v>3918</v>
+        <v>3916</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" t="s">
-        <v>3919</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" t="s">
-        <v>3921</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" t="s">
-        <v>3922</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="321" spans="1:1">
       <c r="A321" t="s">
-        <v>3923</v>
+        <v>3921</v>
       </c>
     </row>
     <row r="322" spans="1:1">
       <c r="A322" t="s">
-        <v>3925</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="323" spans="1:1">
       <c r="A323" t="s">
-        <v>3926</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="324" spans="1:1">
       <c r="A324" t="s">
-        <v>3927</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="325" spans="1:1">
       <c r="A325" t="s">
-        <v>3928</v>
+        <v>3926</v>
       </c>
     </row>
     <row r="326" spans="1:1">
       <c r="A326" t="s">
-        <v>3929</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="327" spans="1:1">
       <c r="A327" t="s">
-        <v>3930</v>
+        <v>3928</v>
       </c>
     </row>
     <row r="328" spans="1:1">
       <c r="A328" t="s">
-        <v>3931</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="329" spans="1:1">
       <c r="A329" t="s">
-        <v>3933</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="330" spans="1:1">
       <c r="A330" t="s">
-        <v>3934</v>
+        <v>3932</v>
       </c>
     </row>
     <row r="331" spans="1:1">
       <c r="A331" t="s">
-        <v>3935</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="332" spans="1:1">
       <c r="A332" t="s">
-        <v>3936</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="333" spans="1:1">
       <c r="A333" t="s">
-        <v>3937</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="334" spans="1:1">
       <c r="A334" t="s">
-        <v>3938</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="335" spans="1:1">
       <c r="A335" t="s">
-        <v>3939</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="336" spans="1:1">
       <c r="A336" t="s">
-        <v>3940</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="337" spans="1:1">
       <c r="A337" t="s">
-        <v>3941</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="338" spans="1:1">
       <c r="A338" t="s">
-        <v>3942</v>
+        <v>3940</v>
       </c>
     </row>
     <row r="339" spans="1:1">
       <c r="A339" t="s">
-        <v>3943</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="340" spans="1:1">
       <c r="A340" t="s">
-        <v>3945</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="341" spans="1:1">
       <c r="A341" t="s">
-        <v>3946</v>
+        <v>3944</v>
       </c>
     </row>
     <row r="342" spans="1:1">
       <c r="A342" t="s">
-        <v>3947</v>
+        <v>3945</v>
       </c>
     </row>
     <row r="343" spans="1:1">
       <c r="A343" t="s">
-        <v>3948</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="344" spans="1:1">
@@ -29879,97 +30130,97 @@
     </row>
     <row r="345" spans="1:1">
       <c r="A345" t="s">
-        <v>3949</v>
+        <v>3947</v>
       </c>
     </row>
     <row r="346" spans="1:1">
       <c r="A346" t="s">
-        <v>3950</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="347" spans="1:1">
       <c r="A347" t="s">
-        <v>3951</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="348" spans="1:1">
       <c r="A348" t="s">
-        <v>3954</v>
+        <v>3952</v>
       </c>
     </row>
     <row r="349" spans="1:1">
       <c r="A349" t="s">
-        <v>3955</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="350" spans="1:1">
       <c r="A350" t="s">
-        <v>3956</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="351" spans="1:1">
       <c r="A351" t="s">
-        <v>3958</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="352" spans="1:1">
       <c r="A352" t="s">
-        <v>3959</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
-        <v>3960</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
-        <v>3961</v>
+        <v>3959</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
-        <v>3962</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
-        <v>3963</v>
+        <v>3961</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
-        <v>3964</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
-        <v>3965</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>3966</v>
+        <v>3964</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>3967</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>3968</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
-        <v>3969</v>
+        <v>3967</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>3971</v>
+        <v>3969</v>
       </c>
       <c r="B363" t="s">
         <v>1986</v>
@@ -29977,52 +30228,52 @@
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>3972</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" t="s">
-        <v>3973</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
-        <v>3974</v>
+        <v>3972</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>3975</v>
+        <v>3973</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>3976</v>
+        <v>3974</v>
       </c>
     </row>
     <row r="369" spans="1:1">
       <c r="A369" t="s">
-        <v>3977</v>
+        <v>3975</v>
       </c>
     </row>
     <row r="370" spans="1:1">
       <c r="A370" t="s">
-        <v>3978</v>
+        <v>3976</v>
       </c>
     </row>
     <row r="371" spans="1:1">
       <c r="A371" t="s">
-        <v>3979</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="372" spans="1:1">
       <c r="A372" t="s">
-        <v>3980</v>
+        <v>3978</v>
       </c>
     </row>
     <row r="373" spans="1:1">
       <c r="A373" t="s">
-        <v>3981</v>
+        <v>3979</v>
       </c>
     </row>
     <row r="374" spans="1:1">
@@ -30032,222 +30283,222 @@
     </row>
     <row r="375" spans="1:1">
       <c r="A375" t="s">
-        <v>3982</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="376" spans="1:1">
       <c r="A376" t="s">
-        <v>3983</v>
+        <v>3981</v>
       </c>
     </row>
     <row r="377" spans="1:1">
       <c r="A377" t="s">
-        <v>3984</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="378" spans="1:1">
       <c r="A378" t="s">
-        <v>3977</v>
+        <v>3975</v>
       </c>
     </row>
     <row r="379" spans="1:1">
       <c r="A379" t="s">
-        <v>3978</v>
+        <v>3976</v>
       </c>
     </row>
     <row r="380" spans="1:1">
       <c r="A380" t="s">
-        <v>3979</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="381" spans="1:1">
       <c r="A381" t="s">
-        <v>3986</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="382" spans="1:1">
       <c r="A382" t="s">
-        <v>3987</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="383" spans="1:1">
       <c r="A383" t="s">
-        <v>3988</v>
+        <v>3986</v>
       </c>
     </row>
     <row r="384" spans="1:1">
       <c r="A384" t="s">
-        <v>3989</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="385" spans="1:1">
       <c r="A385" t="s">
-        <v>3990</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="386" spans="1:1">
       <c r="A386" t="s">
-        <v>3991</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="387" spans="1:1">
       <c r="A387" t="s">
-        <v>3992</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="388" spans="1:1">
       <c r="A388" t="s">
-        <v>3993</v>
+        <v>3991</v>
       </c>
     </row>
     <row r="389" spans="1:1">
       <c r="A389" t="s">
-        <v>3994</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="390" spans="1:1">
       <c r="A390" t="s">
-        <v>3995</v>
+        <v>3993</v>
       </c>
     </row>
     <row r="391" spans="1:1">
       <c r="A391" t="s">
-        <v>3996</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="392" spans="1:1">
       <c r="A392" t="s">
-        <v>3997</v>
+        <v>3995</v>
       </c>
     </row>
     <row r="393" spans="1:1">
       <c r="A393" t="s">
-        <v>3999</v>
+        <v>3997</v>
       </c>
     </row>
     <row r="394" spans="1:1">
       <c r="A394" t="s">
-        <v>4000</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="395" spans="1:1">
       <c r="A395" t="s">
-        <v>4001</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="396" spans="1:1">
       <c r="A396" t="s">
-        <v>4002</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="397" spans="1:1">
       <c r="A397" t="s">
-        <v>4003</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="398" spans="1:1">
       <c r="A398" t="s">
-        <v>4004</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="399" spans="1:1">
       <c r="A399" t="s">
-        <v>4005</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="400" spans="1:1">
       <c r="A400" t="s">
-        <v>4006</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="401" spans="1:1">
       <c r="A401" t="s">
-        <v>4007</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="402" spans="1:1">
       <c r="A402" t="s">
-        <v>4008</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="403" spans="1:1">
       <c r="A403" t="s">
-        <v>4009</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="404" spans="1:1">
       <c r="A404" t="s">
-        <v>4010</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="405" spans="1:1">
       <c r="A405" t="s">
-        <v>4011</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="406" spans="1:1">
       <c r="A406" t="s">
-        <v>4012</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="407" spans="1:1">
       <c r="A407" t="s">
-        <v>4013</v>
+        <v>4011</v>
       </c>
     </row>
     <row r="408" spans="1:1">
       <c r="A408" t="s">
-        <v>4014</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="409" spans="1:1">
       <c r="A409" t="s">
-        <v>4015</v>
+        <v>4013</v>
       </c>
     </row>
     <row r="410" spans="1:1">
       <c r="A410" t="s">
-        <v>4016</v>
+        <v>4014</v>
       </c>
     </row>
     <row r="411" spans="1:1">
       <c r="A411" t="s">
-        <v>4019</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="412" spans="1:1">
       <c r="A412" t="s">
-        <v>4021</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="413" spans="1:1">
       <c r="A413" t="s">
-        <v>4022</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="414" spans="1:1">
       <c r="A414" t="s">
-        <v>4023</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="415" spans="1:1">
       <c r="A415" t="s">
-        <v>4024</v>
+        <v>4022</v>
       </c>
     </row>
     <row r="416" spans="1:1">
       <c r="A416" t="s">
-        <v>4026</v>
+        <v>4024</v>
       </c>
     </row>
     <row r="417" spans="1:1">
       <c r="A417" t="s">
-        <v>4027</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="418" spans="1:1">
       <c r="A418" t="s">
-        <v>4028</v>
+        <v>4026</v>
       </c>
     </row>
     <row r="419" spans="1:1">
@@ -30257,92 +30508,92 @@
     </row>
     <row r="420" spans="1:1">
       <c r="A420" t="s">
-        <v>4029</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="421" spans="1:1">
       <c r="A421" t="s">
-        <v>4030</v>
+        <v>4028</v>
       </c>
     </row>
     <row r="422" spans="1:1">
       <c r="A422" t="s">
-        <v>4031</v>
+        <v>4029</v>
       </c>
     </row>
     <row r="423" spans="1:1">
       <c r="A423" t="s">
-        <v>4032</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="424" spans="1:1">
       <c r="A424" t="s">
-        <v>4033</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="425" spans="1:1">
       <c r="A425" t="s">
-        <v>3768</v>
+        <v>3766</v>
       </c>
     </row>
     <row r="426" spans="1:1">
       <c r="A426" t="s">
-        <v>4034</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="427" spans="1:1">
       <c r="A427" t="s">
-        <v>4035</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="428" spans="1:1">
       <c r="A428" t="s">
-        <v>4037</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="429" spans="1:1">
       <c r="A429" t="s">
-        <v>4038</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="430" spans="1:1">
       <c r="A430" t="s">
-        <v>4039</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="431" spans="1:1">
       <c r="A431" t="s">
-        <v>4040</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="432" spans="1:1">
       <c r="A432" t="s">
-        <v>4041</v>
+        <v>4039</v>
       </c>
     </row>
     <row r="433" spans="1:1">
       <c r="A433" t="s">
-        <v>4042</v>
+        <v>4040</v>
       </c>
     </row>
     <row r="434" spans="1:1">
       <c r="A434" t="s">
-        <v>4043</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="435" spans="1:1">
       <c r="A435" t="s">
-        <v>4044</v>
+        <v>4042</v>
       </c>
     </row>
     <row r="436" spans="1:1">
       <c r="A436" t="s">
-        <v>4045</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="437" spans="1:1">
       <c r="A437" t="s">
-        <v>4046</v>
+        <v>4044</v>
       </c>
     </row>
   </sheetData>
@@ -30354,19 +30605,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C8DBF6E-AC4E-4CA7-A472-CBBE682B211E}">
   <dimension ref="A1:B133"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>3672</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>3703</v>
+        <v>3701</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -30376,102 +30627,102 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>3704</v>
+        <v>3702</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>3709</v>
+        <v>3707</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>3713</v>
+        <v>3711</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>3719</v>
+        <v>3717</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>3760</v>
+        <v>3758</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>3765</v>
+        <v>3763</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>3784</v>
+        <v>3782</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>3785</v>
+        <v>3783</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>3787</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>3814</v>
+        <v>3812</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>3816</v>
+        <v>3814</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>3817</v>
+        <v>3815</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>3818</v>
+        <v>3816</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>3842</v>
+        <v>3840</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>3845</v>
+        <v>3843</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>3846</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>3855</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>3870</v>
+        <v>3868</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>3879</v>
+        <v>3877</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>3885</v>
+        <v>3883</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -30486,27 +30737,27 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>3897</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>3920</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>3924</v>
+        <v>3922</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>3932</v>
+        <v>3930</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>3944</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -30514,52 +30765,203 @@
         <v>1027</v>
       </c>
       <c r="B31" t="s">
-        <v>3952</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>3953</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>3957</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>3985</v>
+        <v>3983</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>3998</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>4017</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>4018</v>
+        <v>4016</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>4020</v>
+        <v>4018</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>4025</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>4036</v>
+        <v>4034</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>3046</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="B133" t="s">
+        <v>3217</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A609A4-3153-466B-A62A-545BF37E7FA2}">
+  <dimension ref="A1:B133"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="24.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>3670</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>3184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>3702</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>3707</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>3227</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>3895</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>3918</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>3983</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>4034</v>
       </c>
     </row>
     <row r="132" spans="1:2">

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF9EBFC-D467-46BA-A9B9-779990629BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BADFE4-97E4-419D-9686-ED0EBC9FE11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="736" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21990,7 +21990,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCB9A67-77EF-4B4B-A409-BADD45AFE303}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:XFD3509"/>
+  <dimension ref="A1:XFD3501"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
@@ -31790,7 +31790,7 @@
         <v>6241</v>
       </c>
     </row>
-    <row r="1226" spans="1:2" hidden="1">
+    <row r="1226" spans="1:2">
       <c r="A1226" t="s">
         <v>2240</v>
       </c>
@@ -31798,7 +31798,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="1227" spans="1:2" hidden="1">
+    <row r="1227" spans="1:2">
       <c r="A1227" t="s">
         <v>2247</v>
       </c>
@@ -31806,7 +31806,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="1228" spans="1:2" hidden="1">
+    <row r="1228" spans="1:2">
       <c r="A1228" t="s">
         <v>2242</v>
       </c>
@@ -31814,7 +31814,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="1229" spans="1:2" hidden="1">
+    <row r="1229" spans="1:2">
       <c r="A1229" t="s">
         <v>2244</v>
       </c>
@@ -31822,7 +31822,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="1230" spans="1:2" hidden="1">
+    <row r="1230" spans="1:2">
       <c r="A1230" t="s">
         <v>2248</v>
       </c>
@@ -31830,7 +31830,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="1231" spans="1:2" hidden="1">
+    <row r="1231" spans="1:2">
       <c r="A1231" s="1" t="s">
         <v>365</v>
       </c>
@@ -84990,6 +84990,7 @@
         <v>6973</v>
       </c>
     </row>
+    <row r="1735" spans="1:2" hidden="1"/>
     <row r="1736" spans="1:2" hidden="1">
       <c r="A1736" t="s">
         <v>6292</v>
@@ -86414,6 +86415,7 @@
         <v>1836</v>
       </c>
     </row>
+    <row r="1914" spans="1:2" hidden="1"/>
     <row r="1915" spans="1:2" hidden="1">
       <c r="A1915" t="s">
         <v>3560</v>
@@ -99023,6 +99025,12 @@
         <v>1785</v>
       </c>
     </row>
+    <row r="3489" spans="1:2" hidden="1"/>
+    <row r="3490" spans="1:2" hidden="1"/>
+    <row r="3491" spans="1:2" hidden="1"/>
+    <row r="3492" spans="1:2" hidden="1"/>
+    <row r="3493" spans="1:2" hidden="1"/>
+    <row r="3494" spans="1:2" hidden="1"/>
     <row r="3495" spans="1:2" hidden="1">
       <c r="A3495" t="s">
         <v>7011</v>
@@ -99079,23 +99087,16 @@
         <v>7024</v>
       </c>
     </row>
-    <row r="3505" customFormat="1"/>
-    <row r="3506" customFormat="1"/>
-    <row r="3507" customFormat="1"/>
-    <row r="3508" customFormat="1"/>
-    <row r="3509" customFormat="1"/>
   </sheetData>
   <autoFilter ref="A1:B3501" xr:uid="{FDCB9A67-77EF-4B4B-A409-BADD45AFE303}">
     <filterColumn colId="0">
       <filters>
-        <filter val="зомби-команд"/>
-        <filter val="зомби-команда"/>
-        <filter val="зомби-командам"/>
-        <filter val="зомби-командами"/>
-        <filter val="зомби-команду"/>
-        <filter val="зомби-команды"/>
-        <filter val="мини-"/>
-        <filter val="объемно-резонирующей"/>
+        <filter val="командир"/>
+        <filter val="командира"/>
+        <filter val="командирами"/>
+        <filter val="командиров"/>
+        <filter val="командиры"/>
+        <filter val="командование"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/словари/Главный словарь.xlsx
+++ b/словари/Главный словарь.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37090F05-E177-4617-B733-C1741D3966BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C6F188-CA8A-4B57-993E-199478B1CEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="2110" windowWidth="25820" windowHeight="10300" tabRatio="736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Простые" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -23438,7 +23435,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDCB9A67-77EF-4B4B-A409-BADD45AFE303}">
   <dimension ref="A1:XFD3937"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="21.7265625" customWidth="1"/>
     <col min="2" max="2" width="42.453125" customWidth="1"/>
@@ -24085,7 +24082,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75">
+    <row r="82" spans="1:2" ht="15.5">
       <c r="A82" s="14" t="s">
         <v>2418</v>
       </c>
@@ -25845,7 +25842,7 @@
         <v>4169</v>
       </c>
     </row>
-    <row r="302" spans="1:2" ht="15.75">
+    <row r="302" spans="1:2" ht="15.5">
       <c r="A302" s="14" t="s">
         <v>5</v>
       </c>
@@ -25853,7 +25850,7 @@
         <v>4039</v>
       </c>
     </row>
-    <row r="303" spans="1:2" ht="15.75">
+    <row r="303" spans="1:2" ht="15.5">
       <c r="A303" s="14" t="s">
         <v>4044</v>
       </c>
@@ -25861,7 +25858,7 @@
         <v>4041</v>
       </c>
     </row>
-    <row r="304" spans="1:2" ht="15.75">
+    <row r="304" spans="1:2" ht="15.5">
       <c r="A304" s="14" t="s">
         <v>4042</v>
       </c>
@@ -25869,7 +25866,7 @@
         <v>4043</v>
       </c>
     </row>
-    <row r="305" spans="1:2" ht="15.75">
+    <row r="305" spans="1:2" ht="15.5">
       <c r="A305" s="14" t="s">
         <v>4040</v>
       </c>
@@ -26821,7 +26818,7 @@
         <v>6974</v>
       </c>
     </row>
-    <row r="424" spans="1:2" ht="15.75">
+    <row r="424" spans="1:2" ht="15.5">
       <c r="A424" s="14" t="s">
         <v>5700</v>
       </c>
@@ -26829,7 +26826,7 @@
         <v>5701</v>
       </c>
     </row>
-    <row r="425" spans="1:2" ht="15.75">
+    <row r="425" spans="1:2" ht="15.5">
       <c r="A425" s="14" t="s">
         <v>5691</v>
       </c>
@@ -26837,7 +26834,7 @@
         <v>5693</v>
       </c>
     </row>
-    <row r="426" spans="1:2" ht="15.75">
+    <row r="426" spans="1:2" ht="15.5">
       <c r="A426" s="14" t="s">
         <v>5696</v>
       </c>
@@ -26845,7 +26842,7 @@
         <v>5697</v>
       </c>
     </row>
-    <row r="427" spans="1:2" ht="15.75">
+    <row r="427" spans="1:2" ht="15.5">
       <c r="A427" s="14" t="s">
         <v>5689</v>
       </c>
@@ -26853,7 +26850,7 @@
         <v>5690</v>
       </c>
     </row>
-    <row r="428" spans="1:2" ht="15.75">
+    <row r="428" spans="1:2" ht="15.5">
       <c r="A428" s="14" t="s">
         <v>5692</v>
       </c>
@@ -26861,7 +26858,7 @@
         <v>5688</v>
       </c>
     </row>
-    <row r="429" spans="1:2" ht="15.75">
+    <row r="429" spans="1:2" ht="15.5">
       <c r="A429" s="14" t="s">
         <v>5712</v>
       </c>
@@ -26869,7 +26866,7 @@
         <v>5713</v>
       </c>
     </row>
-    <row r="430" spans="1:2" ht="15.75">
+    <row r="430" spans="1:2" ht="15.5">
       <c r="A430" s="14" t="s">
         <v>5706</v>
       </c>
@@ -26877,7 +26874,7 @@
         <v>5707</v>
       </c>
     </row>
-    <row r="431" spans="1:2" ht="15.75">
+    <row r="431" spans="1:2" ht="15.5">
       <c r="A431" s="14" t="s">
         <v>5704</v>
       </c>
@@ -26885,7 +26882,7 @@
         <v>5705</v>
       </c>
     </row>
-    <row r="432" spans="1:2" ht="15.75">
+    <row r="432" spans="1:2" ht="15.5">
       <c r="A432" s="14" t="s">
         <v>5702</v>
       </c>
@@ -26893,7 +26890,7 @@
         <v>5703</v>
       </c>
     </row>
-    <row r="433" spans="1:2" ht="15.75">
+    <row r="433" spans="1:2" ht="15.5">
       <c r="A433" s="14" t="s">
         <v>5694</v>
       </c>
@@ -26901,7 +26898,7 @@
         <v>5695</v>
       </c>
     </row>
-    <row r="434" spans="1:2" ht="15.75">
+    <row r="434" spans="1:2" ht="15.5">
       <c r="A434" s="14" t="s">
         <v>5698</v>
       </c>
@@ -26909,7 +26906,7 @@
         <v>5699</v>
       </c>
     </row>
-    <row r="435" spans="1:2" ht="15.75">
+    <row r="435" spans="1:2" ht="15.5">
       <c r="A435" s="14" t="s">
         <v>5708</v>
       </c>
@@ -26917,7 +26914,7 @@
         <v>5709</v>
       </c>
     </row>
-    <row r="436" spans="1:2" ht="15.75">
+    <row r="436" spans="1:2" ht="15.5">
       <c r="A436" s="14" t="s">
         <v>5710</v>
       </c>
@@ -26925,7 +26922,7 @@
         <v>5711</v>
       </c>
     </row>
-    <row r="437" spans="1:2" ht="15.75">
+    <row r="437" spans="1:2" ht="15.5">
       <c r="A437" s="14" t="s">
         <v>5716</v>
       </c>
@@ -26933,7 +26930,7 @@
         <v>5717</v>
       </c>
     </row>
-    <row r="438" spans="1:2" ht="15.75">
+    <row r="438" spans="1:2" ht="15.5">
       <c r="A438" s="14" t="s">
         <v>5714</v>
       </c>
@@ -29509,7 +29506,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="761" spans="1:2" ht="15.75">
+    <row r="761" spans="1:2" ht="15.5">
       <c r="A761" s="14" t="s">
         <v>3207</v>
       </c>
@@ -29517,7 +29514,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="762" spans="1:2" ht="15.75">
+    <row r="762" spans="1:2" ht="15.5">
       <c r="A762" s="14" t="s">
         <v>3198</v>
       </c>
@@ -29525,7 +29522,7 @@
         <v>3199</v>
       </c>
     </row>
-    <row r="763" spans="1:2" ht="15.75">
+    <row r="763" spans="1:2" ht="15.5">
       <c r="A763" s="14" t="s">
         <v>3204</v>
       </c>
@@ -29533,7 +29530,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="764" spans="1:2" ht="15.75">
+    <row r="764" spans="1:2" ht="15.5">
       <c r="A764" s="14" t="s">
         <v>2409</v>
       </c>
@@ -29541,7 +29538,7 @@
         <v>3192</v>
       </c>
     </row>
-    <row r="765" spans="1:2" ht="15.75">
+    <row r="765" spans="1:2" ht="15.5">
       <c r="A765" s="14" t="s">
         <v>3200</v>
       </c>
@@ -29549,7 +29546,7 @@
         <v>3201</v>
       </c>
     </row>
-    <row r="766" spans="1:2" ht="15.75">
+    <row r="766" spans="1:2" ht="15.5">
       <c r="A766" s="14" t="s">
         <v>3202</v>
       </c>
@@ -29557,7 +29554,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="767" spans="1:2" ht="15.75">
+    <row r="767" spans="1:2" ht="15.5">
       <c r="A767" s="14" t="s">
         <v>3197</v>
       </c>
@@ -29565,7 +29562,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="768" spans="1:2" ht="15.75">
+    <row r="768" spans="1:2" ht="15.5">
       <c r="A768" s="14" t="s">
         <v>3193</v>
       </c>
@@ -29573,7 +29570,7 @@
         <v>3194</v>
       </c>
     </row>
-    <row r="769" spans="1:2" ht="15.75">
+    <row r="769" spans="1:2" ht="15.5">
       <c r="A769" s="14" t="s">
         <v>3205</v>
       </c>
@@ -29581,7 +29578,7 @@
         <v>3206</v>
       </c>
     </row>
-    <row r="770" spans="1:2" ht="15.75">
+    <row r="770" spans="1:2" ht="15.5">
       <c r="A770" s="14" t="s">
         <v>3195</v>
       </c>
@@ -31624,7 +31621,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="1025" spans="1:2" ht="15.75">
+    <row r="1025" spans="1:2" ht="15.5">
       <c r="A1025" s="14" t="s">
         <v>2416</v>
       </c>
@@ -83266,7 +83263,7 @@
         <v>3629</v>
       </c>
     </row>
-    <row r="1338" spans="1:16384" customFormat="1" ht="15.75">
+    <row r="1338" spans="1:16384" customFormat="1" ht="15.5">
       <c r="A1338" s="14" t="s">
         <v>3215</v>
       </c>
@@ -83282,7 +83279,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="1340" spans="1:16384" customFormat="1" ht="15.75">
+    <row r="1340" spans="1:16384" customFormat="1" ht="15.5">
       <c r="A1340" s="14" t="s">
         <v>3214</v>
       </c>
@@ -83290,7 +83287,7 @@
         <v>3219</v>
       </c>
     </row>
-    <row r="1341" spans="1:16384" customFormat="1" ht="15.75">
+    <row r="1341" spans="1:16384" customFormat="1" ht="15.5">
       <c r="A1341" s="14" t="s">
         <v>3216</v>
       </c>
@@ -83298,7 +83295,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="1342" spans="1:16384" customFormat="1" ht="15.75">
+    <row r="1342" spans="1:16384" customFormat="1" ht="15.5">
       <c r="A1342" s="14" t="s">
         <v>2402</v>
       </c>
@@ -83306,7 +83303,7 @@
         <v>3217</v>
       </c>
     </row>
-    <row r="1343" spans="1:16384" customFormat="1" ht="15.75">
+    <row r="1343" spans="1:16384" customFormat="1" ht="15.5">
       <c r="A1343" s="14" t="s">
         <v>3222</v>
       </c>
@@ -83314,7 +83311,7 @@
         <v>3223</v>
       </c>
     </row>
-    <row r="1344" spans="1:16384" customFormat="1" ht="15.75">
+    <row r="1344" spans="1:16384" customFormat="1" ht="15.5">
       <c r="A1344" s="14" t="s">
         <v>3213</v>
       </c>
@@ -83722,7 +83719,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="1395" spans="1:2" ht="15.75">
+    <row r="1395" spans="1:2" ht="15.5">
       <c r="A1395" s="14" t="s">
         <v>2396</v>
       </c>
@@ -83730,7 +83727,7 @@
         <v>3224</v>
       </c>
     </row>
-    <row r="1396" spans="1:2" ht="15.75">
+    <row r="1396" spans="1:2" ht="15.5">
       <c r="A1396" s="14" t="s">
         <v>3227</v>
       </c>
@@ -83738,7 +83735,7 @@
         <v>3228</v>
       </c>
     </row>
-    <row r="1397" spans="1:2" ht="15.75">
+    <row r="1397" spans="1:2" ht="15.5">
       <c r="A1397" s="14" t="s">
         <v>3225</v>
       </c>
@@ -83746,7 +83743,7 @@
         <v>3226</v>
       </c>
     </row>
-    <row r="1398" spans="1:2" ht="15.75">
+    <row r="1398" spans="1:2" ht="15.5">
       <c r="A1398" s="14" t="s">
         <v>3229</v>
       </c>
@@ -83994,7 +83991,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="1429" spans="1:2" ht="15.75">
+    <row r="1429" spans="1:2" ht="15.5">
       <c r="A1429" s="14" t="s">
         <v>2397</v>
       </c>
@@ -84917,7 +84914,7 @@
         <v>6845</v>
       </c>
     </row>
-    <row r="1544" spans="1:3" ht="15.75">
+    <row r="1544" spans="1:3" ht="15.5">
       <c r="A1544" s="18" t="s">
         <v>6840</v>
       </c>
@@ -85749,7 +85746,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="1648" spans="1:2" ht="15.75">
+    <row r="1648" spans="1:2" ht="15.5">
       <c r="A1648" s="14" t="s">
         <v>6140</v>
       </c>
@@ -85757,7 +85754,7 @@
         <v>5393</v>
       </c>
     </row>
-    <row r="1649" spans="1:2" ht="15.75">
+    <row r="1649" spans="1:2" ht="15.5">
       <c r="A1649" s="14" t="s">
         <v>6139</v>
       </c>
@@ -85765,7 +85762,7 @@
         <v>5393</v>
       </c>
     </row>
-    <row r="1650" spans="1:2" ht="15.75">
+    <row r="1650" spans="1:2" ht="15.5">
       <c r="A1650" s="14" t="s">
         <v>6136</v>
       </c>
@@ -85773,7 +85770,7 @@
         <v>6137</v>
       </c>
     </row>
-    <row r="1651" spans="1:2" ht="15.75">
+    <row r="1651" spans="1:2" ht="15.5">
       <c r="A1651" s="14" t="s">
         <v>6138</v>
       </c>
@@ -85781,7 +85778,7 @@
         <v>5389</v>
       </c>
     </row>
-    <row r="1652" spans="1:2" ht="15.75">
+    <row r="1652" spans="1:2" ht="15.5">
       <c r="A1652" s="14" t="s">
         <v>6141</v>
       </c>
@@ -85789,7 +85786,7 @@
         <v>5391</v>
       </c>
     </row>
-    <row r="1653" spans="1:2" ht="15.75">
+    <row r="1653" spans="1:2" ht="15.5">
       <c r="A1653" s="14" t="s">
         <v>3647</v>
       </c>
@@ -85797,7 +85794,7 @@
         <v>5388</v>
       </c>
     </row>
-    <row r="1654" spans="1:2" ht="15.75">
+    <row r="1654" spans="1:2" ht="15.5">
       <c r="A1654" s="14" t="s">
         <v>6134</v>
       </c>
@@ -85805,7 +85802,7 @@
         <v>6135</v>
       </c>
     </row>
-    <row r="1655" spans="1:2" ht="15.75">
+    <row r="1655" spans="1:2" ht="15.5">
       <c r="A1655" s="14" t="s">
         <v>6130</v>
       </c>
@@ -85813,7 +85810,7 @@
         <v>6131</v>
       </c>
     </row>
-    <row r="1656" spans="1:2" ht="15.75">
+    <row r="1656" spans="1:2" ht="15.5">
       <c r="A1656" s="14" t="s">
         <v>6132</v>
       </c>
@@ -85821,7 +85818,7 @@
         <v>5384</v>
       </c>
     </row>
-    <row r="1657" spans="1:2" ht="15.75">
+    <row r="1657" spans="1:2" ht="15.5">
       <c r="A1657" s="14" t="s">
         <v>6133</v>
       </c>
@@ -85829,7 +85826,7 @@
         <v>5382</v>
       </c>
     </row>
-    <row r="1658" spans="1:2" ht="15.75">
+    <row r="1658" spans="1:2" ht="15.5">
       <c r="A1658" s="14" t="s">
         <v>6129</v>
       </c>
@@ -86253,7 +86250,7 @@
         <v>6513</v>
       </c>
     </row>
-    <row r="1711" spans="1:2" ht="15.75">
+    <row r="1711" spans="1:2" ht="15.5">
       <c r="A1711" s="14" t="s">
         <v>1470</v>
       </c>
@@ -86261,7 +86258,7 @@
         <v>6120</v>
       </c>
     </row>
-    <row r="1712" spans="1:2" ht="15.75">
+    <row r="1712" spans="1:2" ht="15.5">
       <c r="A1712" s="14" t="s">
         <v>2413</v>
       </c>
@@ -86269,7 +86266,7 @@
         <v>6119</v>
       </c>
     </row>
-    <row r="1713" spans="1:3" ht="15.75">
+    <row r="1713" spans="1:3" ht="15.5">
       <c r="A1713" s="14" t="s">
         <v>6121</v>
       </c>
@@ -86277,7 +86274,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="1714" spans="1:3" ht="15.75">
+    <row r="1714" spans="1:3" ht="15.5">
       <c r="A1714" s="14" t="s">
         <v>6124</v>
       </c>
@@ -86389,7 +86386,7 @@
         <v>4913</v>
       </c>
     </row>
-    <row r="1728" spans="1:3" ht="15.75">
+    <row r="1728" spans="1:3" ht="15.5">
       <c r="A1728" s="14" t="s">
         <v>112</v>
       </c>
@@ -86400,7 +86397,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="1729" spans="1:3" ht="15.75">
+    <row r="1729" spans="1:3" ht="15.5">
       <c r="A1729" s="14" t="s">
         <v>6122</v>
       </c>
@@ -86408,7 +86405,7 @@
         <v>6123</v>
       </c>
     </row>
-    <row r="1730" spans="1:3" ht="15.75">
+    <row r="1730" spans="1:3" ht="15.5">
       <c r="A1730" s="14" t="s">
         <v>6125</v>
       </c>
@@ -86416,7 +86413,7 @@
         <v>6126</v>
       </c>
     </row>
-    <row r="1731" spans="1:3" ht="15.75">
+    <row r="1731" spans="1:3" ht="15.5">
       <c r="A1731" s="14" t="s">
         <v>109</v>
       </c>
@@ -86851,7 +86848,7 @@
         <v>6866</v>
       </c>
     </row>
-    <row r="1785" spans="1:2" ht="15.75">
+    <row r="1785" spans="1:2" ht="15.5">
       <c r="A1785" s="18" t="s">
         <v>6860</v>
       </c>
@@ -88758,7 +88755,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="2025" spans="1:2" ht="15.75">
+    <row r="2025" spans="1:2" ht="15.5">
       <c r="A2025" s="14" t="s">
         <v>5107</v>
       </c>
@@ -88766,7 +88763,7 @@
         <v>5108</v>
       </c>
     </row>
-    <row r="2026" spans="1:2" ht="15.75">
+    <row r="2026" spans="1:2" ht="15.5">
       <c r="A2026" s="14" t="s">
         <v>5096</v>
       </c>
@@ -88774,7 +88771,7 @@
         <v>5097</v>
       </c>
     </row>
-    <row r="2027" spans="1:2" ht="15.75">
+    <row r="2027" spans="1:2" ht="15.5">
       <c r="A2027" s="14" t="s">
         <v>5111</v>
       </c>
@@ -88782,7 +88779,7 @@
         <v>5112</v>
       </c>
     </row>
-    <row r="2028" spans="1:2" ht="15.75">
+    <row r="2028" spans="1:2" ht="15.5">
       <c r="A2028" s="14" t="s">
         <v>5098</v>
       </c>
@@ -88790,7 +88787,7 @@
         <v>5099</v>
       </c>
     </row>
-    <row r="2029" spans="1:2" ht="15.75">
+    <row r="2029" spans="1:2" ht="15.5">
       <c r="A2029" s="14" t="s">
         <v>5102</v>
       </c>
@@ -88798,7 +88795,7 @@
         <v>5103</v>
       </c>
     </row>
-    <row r="2030" spans="1:2" ht="15.75">
+    <row r="2030" spans="1:2" ht="15.5">
       <c r="A2030" s="14" t="s">
         <v>5092</v>
       </c>
@@ -88806,7 +88803,7 @@
         <v>5093</v>
       </c>
     </row>
-    <row r="2031" spans="1:2" ht="15.75">
+    <row r="2031" spans="1:2" ht="15.5">
       <c r="A2031" s="14" t="s">
         <v>5094</v>
       </c>
@@ -88814,7 +88811,7 @@
         <v>5095</v>
       </c>
     </row>
-    <row r="2032" spans="1:2" ht="15.75">
+    <row r="2032" spans="1:2" ht="15.5">
       <c r="A2032" s="14" t="s">
         <v>3026</v>
       </c>
@@ -88822,7 +88819,7 @@
         <v>5085</v>
       </c>
     </row>
-    <row r="2033" spans="1:2" ht="15.75">
+    <row r="2033" spans="1:2" ht="15.5">
       <c r="A2033" s="14" t="s">
         <v>5100</v>
       </c>
@@ -88830,7 +88827,7 @@
         <v>5101</v>
       </c>
     </row>
-    <row r="2034" spans="1:2" ht="15.75">
+    <row r="2034" spans="1:2" ht="15.5">
       <c r="A2034" s="14" t="s">
         <v>5088</v>
       </c>
@@ -88838,7 +88835,7 @@
         <v>5089</v>
       </c>
     </row>
-    <row r="2035" spans="1:2" ht="15.75">
+    <row r="2035" spans="1:2" ht="15.5">
       <c r="A2035" s="14" t="s">
         <v>5090</v>
       </c>
@@ -88846,7 +88843,7 @@
         <v>5091</v>
       </c>
     </row>
-    <row r="2036" spans="1:2" ht="15.75">
+    <row r="2036" spans="1:2" ht="15.5">
       <c r="A2036" s="14" t="s">
         <v>5086</v>
       </c>
@@ -88854,7 +88851,7 @@
         <v>5087</v>
       </c>
     </row>
-    <row r="2037" spans="1:2" ht="15.75">
+    <row r="2037" spans="1:2" ht="15.5">
       <c r="A2037" s="14" t="s">
         <v>3552</v>
       </c>
@@ -88862,7 +88859,7 @@
         <v>5121</v>
       </c>
     </row>
-    <row r="2038" spans="1:2" ht="15.75">
+    <row r="2038" spans="1:2" ht="15.5">
       <c r="A2038" s="14" t="s">
         <v>3587</v>
       </c>
@@ -89561,7 +89558,7 @@
         <v>4166</v>
       </c>
     </row>
-    <row r="2125" spans="1:2" ht="15.75">
+    <row r="2125" spans="1:2" ht="15.5">
       <c r="A2125" s="14" t="s">
         <v>6127</v>
       </c>
@@ -91169,7 +91166,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="2326" spans="1:2" ht="15.75">
+    <row r="2326" spans="1:2" ht="15.5">
       <c r="A2326" s="5" t="s">
         <v>1126</v>
       </c>
@@ -91337,7 +91334,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="2347" spans="1:2" ht="15.75">
+    <row r="2347" spans="1:2" ht="15.5">
       <c r="A2347" s="14" t="s">
         <v>3210</v>
       </c>
@@ -91345,7 +91342,7 @@
         <v>3276</v>
       </c>
     </row>
-    <row r="2348" spans="1:2" ht="15.75">
+    <row r="2348" spans="1:2" ht="15.5">
       <c r="A2348" s="14" t="s">
         <v>832</v>
       </c>
@@ -91361,7 +91358,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="2350" spans="1:2" ht="15.75">
+    <row r="2350" spans="1:2" ht="15.5">
       <c r="A2350" s="14" t="s">
         <v>2388</v>
       </c>
@@ -91377,7 +91374,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="2352" spans="1:2" ht="15.75">
+    <row r="2352" spans="1:2" ht="15.5">
       <c r="A2352" s="14" t="s">
         <v>3211</v>
       </c>
@@ -91385,7 +91382,7 @@
         <v>3277</v>
       </c>
     </row>
-    <row r="2353" spans="1:2" ht="15.75">
+    <row r="2353" spans="1:2" ht="15.5">
       <c r="A2353" s="14" t="s">
         <v>3208</v>
       </c>
@@ -91393,7 +91390,7 @@
         <v>3272</v>
       </c>
     </row>
-    <row r="2354" spans="1:2" ht="15.75">
+    <row r="2354" spans="1:2" ht="15.5">
       <c r="A2354" s="14" t="s">
         <v>3212</v>
       </c>
@@ -91401,7 +91398,7 @@
         <v>3278</v>
       </c>
     </row>
-    <row r="2355" spans="1:2" ht="15.75">
+    <row r="2355" spans="1:2" ht="15.5">
       <c r="A2355" s="14" t="s">
         <v>3209</v>
       </c>
@@ -91425,7 +91422,7 @@
         <v>6795</v>
       </c>
     </row>
-    <row r="2358" spans="1:2" ht="15.75">
+    <row r="2358" spans="1:2" ht="15.5">
       <c r="A2358" s="14" t="s">
         <v>810</v>
       </c>
@@ -91713,7 +91710,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="2394" spans="1:2" ht="15.75">
+    <row r="2394" spans="1:2" ht="15.5">
       <c r="A2394" s="14" t="s">
         <v>2433</v>
       </c>
@@ -92313,7 +92310,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="2469" spans="1:2" ht="15.75">
+    <row r="2469" spans="1:2" ht="15.5">
       <c r="A2469" s="14" t="s">
         <v>4086</v>
       </c>
@@ -92321,7 +92318,7 @@
         <v>4087</v>
       </c>
     </row>
-    <row r="2470" spans="1:2" ht="15.75">
+    <row r="2470" spans="1:2" ht="15.5">
       <c r="A2470" s="14" t="s">
         <v>4088</v>
       </c>
@@ -92377,7 +92374,7 @@
         <v>4091</v>
       </c>
     </row>
-    <row r="2477" spans="1:2" ht="15.75">
+    <row r="2477" spans="1:2" ht="15.5">
       <c r="A2477" s="14" t="s">
         <v>4075</v>
       </c>
@@ -92385,7 +92382,7 @@
         <v>4076</v>
       </c>
     </row>
-    <row r="2478" spans="1:2" ht="15.75">
+    <row r="2478" spans="1:2" ht="15.5">
       <c r="A2478" s="14" t="s">
         <v>4079</v>
       </c>
@@ -92393,7 +92390,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="2479" spans="1:2" ht="15.75">
+    <row r="2479" spans="1:2" ht="15.5">
       <c r="A2479" s="14" t="s">
         <v>4077</v>
       </c>
@@ -92401,7 +92398,7 @@
         <v>4078</v>
       </c>
     </row>
-    <row r="2480" spans="1:2" ht="15.75">
+    <row r="2480" spans="1:2" ht="15.5">
       <c r="A2480" s="14" t="s">
         <v>4073</v>
       </c>
@@ -92409,7 +92406,7 @@
         <v>4074</v>
       </c>
     </row>
-    <row r="2481" spans="1:4" ht="15.75">
+    <row r="2481" spans="1:4" ht="15.5">
       <c r="A2481" s="14" t="s">
         <v>2412</v>
       </c>
@@ -92417,7 +92414,7 @@
         <v>4072</v>
       </c>
     </row>
-    <row r="2482" spans="1:4" ht="15.75">
+    <row r="2482" spans="1:4" ht="15.5">
       <c r="A2482" s="14" t="s">
         <v>4084</v>
       </c>
@@ -92425,7 +92422,7 @@
         <v>4085</v>
       </c>
     </row>
-    <row r="2483" spans="1:4" ht="15.75">
+    <row r="2483" spans="1:4" ht="15.5">
       <c r="A2483" s="14" t="s">
         <v>4925</v>
       </c>
@@ -92436,7 +92433,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="2484" spans="1:4" ht="15.75">
+    <row r="2484" spans="1:4" ht="15.5">
       <c r="A2484" s="14" t="s">
         <v>4926</v>
       </c>
@@ -92444,7 +92441,7 @@
         <v>4927</v>
       </c>
     </row>
-    <row r="2485" spans="1:4" ht="15.75">
+    <row r="2485" spans="1:4" ht="15.5">
       <c r="A2485" s="14" t="s">
         <v>4930</v>
       </c>
@@ -92452,7 +92449,7 @@
         <v>4931</v>
       </c>
     </row>
-    <row r="2486" spans="1:4" ht="15.75">
+    <row r="2486" spans="1:4" ht="15.5">
       <c r="A2486" s="14" t="s">
         <v>4932</v>
       </c>
@@ -92564,7 +92561,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="2500" spans="1:2" ht="15.75">
+    <row r="2500" spans="1:2" ht="15.5">
       <c r="A2500" s="14" t="s">
         <v>4929</v>
       </c>
@@ -92572,7 +92569,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="2501" spans="1:2" ht="15.75">
+    <row r="2501" spans="1:2" ht="15.5">
       <c r="A2501" s="14" t="s">
         <v>4928</v>
       </c>
@@ -95864,7 +95861,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="2912" spans="1:3" ht="15.75">
+    <row r="2912" spans="1:3" ht="15.5">
       <c r="A2912" s="14" t="s">
         <v>4303</v>
       </c>
@@ -95872,7 +95869,7 @@
         <v>4304</v>
       </c>
     </row>
-    <row r="2913" spans="1:2" ht="15.75">
+    <row r="2913" spans="1:2" ht="15.5">
       <c r="A2913" s="14" t="s">
         <v>4302</v>
       </c>
@@ -95880,7 +95877,7 @@
         <v>4295</v>
       </c>
     </row>
-    <row r="2914" spans="1:2" ht="15.75">
+    <row r="2914" spans="1:2" ht="15.5">
       <c r="A2914" s="14" t="s">
         <v>4305</v>
       </c>
@@ -95976,7 +95973,7 @@
         <v>4313</v>
       </c>
     </row>
-    <row r="2926" spans="1:2" ht="15.75">
+    <row r="2926" spans="1:2" ht="15.5">
       <c r="A2926" s="14" t="s">
         <v>4045</v>
       </c>
@@ -95984,7 +95981,7 @@
         <v>4294</v>
       </c>
     </row>
-    <row r="2927" spans="1:2" ht="15.75">
+    <row r="2927" spans="1:2" ht="15.5">
       <c r="A2927" s="14" t="s">
         <v>1654</v>
       </c>
@@ -97230,7 +97227,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="3083" spans="1:2" ht="15.75">
+    <row r="3083" spans="1:2" ht="15.5">
       <c r="A3083" s="14" t="s">
         <v>5115</v>
       </c>
@@ -99545,7 +99542,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="3373" spans="1:2" ht="15.75">
+    <row r="3373" spans="1:2" ht="15.5">
       <c r="A3373" s="14" t="s">
         <v>3188</v>
       </c>
@@ -99553,7 +99550,7 @@
         <v>3189</v>
       </c>
     </row>
-    <row r="3374" spans="1:2" ht="15.75">
+    <row r="3374" spans="1:2" ht="15.5">
       <c r="A3374" s="14" t="s">
         <v>3190</v>
       </c>
@@ -99561,7 +99558,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="3375" spans="1:2" ht="15.75">
+    <row r="3375" spans="1:2" ht="15.5">
       <c r="A3375" s="14" t="s">
         <v>2414</v>
       </c>
@@ -100457,7 +100454,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="3487" spans="1:2" ht="15.75">
+    <row r="3487" spans="1:2" ht="15.5">
       <c r="A3487" s="14" t="s">
         <v>3759</v>
       </c>
@@ -100473,7 +100470,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="3489" spans="1:2" ht="15.75">
+    <row r="3489" spans="1:2" ht="15.5">
       <c r="A3489" s="14" t="s">
         <v>3550</v>
       </c>
@@ -100481,7 +100478,7 @@
         <v>3765</v>
       </c>
     </row>
-    <row r="3490" spans="1:2" ht="15.75">
+    <row r="3490" spans="1:2" ht="15.5">
       <c r="A3490" s="14" t="s">
         <v>3770</v>
       </c>
@@ -100489,7 +100486,7 @@
         <v>3771</v>
       </c>
     </row>
-    <row r="3491" spans="1:2" ht="15.75">
+    <row r="3491" spans="1:2" ht="15.5">
       <c r="A3491" s="14" t="s">
         <v>3766</v>
       </c>
@@ -100497,7 +100494,7 @@
         <v>3767</v>
       </c>
     </row>
-    <row r="3492" spans="1:2" ht="15.75">
+    <row r="3492" spans="1:2" ht="15.5">
       <c r="A3492" s="14" t="s">
         <v>3768</v>
       </c>
@@ -100505,7 +100502,7 @@
         <v>3769</v>
       </c>
     </row>
-    <row r="3493" spans="1:2" ht="15.75">
+    <row r="3493" spans="1:2" ht="15.5">
       <c r="A3493" s="14" t="s">
         <v>3762</v>
       </c>
@@ -100513,7 +100510,7 @@
         <v>3763</v>
       </c>
     </row>
-    <row r="3494" spans="1:2" ht="15.75">
+    <row r="3494" spans="1:2" ht="15.5">
       <c r="A3494" s="14" t="s">
         <v>3609</v>
       </c>
@@ -100601,7 +100598,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="3505" spans="1:2" ht="15.75">
+    <row r="3505" spans="1:2" ht="15.5">
       <c r="A3505" s="14" t="s">
         <v>3595</v>
       </c>
@@ -100609,7 +100606,7 @@
         <v>3764</v>
       </c>
     </row>
-    <row r="3506" spans="1:2" ht="15.75">
+    <row r="3506" spans="1:2" ht="15.5">
       <c r="A3506" s="14" t="s">
         <v>3760</v>
       </c>
@@ -100617,7 +100614,7 @@
         <v>3761</v>
       </c>
     </row>
-    <row r="3507" spans="1:2" ht="15.75">
+    <row r="3507" spans="1:2" ht="15.5">
       <c r="A3507" s="14" t="s">
         <v>3580</v>
       </c>
@@ -100721,7 +100718,7 @@
         <v>3410</v>
       </c>
     </row>
-    <row r="3520" spans="1:2" ht="15.75">
+    <row r="3520" spans="1:2" ht="15.5">
       <c r="A3520" s="14" t="s">
         <v>4023</v>
       </c>
@@ -101241,7 +101238,7 @@
         <v>5152</v>
       </c>
     </row>
-    <row r="3585" spans="1:2" ht="15.75">
+    <row r="3585" spans="1:2" ht="15.5">
       <c r="A3585" s="14" t="s">
         <v>5140</v>
       </c>
@@ -101265,7 +101262,7 @@
         <v>5146</v>
       </c>
     </row>
-    <row r="3588" spans="1:2" ht="15.75">
+    <row r="3588" spans="1:2" ht="15.5">
       <c r="A3588" s="14" t="s">
         <v>5142</v>
       </c>
@@ -103927,7 +103924,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D669A2-CEB8-B743-9F48-CA926DA2420B}">
   <dimension ref="A1:C144"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="39.26953125" customWidth="1"/>
     <col min="2" max="2" width="29.08984375" customWidth="1"/>
@@ -104336,7 +104333,7 @@
         <v>3007</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75">
+    <row r="53" spans="1:2" ht="15.5">
       <c r="A53" s="14" t="s">
         <v>2410</v>
       </c>
@@ -104344,7 +104341,7 @@
         <v>3009</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75">
+    <row r="54" spans="1:2" ht="15.5">
       <c r="A54" s="14" t="s">
         <v>3010</v>
       </c>
@@ -105059,7 +105056,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5409384-14AD-406E-9225-D6E905D70DE3}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="17.36328125" customWidth="1"/>
     <col min="2" max="2" width="22.36328125" customWidth="1"/>
@@ -105142,7 +105139,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AD7347-2C61-4ECD-8840-77BC33B67550}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.453125" bestFit="1" customWidth="1"/>
@@ -105235,7 +105232,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E9C919-AB17-4E01-B682-B50EBBDCE176}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
